--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="134">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>Prior-Year ADA</t>
+  </si>
+  <si>
+    <t>Attendance Ratio (ADA ÷ ADM)</t>
   </si>
   <si>
     <t>Per-Pupil Rate — K-5</t>
@@ -598,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -621,6 +624,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1555,9 +1561,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C70" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D70" s="14">
+        <v>0.95</v>
+      </c>
+    </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C71" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D71" s="12">
         <v>8200</v>
@@ -1565,7 +1579,7 @@
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C72" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D72" s="12">
         <v>9100</v>
@@ -1573,40 +1587,40 @@
     </row>
     <row r="73" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C73" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D73" s="12">
         <v>10500</v>
       </c>
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C75" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D75" s="14"/>
+      <c r="C75" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D75" s="15"/>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C76" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D76" s="15" t="s">
         <v>76</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C77" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D77" s="15" t="s">
         <v>78</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C78" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78" s="15" t="s">
         <v>80</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1645,7 +1659,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -1654,444 +1668,444 @@
       <c r="G1" s="7"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>86</v>
       </c>
+      <c r="G3" s="18" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="B4" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="20">
         <f>Assumptions!D12</f>
         <v>120</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="20">
         <f>Assumptions!D13</f>
         <v>200</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="20">
         <f>Assumptions!D14</f>
         <v>300</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="20">
         <f>Assumptions!D15</f>
         <v>400</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="20">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="20" t="str">
+      <c r="B5" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="21" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="20" t="str">
+      <c r="D5" s="21" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="20" t="str">
+      <c r="E5" s="21" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="20" t="str">
+      <c r="F5" s="21" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="20" t="str">
+      <c r="G5" s="21" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="20" t="str">
+      <c r="B6" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="21" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="20" t="str">
+      <c r="D6" s="21" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="21" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20" t="str">
+      <c r="F6" s="21" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="20" t="str">
+      <c r="G6" s="21" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="21">
         <f>Assumptions!D12*Assumptions!D22</f>
         <v>1242000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>2111400</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>3230442</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>4393401.12</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>5601586.428</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="21">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>48000</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>82400</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>127308</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>174836.32</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="21">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>225101.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="21">
         <f>Assumptions!D27</f>
         <v>175000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>175000</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>175000</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>175000</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="21">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>175000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="B10" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="23">
         <f>C6+C7+C8+C9</f>
         <v>1465000</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="23">
         <f>D6+D7+D8+D9</f>
         <v>2368800</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="23">
         <f>E6+E7+E8+E9</f>
         <v>3532750</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="23">
         <f>F6+F7+F8+F9</f>
         <v>4743237.44</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="23">
         <f>G6+G7+G8+G9</f>
         <v>6001688.19</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="19">
+      <c r="B12" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="20">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>16</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>24</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="20">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>31</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="20">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="20">
+      <c r="B13" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="21">
         <f>C12*Assumptions!D33</f>
         <v>436670</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>719632.16</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>1111831.6872</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>1479199.407179</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>1916756.13504453</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="20">
+      <c r="B14" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="21">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>356250</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>366937.5</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="21">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>377945.625</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="21">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>389283.99375</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="21">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>400962.5135625</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="20">
+      <c r="B15" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="21">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>192566.28571429</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="21">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>263881.20314286</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>361803.06153429</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>453774.54022561</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="21">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>562874.52894742</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="22">
+      <c r="B16" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="23">
         <f>C13+C14+C15</f>
         <v>985486.28571429</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="23">
         <f>D13+D14+D15</f>
         <v>1350450.86314286</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="23">
         <f>E13+E14+E15</f>
         <v>1851580.37373429</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="23">
         <f>F13+F14+F15</f>
         <v>2322257.94115461</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <f>G13+G14+G15</f>
         <v>2880593.17755445</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="20">
+      <c r="B18" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="21">
         <f>Assumptions!D46</f>
         <v>322000</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>331660</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="21">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>341609.8</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="21">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>351858.094</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>362413.83682</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="20" t="str">
+      <c r="B19" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="21" t="str">
         <f>Assumptions!D48</f>
         <v>0</v>
       </c>
-      <c r="D19" s="20" t="str">
+      <c r="D19" s="21" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="20" t="str">
+      <c r="E19" s="21" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>0</v>
       </c>
-      <c r="F19" s="20" t="str">
+      <c r="F19" s="21" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>0</v>
       </c>
-      <c r="G19" s="20" t="str">
+      <c r="G19" s="21" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" s="20">
+      <c r="B20" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="21">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>78000</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="21">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>223333.33333333</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="21">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>575512.82051282</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="21">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>1318268.68288407</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="21">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>2830897.49209079</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C21" s="20">
+      <c r="B21" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="21">
         <f>Assumptions!D52</f>
         <v>204000</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="21">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>309200</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="21">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>468650.19607843</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="21">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>710326.66974241</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="21">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>1076632.38374682</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="C22" s="22">
+      <c r="B22" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="23">
         <f>C18+C19+C20+C21</f>
         <v>604000</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <f>D18+D19+D20+D21</f>
         <v>864193.33333333</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="23">
         <f>E18+E19+E20+E21</f>
         <v>1385772.81659125</v>
       </c>
-      <c r="F22" s="22">
+      <c r="F22" s="23">
         <f>F18+F19+F20+F21</f>
         <v>2380453.44662647</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="23">
         <f>G18+G19+G20+G21</f>
         <v>4269943.71265761</v>
       </c>
@@ -2124,7 +2138,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -2133,294 +2147,294 @@
       <c r="G1" s="7"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>86</v>
       </c>
+      <c r="G3" s="18" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="B5" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="20">
         <f>Drivers!C4</f>
         <v>120</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <f>Drivers!D4</f>
         <v>200</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="20">
         <f>Drivers!E4</f>
         <v>300</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="20">
         <f>Drivers!F4</f>
         <v>400</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="20">
         <f>Drivers!G4</f>
         <v>500</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="20" t="str">
+      <c r="B6" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="21" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="20" t="str">
+      <c r="D6" s="21" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="20" t="str">
+      <c r="E6" s="21" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="20" t="str">
+      <c r="F6" s="21" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="20" t="str">
+      <c r="G6" s="21" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="21">
         <f>Drivers!C7</f>
         <v>1242000</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <f>Drivers!D7</f>
         <v>2111400</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <f>Drivers!E7</f>
         <v>3230442</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <f>Drivers!F7</f>
         <v>4393401.12</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <f>Drivers!G7</f>
         <v>5601586.428</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="21">
         <f>Drivers!C8</f>
         <v>48000</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <f>Drivers!D8</f>
         <v>82400</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <f>Drivers!E8</f>
         <v>127308</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <f>Drivers!F8</f>
         <v>174836.32</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="21">
         <f>Drivers!G8</f>
         <v>225101.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="21">
         <f>Drivers!C9</f>
         <v>175000</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <f>Drivers!D9</f>
         <v>175000</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <f>Drivers!E9</f>
         <v>175000</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <f>Drivers!F9</f>
         <v>175000</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="21">
         <f>Drivers!G9</f>
         <v>175000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="22">
+      <c r="B10" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="23">
         <f>Drivers!C10</f>
         <v>1465000</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="23">
         <f>Drivers!D10</f>
         <v>2368800</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="23">
         <f>Drivers!E10</f>
         <v>3532750</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="23">
         <f>Drivers!F10</f>
         <v>4743237.44</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="23">
         <f>Drivers!G10</f>
         <v>6001688.19</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="20">
+      <c r="B12" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="21">
         <f>Drivers!C16</f>
         <v>985486.28571429</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>Drivers!D16</f>
         <v>1350450.86314286</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>Drivers!E16</f>
         <v>1851580.37373429</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <f>Drivers!F16</f>
         <v>2322257.94115461</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <f>Drivers!G16</f>
         <v>2880593.17755445</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="20">
+      <c r="B13" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="21">
         <f>Drivers!C22</f>
         <v>604000</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>Drivers!D22</f>
         <v>864193.33333333</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>Drivers!E22</f>
         <v>1385772.81659125</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <f>Drivers!F22</f>
         <v>2380453.44662647</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <f>Drivers!G22</f>
         <v>4269943.71265761</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="22">
+      <c r="B15" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="23">
         <f>C12+C13</f>
         <v>1589486.28571429</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="23">
         <f>D12+D13</f>
         <v>2214644.19647619</v>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="23">
         <f>E12+E13</f>
         <v>3237353.19032554</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="23">
         <f>F12+F13</f>
         <v>4702711.38778109</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="23">
         <f>G12+G13</f>
         <v>7150536.89021206</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="23">
+      <c r="B16" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="24">
         <f>C10-C15</f>
         <v>-124486.28571429</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <f>D10-D15</f>
         <v>154155.80352381</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <f>E10-E15</f>
         <v>295396.80967446</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <f>F10-F15</f>
         <v>40526.05221891</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="24">
         <f>G10-G15</f>
         <v>-1148848.70021206</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="25">
+      <c r="B17" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C17" s="26">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.08497357</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>0.06507759</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>0.08361668</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>0.00854396</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>-0.19142092</v>
       </c>
@@ -2453,7 +2467,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -2462,194 +2476,194 @@
       <c r="G1" s="7"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>86</v>
       </c>
+      <c r="G3" s="18" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="20">
+      <c r="B4" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="21">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-124486.28571429</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <f>'5-Year P&amp;L'!D16</f>
         <v>154155.80352381</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="21">
         <f>'5-Year P&amp;L'!E16</f>
         <v>295396.80967446</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <f>'5-Year P&amp;L'!F16</f>
         <v>40526.05221891</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="21">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1148848.70021206</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="20">
+      <c r="B6" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="21">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="20">
+      <c r="B7" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="21">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="23">
         <f>C6+C7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="23">
         <f>D6+D7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="23">
         <f>E6+E7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="23">
         <f>F6+F7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="23">
         <f>G6+G7</f>
         <v>106628.61081549</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="26">
+      <c r="B10" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="27">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.16747545</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>1.44572646</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>2.77033347</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>0.38006734</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="27">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>-10.77430055</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="20">
+      <c r="B12" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="21">
         <f>C4-C8</f>
         <v>-231114.89652978</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>D4-D8</f>
         <v>47527.19270832</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>E4-E8</f>
         <v>188768.19885897</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <f>F4-F8</f>
         <v>-66102.55859658</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <f>G4-G8</f>
         <v>-1255477.31102756</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="28">
+      <c r="B14" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="29">
         <f>Assumptions!D57+C12</f>
         <v>-231114.89652978</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="29">
         <f>C14+D12</f>
         <v>-183587.70382146</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>D14+E12</f>
         <v>5180.49503751</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="29">
         <f>E14+F12</f>
         <v>-60922.06355908</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="29">
         <f>F14+G12</f>
         <v>-1316399.37458663</v>
       </c>
@@ -2682,7 +2696,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -2691,94 +2705,94 @@
       <c r="G1" s="7"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="17" t="s">
+      <c r="B3" s="17"/>
+      <c r="C3" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="D3" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>86</v>
       </c>
+      <c r="G3" s="18" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" s="19">
+      <c r="B4" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="20">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="20">
         <f>Drivers!D12</f>
         <v>16</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="20">
         <f>Drivers!E12</f>
         <v>24</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="20">
         <f>Drivers!F12</f>
         <v>31</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="20">
         <f>Drivers!G12</f>
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="19">
+      <c r="B5" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="20">
         <f>Assumptions!D35</f>
         <v>5</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <f>Assumptions!D36</f>
         <v>5</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="20">
         <f>Assumptions!D37</f>
         <v>5</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="20">
         <f>Assumptions!D38</f>
         <v>5</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="20">
         <f>Assumptions!D39</f>
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="30">
+      <c r="B6" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="31">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="31">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -2811,51 +2825,51 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C1" s="7"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="20">
+      <c r="B3" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="21">
         <f>Assumptions!D59</f>
         <v>350000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="B4" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="26">
         <f>Assumptions!D60</f>
         <v>0.06</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="20">
         <f>Assumptions!D61</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="31">
+      <c r="B6" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="32">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="26">
+      <c r="B8" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="27">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.16747545</v>
       </c>
@@ -2888,76 +2902,76 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C1" s="7"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="18" t="str">
+      <c r="C3" s="19" t="str">
         <f>Assumptions!D5</f>
         <v>Heritage Academy Charter</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="18" t="str">
+      <c r="C4" s="19" t="str">
         <f>Assumptions!D7</f>
         <v>Charter School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="18" t="str">
+      <c r="C5" s="19" t="str">
         <f>Assumptions!D6</f>
         <v>AZ</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="B6" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="19">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="20">
+      <c r="B9" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="21">
         <f>Drivers!G10</f>
         <v>6001688.19</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="C10" s="28">
+      <c r="B10" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="29">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1148848.70021206</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -601,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -658,13 +658,7 @@
     <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,7 +1252,7 @@
         <v>30</v>
       </c>
       <c r="D22" s="12">
-        <v>10350</v>
+        <v>9925</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
@@ -1266,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="D23" s="13">
-        <v>0.02</v>
+        <v>0.005163727959697733</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
@@ -1766,23 +1760,23 @@
       </c>
       <c r="C7" s="21">
         <f>Assumptions!D12*Assumptions!D22</f>
-        <v>1242000</v>
+        <v>1191000</v>
       </c>
       <c r="D7" s="21">
         <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
-        <v>2111400</v>
+        <v>1995250</v>
       </c>
       <c r="E7" s="21">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
-        <v>3230442</v>
+        <v>3008329.39231738</v>
       </c>
       <c r="F7" s="21">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
-        <v>4393401.12</v>
+        <v>4031818.11588329</v>
       </c>
       <c r="G7" s="21">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
-        <v>5601586.428</v>
+        <v>5065796.65977087</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -1841,23 +1835,23 @@
       </c>
       <c r="C10" s="23">
         <f>C6+C7+C8+C9</f>
-        <v>1465000</v>
+        <v>1414000</v>
       </c>
       <c r="D10" s="23">
         <f>D6+D7+D8+D9</f>
-        <v>2368800</v>
+        <v>2252650</v>
       </c>
       <c r="E10" s="23">
         <f>E6+E7+E8+E9</f>
-        <v>3532750</v>
+        <v>3310637.39231738</v>
       </c>
       <c r="F10" s="23">
         <f>F6+F7+F8+F9</f>
-        <v>4743237.44</v>
+        <v>4381654.43588329</v>
       </c>
       <c r="G10" s="23">
         <f>G6+G7+G8+G9</f>
-        <v>6001688.19</v>
+        <v>5465898.42177087</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2220,23 +2214,23 @@
       </c>
       <c r="C7" s="21">
         <f>Drivers!C7</f>
-        <v>1242000</v>
+        <v>1191000</v>
       </c>
       <c r="D7" s="21">
         <f>Drivers!D7</f>
-        <v>2111400</v>
+        <v>1995250</v>
       </c>
       <c r="E7" s="21">
         <f>Drivers!E7</f>
-        <v>3230442</v>
+        <v>3008329.39231738</v>
       </c>
       <c r="F7" s="21">
         <f>Drivers!F7</f>
-        <v>4393401.12</v>
+        <v>4031818.11588329</v>
       </c>
       <c r="G7" s="21">
         <f>Drivers!G7</f>
-        <v>5601586.428</v>
+        <v>5065796.65977087</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2295,23 +2289,23 @@
       </c>
       <c r="C10" s="23">
         <f>Drivers!C10</f>
-        <v>1465000</v>
+        <v>1414000</v>
       </c>
       <c r="D10" s="23">
         <f>Drivers!D10</f>
-        <v>2368800</v>
+        <v>2252650</v>
       </c>
       <c r="E10" s="23">
         <f>Drivers!E10</f>
-        <v>3532750</v>
+        <v>3310637.39231738</v>
       </c>
       <c r="F10" s="23">
         <f>Drivers!F10</f>
-        <v>4743237.44</v>
+        <v>4381654.43588329</v>
       </c>
       <c r="G10" s="23">
         <f>Drivers!G10</f>
-        <v>6001688.19</v>
+        <v>5465898.42177087</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2395,23 +2389,23 @@
       </c>
       <c r="C16" s="24">
         <f>C10-C15</f>
-        <v>-124486.28571429</v>
+        <v>-175486.28571429</v>
       </c>
       <c r="D16" s="25">
         <f>D10-D15</f>
-        <v>154155.80352381</v>
+        <v>38005.80352381</v>
       </c>
       <c r="E16" s="25">
         <f>E10-E15</f>
-        <v>295396.80967446</v>
-      </c>
-      <c r="F16" s="25">
+        <v>73284.20199184</v>
+      </c>
+      <c r="F16" s="24">
         <f>F10-F15</f>
-        <v>40526.05221891</v>
+        <v>-321056.9518978</v>
       </c>
       <c r="G16" s="24">
         <f>G10-G15</f>
-        <v>-1148848.70021206</v>
+        <v>-1684638.46844119</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2420,23 +2414,23 @@
       </c>
       <c r="C17" s="26">
         <f>IF(C10&gt;0,C16/C10,0)</f>
-        <v>-0.08497357</v>
+        <v>-0.12410628</v>
       </c>
       <c r="D17" s="26">
         <f>IF(D10&gt;0,D16/D10,0)</f>
-        <v>0.06507759</v>
+        <v>0.0168716</v>
       </c>
       <c r="E17" s="26">
         <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0.08361668</v>
+        <v>0.02213598</v>
       </c>
       <c r="F17" s="26">
         <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>0.00854396</v>
+        <v>-0.073273</v>
       </c>
       <c r="G17" s="26">
         <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>-0.19142092</v>
+        <v>-0.30820889</v>
       </c>
     </row>
   </sheetData>
@@ -2499,23 +2493,23 @@
       </c>
       <c r="C4" s="21">
         <f>'5-Year P&amp;L'!C16</f>
-        <v>-124486.28571429</v>
+        <v>-175486.28571429</v>
       </c>
       <c r="D4" s="21">
         <f>'5-Year P&amp;L'!D16</f>
-        <v>154155.80352381</v>
+        <v>38005.80352381</v>
       </c>
       <c r="E4" s="21">
         <f>'5-Year P&amp;L'!E16</f>
-        <v>295396.80967446</v>
+        <v>73284.20199184</v>
       </c>
       <c r="F4" s="21">
         <f>'5-Year P&amp;L'!F16</f>
-        <v>40526.05221891</v>
+        <v>-321056.9518978</v>
       </c>
       <c r="G4" s="21">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-1148848.70021206</v>
+        <v>-1684638.46844119</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2599,23 +2593,23 @@
       </c>
       <c r="C10" s="27">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
-        <v>-1.16747545</v>
-      </c>
-      <c r="D10" s="28">
+        <v>-1.6457711</v>
+      </c>
+      <c r="D10" s="27">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
-        <v>1.44572646</v>
-      </c>
-      <c r="E10" s="28">
+        <v>0.35643157</v>
+      </c>
+      <c r="E10" s="27">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
-        <v>2.77033347</v>
+        <v>0.6872846</v>
       </c>
       <c r="F10" s="27">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
-        <v>0.38006734</v>
+        <v>-3.01098316</v>
       </c>
       <c r="G10" s="27">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
-        <v>-10.77430055</v>
+        <v>-15.79912235</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2624,48 +2618,48 @@
       </c>
       <c r="C12" s="21">
         <f>C4-C8</f>
-        <v>-231114.89652978</v>
+        <v>-282114.89652978</v>
       </c>
       <c r="D12" s="21">
         <f>D4-D8</f>
-        <v>47527.19270832</v>
+        <v>-68622.80729168</v>
       </c>
       <c r="E12" s="21">
         <f>E4-E8</f>
-        <v>188768.19885897</v>
+        <v>-33344.40882365</v>
       </c>
       <c r="F12" s="21">
         <f>F4-F8</f>
-        <v>-66102.55859658</v>
+        <v>-427685.56271329</v>
       </c>
       <c r="G12" s="21">
         <f>G4-G8</f>
-        <v>-1255477.31102756</v>
+        <v>-1791267.07925669</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="28">
         <f>Assumptions!D57+C12</f>
-        <v>-231114.89652978</v>
-      </c>
-      <c r="D14" s="29">
+        <v>-282114.89652978</v>
+      </c>
+      <c r="D14" s="28">
         <f>C14+D12</f>
-        <v>-183587.70382146</v>
-      </c>
-      <c r="E14" s="30">
+        <v>-350737.70382146</v>
+      </c>
+      <c r="E14" s="28">
         <f>D14+E12</f>
-        <v>5180.49503751</v>
-      </c>
-      <c r="F14" s="29">
+        <v>-384082.11264511</v>
+      </c>
+      <c r="F14" s="28">
         <f>E14+F12</f>
-        <v>-60922.06355908</v>
-      </c>
-      <c r="G14" s="29">
+        <v>-811767.6753584</v>
+      </c>
+      <c r="G14" s="28">
         <f>F14+G12</f>
-        <v>-1316399.37458663</v>
+        <v>-2603034.75461509</v>
       </c>
     </row>
   </sheetData>
@@ -2776,23 +2770,23 @@
       <c r="B6" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="29">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="29">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="29">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="29">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="31">
+      <c r="G6" s="29">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -2860,7 +2854,7 @@
       <c r="B6" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
@@ -2871,7 +2865,7 @@
       </c>
       <c r="C8" s="27">
         <f>'Cash Flow &amp; DSCR'!C10</f>
-        <v>-1.16747545</v>
+        <v>-1.6457711</v>
       </c>
     </row>
   </sheetData>
@@ -2957,16 +2951,16 @@
       </c>
       <c r="C9" s="21">
         <f>Drivers!G10</f>
-        <v>6001688.19</v>
+        <v>5465898.42177087</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="28">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-1148848.70021206</v>
+        <v>-1684638.46844119</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -513,7 +513,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,6 +538,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -601,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -656,6 +661,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1252,7 +1260,7 @@
         <v>30</v>
       </c>
       <c r="D22" s="12">
-        <v>9925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
@@ -1260,7 +1268,7 @@
         <v>31</v>
       </c>
       <c r="D23" s="13">
-        <v>0.005163727959697733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
@@ -1768,15 +1776,15 @@
       </c>
       <c r="E7" s="21">
         <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
-        <v>3008329.39231738</v>
+        <v>3043400</v>
       </c>
       <c r="F7" s="21">
         <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
-        <v>4031818.11588329</v>
+        <v>4113050</v>
       </c>
       <c r="G7" s="21">
         <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
-        <v>5065796.65977087</v>
+        <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -1843,15 +1851,15 @@
       </c>
       <c r="E10" s="23">
         <f>E6+E7+E8+E9</f>
-        <v>3310637.39231738</v>
+        <v>3345708</v>
       </c>
       <c r="F10" s="23">
         <f>F6+F7+F8+F9</f>
-        <v>4381654.43588329</v>
+        <v>4462886.32</v>
       </c>
       <c r="G10" s="23">
         <f>G6+G7+G8+G9</f>
-        <v>5465898.42177087</v>
+        <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2222,15 +2230,15 @@
       </c>
       <c r="E7" s="21">
         <f>Drivers!E7</f>
-        <v>3008329.39231738</v>
+        <v>3043400</v>
       </c>
       <c r="F7" s="21">
         <f>Drivers!F7</f>
-        <v>4031818.11588329</v>
+        <v>4113050</v>
       </c>
       <c r="G7" s="21">
         <f>Drivers!G7</f>
-        <v>5065796.65977087</v>
+        <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2297,15 +2305,15 @@
       </c>
       <c r="E10" s="23">
         <f>Drivers!E10</f>
-        <v>3310637.39231738</v>
+        <v>3345708</v>
       </c>
       <c r="F10" s="23">
         <f>Drivers!F10</f>
-        <v>4381654.43588329</v>
+        <v>4462886.32</v>
       </c>
       <c r="G10" s="23">
         <f>Drivers!G10</f>
-        <v>5465898.42177087</v>
+        <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2397,15 +2405,15 @@
       </c>
       <c r="E16" s="25">
         <f>E10-E15</f>
-        <v>73284.20199184</v>
+        <v>108354.80967446</v>
       </c>
       <c r="F16" s="24">
         <f>F10-F15</f>
-        <v>-321056.9518978</v>
+        <v>-239825.06778109</v>
       </c>
       <c r="G16" s="24">
         <f>G10-G15</f>
-        <v>-1684638.46844119</v>
+        <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2422,15 +2430,15 @@
       </c>
       <c r="E17" s="26">
         <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0.02213598</v>
+        <v>0.03238621</v>
       </c>
       <c r="F17" s="26">
         <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>-0.073273</v>
+        <v>-0.05373766</v>
       </c>
       <c r="G17" s="26">
         <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>-0.30820889</v>
+        <v>-0.26899529</v>
       </c>
     </row>
   </sheetData>
@@ -2501,15 +2509,15 @@
       </c>
       <c r="E4" s="21">
         <f>'5-Year P&amp;L'!E16</f>
-        <v>73284.20199184</v>
+        <v>108354.80967446</v>
       </c>
       <c r="F4" s="21">
         <f>'5-Year P&amp;L'!F16</f>
-        <v>-321056.9518978</v>
+        <v>-239825.06778109</v>
       </c>
       <c r="G4" s="21">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-1684638.46844119</v>
+        <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2599,17 +2607,17 @@
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.35643157</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
-        <v>0.6872846</v>
+        <v>1.01618889</v>
       </c>
       <c r="F10" s="27">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
-        <v>-3.01098316</v>
+        <v>-2.24916245</v>
       </c>
       <c r="G10" s="27">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
-        <v>-15.79912235</v>
+        <v>-14.2150884</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2626,40 +2634,40 @@
       </c>
       <c r="E12" s="21">
         <f>E4-E8</f>
-        <v>-33344.40882365</v>
+        <v>1726.19885897</v>
       </c>
       <c r="F12" s="21">
         <f>F4-F8</f>
-        <v>-427685.56271329</v>
+        <v>-346453.67859658</v>
       </c>
       <c r="G12" s="21">
         <f>G4-G8</f>
-        <v>-1791267.07925669</v>
+        <v>-1622363.73902756</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="29">
         <f>Assumptions!D57+C12</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="29">
         <f>C14+D12</f>
         <v>-350737.70382146</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="29">
         <f>D14+E12</f>
-        <v>-384082.11264511</v>
-      </c>
-      <c r="F14" s="28">
+        <v>-349011.50496249</v>
+      </c>
+      <c r="F14" s="29">
         <f>E14+F12</f>
-        <v>-811767.6753584</v>
-      </c>
-      <c r="G14" s="28">
+        <v>-695465.18355908</v>
+      </c>
+      <c r="G14" s="29">
         <f>F14+G12</f>
-        <v>-2603034.75461509</v>
+        <v>-2317828.92258663</v>
       </c>
     </row>
   </sheetData>
@@ -2770,23 +2778,23 @@
       <c r="B6" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="30">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -2854,7 +2862,7 @@
       <c r="B6" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
@@ -2951,16 +2959,16 @@
       </c>
       <c r="C9" s="21">
         <f>Drivers!G10</f>
-        <v>5465898.42177087</v>
+        <v>5634801.762</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-1684638.46844119</v>
+        <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -1767,23 +1767,18 @@
         <v>91</v>
       </c>
       <c r="C7" s="21">
-        <f>Assumptions!D12*Assumptions!D22</f>
         <v>1191000</v>
       </c>
       <c r="D7" s="21">
-        <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>1995250</v>
       </c>
       <c r="E7" s="21">
-        <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
         <v>3043400</v>
       </c>
       <c r="F7" s="21">
-        <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
         <v>4113050</v>
       </c>
       <c r="G7" s="21">
-        <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
         <v>5234700</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -513,7 +513,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,11 +538,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -606,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -661,9 +656,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1260,7 +1252,7 @@
         <v>30</v>
       </c>
       <c r="D22" s="12">
-        <v>0</v>
+        <v>9925</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
@@ -1268,7 +1260,7 @@
         <v>31</v>
       </c>
       <c r="D23" s="13">
-        <v>0</v>
+        <v>0.005163727959697733</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
@@ -1767,19 +1759,24 @@
         <v>91</v>
       </c>
       <c r="C7" s="21">
+        <f>Assumptions!D12*Assumptions!D22</f>
         <v>1191000</v>
       </c>
       <c r="D7" s="21">
+        <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>1995250</v>
       </c>
       <c r="E7" s="21">
-        <v>3043400</v>
+        <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
+        <v>3008329.39231738</v>
       </c>
       <c r="F7" s="21">
-        <v>4113050</v>
+        <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
+        <v>4031818.11588329</v>
       </c>
       <c r="G7" s="21">
-        <v>5234700</v>
+        <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
+        <v>5065796.65977087</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -1846,15 +1843,15 @@
       </c>
       <c r="E10" s="23">
         <f>E6+E7+E8+E9</f>
-        <v>3345708</v>
+        <v>3310637.39231738</v>
       </c>
       <c r="F10" s="23">
         <f>F6+F7+F8+F9</f>
-        <v>4462886.32</v>
+        <v>4381654.43588329</v>
       </c>
       <c r="G10" s="23">
         <f>G6+G7+G8+G9</f>
-        <v>5634801.762</v>
+        <v>5465898.42177087</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2225,15 +2222,15 @@
       </c>
       <c r="E7" s="21">
         <f>Drivers!E7</f>
-        <v>3043400</v>
+        <v>3008329.39231738</v>
       </c>
       <c r="F7" s="21">
         <f>Drivers!F7</f>
-        <v>4113050</v>
+        <v>4031818.11588329</v>
       </c>
       <c r="G7" s="21">
         <f>Drivers!G7</f>
-        <v>5234700</v>
+        <v>5065796.65977087</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2300,15 +2297,15 @@
       </c>
       <c r="E10" s="23">
         <f>Drivers!E10</f>
-        <v>3345708</v>
+        <v>3310637.39231738</v>
       </c>
       <c r="F10" s="23">
         <f>Drivers!F10</f>
-        <v>4462886.32</v>
+        <v>4381654.43588329</v>
       </c>
       <c r="G10" s="23">
         <f>Drivers!G10</f>
-        <v>5634801.762</v>
+        <v>5465898.42177087</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2400,15 +2397,15 @@
       </c>
       <c r="E16" s="25">
         <f>E10-E15</f>
-        <v>108354.80967446</v>
+        <v>73284.20199184</v>
       </c>
       <c r="F16" s="24">
         <f>F10-F15</f>
-        <v>-239825.06778109</v>
+        <v>-321056.9518978</v>
       </c>
       <c r="G16" s="24">
         <f>G10-G15</f>
-        <v>-1515735.12821206</v>
+        <v>-1684638.46844119</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2425,15 +2422,15 @@
       </c>
       <c r="E17" s="26">
         <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0.03238621</v>
+        <v>0.02213598</v>
       </c>
       <c r="F17" s="26">
         <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>-0.05373766</v>
+        <v>-0.073273</v>
       </c>
       <c r="G17" s="26">
         <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>-0.26899529</v>
+        <v>-0.30820889</v>
       </c>
     </row>
   </sheetData>
@@ -2504,15 +2501,15 @@
       </c>
       <c r="E4" s="21">
         <f>'5-Year P&amp;L'!E16</f>
-        <v>108354.80967446</v>
+        <v>73284.20199184</v>
       </c>
       <c r="F4" s="21">
         <f>'5-Year P&amp;L'!F16</f>
-        <v>-239825.06778109</v>
+        <v>-321056.9518978</v>
       </c>
       <c r="G4" s="21">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-1515735.12821206</v>
+        <v>-1684638.46844119</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2602,17 +2599,17 @@
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.35643157</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="27">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
-        <v>1.01618889</v>
+        <v>0.6872846</v>
       </c>
       <c r="F10" s="27">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
-        <v>-2.24916245</v>
+        <v>-3.01098316</v>
       </c>
       <c r="G10" s="27">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
-        <v>-14.2150884</v>
+        <v>-15.79912235</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2629,40 +2626,40 @@
       </c>
       <c r="E12" s="21">
         <f>E4-E8</f>
-        <v>1726.19885897</v>
+        <v>-33344.40882365</v>
       </c>
       <c r="F12" s="21">
         <f>F4-F8</f>
-        <v>-346453.67859658</v>
+        <v>-427685.56271329</v>
       </c>
       <c r="G12" s="21">
         <f>G4-G8</f>
-        <v>-1622363.73902756</v>
+        <v>-1791267.07925669</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="28">
         <f>Assumptions!D57+C12</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="28">
         <f>C14+D12</f>
         <v>-350737.70382146</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="28">
         <f>D14+E12</f>
-        <v>-349011.50496249</v>
-      </c>
-      <c r="F14" s="29">
+        <v>-384082.11264511</v>
+      </c>
+      <c r="F14" s="28">
         <f>E14+F12</f>
-        <v>-695465.18355908</v>
-      </c>
-      <c r="G14" s="29">
+        <v>-811767.6753584</v>
+      </c>
+      <c r="G14" s="28">
         <f>F14+G12</f>
-        <v>-2317828.92258663</v>
+        <v>-2603034.75461509</v>
       </c>
     </row>
   </sheetData>
@@ -2773,23 +2770,23 @@
       <c r="B6" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="29">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="29">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="29">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -2857,7 +2854,7 @@
       <c r="B6" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
@@ -2954,16 +2951,16 @@
       </c>
       <c r="C9" s="21">
         <f>Drivers!G10</f>
-        <v>5634801.762</v>
+        <v>5465898.42177087</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="28">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-1515735.12821206</v>
+        <v>-1684638.46844119</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -53,7 +53,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 16, 2026</t>
+    <t>Generated March 17, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -466,13 +466,13 @@
     <font>
       <u/>
       <color rgb="FF0563C1"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -489,18 +489,18 @@
     </font>
     <font>
       <color rgb="FF374151"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <color rgb="FF1E293B"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FF374151"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -513,7 +513,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,6 +538,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -601,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -656,6 +661,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1252,7 +1260,7 @@
         <v>30</v>
       </c>
       <c r="D22" s="12">
-        <v>9925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
@@ -1260,7 +1268,7 @@
         <v>31</v>
       </c>
       <c r="D23" s="13">
-        <v>0.005163727959697733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
@@ -1759,24 +1767,19 @@
         <v>91</v>
       </c>
       <c r="C7" s="21">
-        <f>Assumptions!D12*Assumptions!D22</f>
         <v>1191000</v>
       </c>
       <c r="D7" s="21">
-        <f>Assumptions!D13*Assumptions!D22*(1+Assumptions!D23)^1</f>
         <v>1995250</v>
       </c>
       <c r="E7" s="21">
-        <f>Assumptions!D14*Assumptions!D22*(1+Assumptions!D23)^2</f>
-        <v>3008329.39231738</v>
+        <v>3043400</v>
       </c>
       <c r="F7" s="21">
-        <f>Assumptions!D15*Assumptions!D22*(1+Assumptions!D23)^3</f>
-        <v>4031818.11588329</v>
+        <v>4113050</v>
       </c>
       <c r="G7" s="21">
-        <f>Assumptions!D16*Assumptions!D22*(1+Assumptions!D23)^4</f>
-        <v>5065796.65977087</v>
+        <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -1843,15 +1846,15 @@
       </c>
       <c r="E10" s="23">
         <f>E6+E7+E8+E9</f>
-        <v>3310637.39231738</v>
+        <v>3345708</v>
       </c>
       <c r="F10" s="23">
         <f>F6+F7+F8+F9</f>
-        <v>4381654.43588329</v>
+        <v>4462886.32</v>
       </c>
       <c r="G10" s="23">
         <f>G6+G7+G8+G9</f>
-        <v>5465898.42177087</v>
+        <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2222,15 +2225,15 @@
       </c>
       <c r="E7" s="21">
         <f>Drivers!E7</f>
-        <v>3008329.39231738</v>
+        <v>3043400</v>
       </c>
       <c r="F7" s="21">
         <f>Drivers!F7</f>
-        <v>4031818.11588329</v>
+        <v>4113050</v>
       </c>
       <c r="G7" s="21">
         <f>Drivers!G7</f>
-        <v>5065796.65977087</v>
+        <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -2297,15 +2300,15 @@
       </c>
       <c r="E10" s="23">
         <f>Drivers!E10</f>
-        <v>3310637.39231738</v>
+        <v>3345708</v>
       </c>
       <c r="F10" s="23">
         <f>Drivers!F10</f>
-        <v>4381654.43588329</v>
+        <v>4462886.32</v>
       </c>
       <c r="G10" s="23">
         <f>Drivers!G10</f>
-        <v>5465898.42177087</v>
+        <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2397,15 +2400,15 @@
       </c>
       <c r="E16" s="25">
         <f>E10-E15</f>
-        <v>73284.20199184</v>
+        <v>108354.80967446</v>
       </c>
       <c r="F16" s="24">
         <f>F10-F15</f>
-        <v>-321056.9518978</v>
+        <v>-239825.06778109</v>
       </c>
       <c r="G16" s="24">
         <f>G10-G15</f>
-        <v>-1684638.46844119</v>
+        <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
@@ -2422,15 +2425,15 @@
       </c>
       <c r="E17" s="26">
         <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0.02213598</v>
+        <v>0.03238621</v>
       </c>
       <c r="F17" s="26">
         <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>-0.073273</v>
+        <v>-0.05373766</v>
       </c>
       <c r="G17" s="26">
         <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>-0.30820889</v>
+        <v>-0.26899529</v>
       </c>
     </row>
   </sheetData>
@@ -2501,15 +2504,15 @@
       </c>
       <c r="E4" s="21">
         <f>'5-Year P&amp;L'!E16</f>
-        <v>73284.20199184</v>
+        <v>108354.80967446</v>
       </c>
       <c r="F4" s="21">
         <f>'5-Year P&amp;L'!F16</f>
-        <v>-321056.9518978</v>
+        <v>-239825.06778109</v>
       </c>
       <c r="G4" s="21">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-1684638.46844119</v>
+        <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -2599,17 +2602,17 @@
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.35643157</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
-        <v>0.6872846</v>
+        <v>1.01618889</v>
       </c>
       <c r="F10" s="27">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
-        <v>-3.01098316</v>
+        <v>-2.24916245</v>
       </c>
       <c r="G10" s="27">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
-        <v>-15.79912235</v>
+        <v>-14.2150884</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -2626,40 +2629,40 @@
       </c>
       <c r="E12" s="21">
         <f>E4-E8</f>
-        <v>-33344.40882365</v>
+        <v>1726.19885897</v>
       </c>
       <c r="F12" s="21">
         <f>F4-F8</f>
-        <v>-427685.56271329</v>
+        <v>-346453.67859658</v>
       </c>
       <c r="G12" s="21">
         <f>G4-G8</f>
-        <v>-1791267.07925669</v>
+        <v>-1622363.73902756</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="29">
         <f>Assumptions!D57+C12</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="29">
         <f>C14+D12</f>
         <v>-350737.70382146</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="29">
         <f>D14+E12</f>
-        <v>-384082.11264511</v>
-      </c>
-      <c r="F14" s="28">
+        <v>-349011.50496249</v>
+      </c>
+      <c r="F14" s="29">
         <f>E14+F12</f>
-        <v>-811767.6753584</v>
-      </c>
-      <c r="G14" s="28">
+        <v>-695465.18355908</v>
+      </c>
+      <c r="G14" s="29">
         <f>F14+G12</f>
-        <v>-2603034.75461509</v>
+        <v>-2317828.92258663</v>
       </c>
     </row>
   </sheetData>
@@ -2770,23 +2773,23 @@
       <c r="B6" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="30">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="30">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -2854,7 +2857,7 @@
       <c r="B6" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
@@ -2951,16 +2954,16 @@
       </c>
       <c r="C9" s="21">
         <f>Drivers!G10</f>
-        <v>5465898.42177087</v>
+        <v>5634801.762</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>'5-Year P&amp;L'!G16</f>
-        <v>-1684638.46844119</v>
+        <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -59,7 +59,7 @@
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
-    <t>SchoolStack Budget — Lender Pro Forma Assumptions</t>
+    <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -143,19 +143,19 @@
     <t>Teacher Salary Growth %</t>
   </si>
   <si>
-    <t>Admin FTE — Year 1</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 2</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 3</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 4</t>
-  </si>
-  <si>
-    <t>Admin FTE — Year 5</t>
+    <t>Admin FTE - Year 1</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 2</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 3</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 4</t>
+  </si>
+  <si>
+    <t>Admin FTE - Year 5</t>
   </si>
   <si>
     <t>Avg Admin Salary (Year 1)</t>
@@ -236,13 +236,13 @@
     <t>Attendance Ratio (ADA ÷ ADM)</t>
   </si>
   <si>
-    <t>Per-Pupil Rate — K-5</t>
-  </si>
-  <si>
-    <t>Per-Pupil Rate — 6-8</t>
-  </si>
-  <si>
-    <t>Per-Pupil Rate — 9-12</t>
+    <t>Per-Pupil Rate - K-5</t>
+  </si>
+  <si>
+    <t>Per-Pupil Rate - 6-8</t>
+  </si>
+  <si>
+    <t>Per-Pupil Rate - 9-12</t>
   </si>
   <si>
     <t>Grade-Band Enrollment by Year</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -53,7 +53,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 17, 2026</t>
+    <t>Generated March 18, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -5,20 +5,22 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Cover" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Assumptions" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Drivers" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="5-Year P&amp;L" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Cash Flow &amp; DSCR" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Staffing" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Loan Snapshot" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Summary" state="visible" r:id="rId11"/>
+    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Assumptions" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Cash Flow &amp; DSCR" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="195">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -53,12 +55,81 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 18, 2026</t>
+    <t>Generated March 26, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
   <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t>Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
+  </si>
+  <si>
+    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
@@ -420,6 +491,120 @@
   </si>
   <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
+  </si>
+  <si>
+    <t>Heritage Academy Charter — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Personnel</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>Debt Service</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>○ Needs attention</t>
+  </si>
+  <si>
+    <t>Year 5 margin of -29% signals the model is not yet on a sustainable path.</t>
+  </si>
+  <si>
+    <t>Revisit revenue assumptions and cost structure to build a clear path to break-even.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+  </si>
+  <si>
+    <t>Secure a line of credit or bridge funding before operations begin.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>Staffing at 51% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 23% of revenue are high. Fixed costs this size create rigidity in your budget.</t>
+  </si>
+  <si>
+    <t>Explore shared space, renegotiate terms, or consider a smaller facility.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of -14.22x means operating income does not cover debt payments. This must be resolved.</t>
+  </si>
+  <si>
+    <t>Reduce loan amounts, extend terms, or increase revenue before committing to this debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>Less than 1 month of reserves by Year 5. The school has no financial cushion.</t>
+  </si>
+  <si>
+    <t>Prioritize building reserves — even a small surplus each year compounds into meaningful protection.</t>
+  </si>
+  <si>
+    <t>2 Healthy  |  0 Watch  |  5 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
@@ -432,7 +617,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -476,6 +661,10 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FF1E293B"/>
       <sz val="14"/>
@@ -504,16 +693,30 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -543,6 +746,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
   </fills>
@@ -606,7 +814,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -614,37 +822,39 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -657,7 +867,7 @@
     <xf numFmtId="165" fontId="13" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -674,6 +884,32 @@
     </xf>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1124,7 +1360,556 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="22">
+        <v>120</v>
+      </c>
+      <c r="D6" s="22">
+        <v>200</v>
+      </c>
+      <c r="E6" s="22">
+        <v>300</v>
+      </c>
+      <c r="F6" s="22">
+        <v>400</v>
+      </c>
+      <c r="G6" s="22">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="23">
+        <v>1414000</v>
+      </c>
+      <c r="D7" s="23">
+        <v>2252650</v>
+      </c>
+      <c r="E7" s="23">
+        <v>3345708</v>
+      </c>
+      <c r="F7" s="23">
+        <v>4462886.32</v>
+      </c>
+      <c r="G7" s="23">
+        <v>5634801.762</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="23">
+        <v>985486.2857142857</v>
+      </c>
+      <c r="D8" s="23">
+        <v>1350450.8631428573</v>
+      </c>
+      <c r="E8" s="23">
+        <v>1851580.3737342858</v>
+      </c>
+      <c r="F8" s="23">
+        <v>2322257.9411546146</v>
+      </c>
+      <c r="G8" s="23">
+        <v>2880593.1775544523</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="23">
+        <v>604000</v>
+      </c>
+      <c r="D9" s="23">
+        <v>864193.3333333334</v>
+      </c>
+      <c r="E9" s="23">
+        <v>1385772.8165912519</v>
+      </c>
+      <c r="F9" s="23">
+        <v>2380453.4466264746</v>
+      </c>
+      <c r="G9" s="23">
+        <v>4269943.712657611</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="23">
+        <v>106628.6108154935</v>
+      </c>
+      <c r="D10" s="23">
+        <v>106628.6108154935</v>
+      </c>
+      <c r="E10" s="23">
+        <v>106628.6108154935</v>
+      </c>
+      <c r="F10" s="23">
+        <v>106628.6108154935</v>
+      </c>
+      <c r="G10" s="23">
+        <v>106628.6108154935</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="26">
+        <v>-282114.8965297792</v>
+      </c>
+      <c r="D11" s="26">
+        <v>-68622.80729168432</v>
+      </c>
+      <c r="E11" s="27">
+        <v>1726.1988589687971</v>
+      </c>
+      <c r="F11" s="26">
+        <v>-346453.6785965824</v>
+      </c>
+      <c r="G11" s="26">
+        <v>-1622363.739027556</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="26">
+        <v>-282114.8965297792</v>
+      </c>
+      <c r="D12" s="26">
+        <v>-350737.7038214635</v>
+      </c>
+      <c r="E12" s="26">
+        <v>-349011.5049624947</v>
+      </c>
+      <c r="F12" s="26">
+        <v>-695465.1835590771</v>
+      </c>
+      <c r="G12" s="26">
+        <v>-2317828.922586633</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="36">
+        <v>-0.19951548552318188</v>
+      </c>
+      <c r="D13" s="36">
+        <v>-0.03046314664581019</v>
+      </c>
+      <c r="E13" s="37">
+        <v>0.0005159442661968101</v>
+      </c>
+      <c r="F13" s="36">
+        <v>-0.07762995822770193</v>
+      </c>
+      <c r="G13" s="36">
+        <v>-0.2879185120528036</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="G15" s="34"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="G16" s="41"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="F17" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G17" s="41"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="G18" s="41"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="E19" s="40"/>
+      <c r="F19" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="G19" s="41"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41" t="s">
+        <v>186</v>
+      </c>
+      <c r="G20" s="41"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="38" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="G21" s="41"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="F22" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="41"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B26:G26"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:B29"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD97706"/>
@@ -1140,489 +1925,489 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="12">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+    </row>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C12" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C13" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C14" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="13">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C15" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="13">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="13">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C20" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C21" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C26" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="15">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C27" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="14">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C28" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C32" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="13">
         <v>13</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="10">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-    </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="11">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="11">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="11">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="11">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="11">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="12">
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C33" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="14">
+        <v>43667</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C34" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D34" s="15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C35" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D35" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C36" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C37" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C38" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C39" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C40" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="14">
+        <v>71250</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C41" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C42" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" s="15">
+        <v>0.24285714285714285</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C46" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="14">
+        <v>322000</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C47" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" s="15">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C48" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="13">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C49" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" s="15">
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="12">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C50" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="14">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C51" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D51" s="15">
+        <v>0.717948717948718</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C52" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" s="14">
+        <v>204000</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C53" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D53" s="15">
+        <v>0.515686274509804</v>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C57" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="13">
+    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C58" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D58" s="14">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C59" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" s="14">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C60" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D60" s="15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C61" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B64" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C64" s="10"/>
+      <c r="D64" s="10"/>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C66" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C67" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C68" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="12">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="13">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="13">
+    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C69" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D69" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C70" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D70" s="16">
         <v>0.95</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="12">
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="11">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="12">
-        <v>43667</v>
-      </c>
-    </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="13">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D40" s="12">
-        <v>71250</v>
-      </c>
-    </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D41" s="13">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" s="13">
-        <v>0.24285714285714285</v>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-    </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="12">
-        <v>322000</v>
-      </c>
-    </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47" s="13">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="13">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50" s="12">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" s="13">
-        <v>0.717948717948718</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52" s="12">
-        <v>204000</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" s="13">
-        <v>0.515686274509804</v>
-      </c>
-    </row>
-    <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-    </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="D57" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D58" s="12">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D59" s="12">
-        <v>350000</v>
-      </c>
-    </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D60" s="13">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D61" s="11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B64" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-    </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C67" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C68" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D68" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C69" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D69" s="11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C70" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D70" s="14">
-        <v>0.95</v>
-      </c>
-    </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C71" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D71" s="12">
+      <c r="C71" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D71" s="14">
         <v>8200</v>
       </c>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C72" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D72" s="12">
+      <c r="C72" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D72" s="14">
         <v>9100</v>
       </c>
     </row>
     <row r="73" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C73" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D73" s="12">
+      <c r="C73" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D73" s="14">
         <v>10500</v>
       </c>
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C75" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D75" s="15"/>
+      <c r="C75" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D75" s="17"/>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C76" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>77</v>
+      <c r="C76" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C77" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>79</v>
+      <c r="C77" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C78" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D78" s="16" t="s">
-        <v>81</v>
+      <c r="C78" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1645,7 +2430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF0D9488"/>
@@ -1660,780 +2445,451 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>87</v>
+      <c r="B3" s="19"/>
+      <c r="C3" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="20">
+      <c r="B4" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="22">
         <f>Assumptions!D12</f>
         <v>120</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="22">
         <f>Assumptions!D13</f>
         <v>200</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="22">
         <f>Assumptions!D14</f>
         <v>300</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="22">
         <f>Assumptions!D15</f>
         <v>400</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="22">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="21" t="str">
+      <c r="B5" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="23" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="21" t="str">
+      <c r="D5" s="23" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="21" t="str">
+      <c r="E5" s="23" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="21" t="str">
+      <c r="F5" s="23" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="21" t="str">
+      <c r="G5" s="23" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="21" t="str">
+      <c r="B6" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="23" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="21" t="str">
+      <c r="D6" s="23" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="21" t="str">
+      <c r="E6" s="23" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="21" t="str">
+      <c r="F6" s="23" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="21" t="str">
+      <c r="G6" s="23" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="21">
+      <c r="B7" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="23">
         <v>1191000</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="23">
         <v>1995250</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="23">
         <v>3043400</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="23">
         <v>4113050</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="23">
         <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="21">
+      <c r="B8" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="23">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>48000</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="23">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>82400</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="23">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>127308</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="23">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>174836.32</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="23">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>225101.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="21">
+      <c r="B9" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="23">
         <f>Assumptions!D27</f>
         <v>175000</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="23">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>175000</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="23">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>175000</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="23">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>175000</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="23">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>175000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="23">
+      <c r="B10" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="25">
         <f>C6+C7+C8+C9</f>
         <v>1414000</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="25">
         <f>D6+D7+D8+D9</f>
         <v>2252650</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="25">
         <f>E6+E7+E8+E9</f>
         <v>3345708</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="25">
         <f>F6+F7+F8+F9</f>
         <v>4462886.32</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="25">
         <f>G6+G7+G8+G9</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="20">
+      <c r="B12" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="22">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="22">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>16</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="22">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>24</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="22">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>31</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="22">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="21">
+      <c r="B13" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="23">
         <f>C12*Assumptions!D33</f>
         <v>436670</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="23">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>719632.16</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="23">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>1111831.6872</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="23">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>1479199.407179</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="23">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>1916756.13504453</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" s="21">
+      <c r="B14" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="23">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>356250</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="23">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>366937.5</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="23">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>377945.625</v>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="23">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>389283.99375</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="23">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>400962.5135625</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="21">
+      <c r="B15" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="23">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>192566.28571429</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="23">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>263881.20314286</v>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="23">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>361803.06153429</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="23">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>453774.54022561</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="23">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>562874.52894742</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="23">
+      <c r="B16" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="25">
         <f>C13+C14+C15</f>
         <v>985486.28571429</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="25">
         <f>D13+D14+D15</f>
         <v>1350450.86314286</v>
       </c>
-      <c r="E16" s="23">
+      <c r="E16" s="25">
         <f>E13+E14+E15</f>
         <v>1851580.37373429</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="25">
         <f>F13+F14+F15</f>
         <v>2322257.94115461</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="25">
         <f>G13+G14+G15</f>
         <v>2880593.17755445</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C18" s="21">
+      <c r="B18" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="23">
         <f>Assumptions!D46</f>
         <v>322000</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="23">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>331660</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="23">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>341609.8</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="23">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>351858.094</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="23">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>362413.83682</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="21" t="str">
+      <c r="B19" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="23" t="str">
         <f>Assumptions!D48</f>
         <v>0</v>
       </c>
-      <c r="D19" s="21" t="str">
+      <c r="D19" s="23" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="21" t="str">
+      <c r="E19" s="23" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>0</v>
       </c>
-      <c r="F19" s="21" t="str">
+      <c r="F19" s="23" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>0</v>
       </c>
-      <c r="G19" s="21" t="str">
+      <c r="G19" s="23" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="21">
+      <c r="B20" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="23">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>78000</v>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="23">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>223333.33333333</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="23">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>575512.82051282</v>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="23">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>1318268.68288407</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="23">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>2830897.49209079</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="21">
+      <c r="B21" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="23">
         <f>Assumptions!D52</f>
         <v>204000</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="23">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>309200</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="23">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>468650.19607843</v>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="23">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>710326.66974241</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="23">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>1076632.38374682</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="23">
+      <c r="B22" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="25">
         <f>C18+C19+C20+C21</f>
         <v>604000</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="25">
         <f>D18+D19+D20+D21</f>
         <v>864193.33333333</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="25">
         <f>E18+E19+E20+E21</f>
         <v>1385772.81659125</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="25">
         <f>F18+F19+F20+F21</f>
         <v>2380453.44662647</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="25">
         <f>G18+G19+G20+G21</f>
         <v>4269943.71265761</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF328555"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="7" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="20">
-        <f>Drivers!C4</f>
-        <v>120</v>
-      </c>
-      <c r="D5" s="20">
-        <f>Drivers!D4</f>
-        <v>200</v>
-      </c>
-      <c r="E5" s="20">
-        <f>Drivers!E4</f>
-        <v>300</v>
-      </c>
-      <c r="F5" s="20">
-        <f>Drivers!F4</f>
-        <v>400</v>
-      </c>
-      <c r="G5" s="20">
-        <f>Drivers!G4</f>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="21" t="str">
-        <f>Drivers!C6</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="21" t="str">
-        <f>Drivers!D6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="21" t="str">
-        <f>Drivers!E6</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="21" t="str">
-        <f>Drivers!F6</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="21" t="str">
-        <f>Drivers!G6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="21">
-        <f>Drivers!C7</f>
-        <v>1191000</v>
-      </c>
-      <c r="D7" s="21">
-        <f>Drivers!D7</f>
-        <v>1995250</v>
-      </c>
-      <c r="E7" s="21">
-        <f>Drivers!E7</f>
-        <v>3043400</v>
-      </c>
-      <c r="F7" s="21">
-        <f>Drivers!F7</f>
-        <v>4113050</v>
-      </c>
-      <c r="G7" s="21">
-        <f>Drivers!G7</f>
-        <v>5234700</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="21">
-        <f>Drivers!C8</f>
-        <v>48000</v>
-      </c>
-      <c r="D8" s="21">
-        <f>Drivers!D8</f>
-        <v>82400</v>
-      </c>
-      <c r="E8" s="21">
-        <f>Drivers!E8</f>
-        <v>127308</v>
-      </c>
-      <c r="F8" s="21">
-        <f>Drivers!F8</f>
-        <v>174836.32</v>
-      </c>
-      <c r="G8" s="21">
-        <f>Drivers!G8</f>
-        <v>225101.762</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="21">
-        <f>Drivers!C9</f>
-        <v>175000</v>
-      </c>
-      <c r="D9" s="21">
-        <f>Drivers!D9</f>
-        <v>175000</v>
-      </c>
-      <c r="E9" s="21">
-        <f>Drivers!E9</f>
-        <v>175000</v>
-      </c>
-      <c r="F9" s="21">
-        <f>Drivers!F9</f>
-        <v>175000</v>
-      </c>
-      <c r="G9" s="21">
-        <f>Drivers!G9</f>
-        <v>175000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="23">
-        <f>Drivers!C10</f>
-        <v>1414000</v>
-      </c>
-      <c r="D10" s="23">
-        <f>Drivers!D10</f>
-        <v>2252650</v>
-      </c>
-      <c r="E10" s="23">
-        <f>Drivers!E10</f>
-        <v>3345708</v>
-      </c>
-      <c r="F10" s="23">
-        <f>Drivers!F10</f>
-        <v>4462886.32</v>
-      </c>
-      <c r="G10" s="23">
-        <f>Drivers!G10</f>
-        <v>5634801.762</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="21">
-        <f>Drivers!C16</f>
-        <v>985486.28571429</v>
-      </c>
-      <c r="D12" s="21">
-        <f>Drivers!D16</f>
-        <v>1350450.86314286</v>
-      </c>
-      <c r="E12" s="21">
-        <f>Drivers!E16</f>
-        <v>1851580.37373429</v>
-      </c>
-      <c r="F12" s="21">
-        <f>Drivers!F16</f>
-        <v>2322257.94115461</v>
-      </c>
-      <c r="G12" s="21">
-        <f>Drivers!G16</f>
-        <v>2880593.17755445</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="21">
-        <f>Drivers!C22</f>
-        <v>604000</v>
-      </c>
-      <c r="D13" s="21">
-        <f>Drivers!D22</f>
-        <v>864193.33333333</v>
-      </c>
-      <c r="E13" s="21">
-        <f>Drivers!E22</f>
-        <v>1385772.81659125</v>
-      </c>
-      <c r="F13" s="21">
-        <f>Drivers!F22</f>
-        <v>2380453.44662647</v>
-      </c>
-      <c r="G13" s="21">
-        <f>Drivers!G22</f>
-        <v>4269943.71265761</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="23">
-        <f>C12+C13</f>
-        <v>1589486.28571429</v>
-      </c>
-      <c r="D15" s="23">
-        <f>D12+D13</f>
-        <v>2214644.19647619</v>
-      </c>
-      <c r="E15" s="23">
-        <f>E12+E13</f>
-        <v>3237353.19032554</v>
-      </c>
-      <c r="F15" s="23">
-        <f>F12+F13</f>
-        <v>4702711.38778109</v>
-      </c>
-      <c r="G15" s="23">
-        <f>G12+G13</f>
-        <v>7150536.89021206</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="24">
-        <f>C10-C15</f>
-        <v>-175486.28571429</v>
-      </c>
-      <c r="D16" s="25">
-        <f>D10-D15</f>
-        <v>38005.80352381</v>
-      </c>
-      <c r="E16" s="25">
-        <f>E10-E15</f>
-        <v>108354.80967446</v>
-      </c>
-      <c r="F16" s="24">
-        <f>F10-F15</f>
-        <v>-239825.06778109</v>
-      </c>
-      <c r="G16" s="24">
-        <f>G10-G15</f>
-        <v>-1515735.12821206</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="26">
-        <f>IF(C10&gt;0,C16/C10,0)</f>
-        <v>-0.12410628</v>
-      </c>
-      <c r="D17" s="26">
-        <f>IF(D10&gt;0,D16/D10,0)</f>
-        <v>0.0168716</v>
-      </c>
-      <c r="E17" s="26">
-        <f>IF(E10&gt;0,E16/E10,0)</f>
-        <v>0.03238621</v>
-      </c>
-      <c r="F17" s="26">
-        <f>IF(F10&gt;0,F16/F10,0)</f>
-        <v>-0.05373766</v>
-      </c>
-      <c r="G17" s="26">
-        <f>IF(G10&gt;0,G16/G10,0)</f>
-        <v>-0.26899529</v>
       </c>
     </row>
   </sheetData>
@@ -2451,10 +2907,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFD97706"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G14"/>
+  <dimension ref="B1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2463,206 +2919,306 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="19"/>
+      <c r="C3" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="22">
+        <f>Drivers!C4</f>
+        <v>120</v>
+      </c>
+      <c r="D5" s="22">
+        <f>Drivers!D4</f>
+        <v>200</v>
+      </c>
+      <c r="E5" s="22">
+        <f>Drivers!E4</f>
+        <v>300</v>
+      </c>
+      <c r="F5" s="22">
+        <f>Drivers!F4</f>
+        <v>400</v>
+      </c>
+      <c r="G5" s="22">
+        <f>Drivers!G4</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="21">
-        <f>'5-Year P&amp;L'!C16</f>
+      <c r="C6" s="23" t="str">
+        <f>Drivers!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="23" t="str">
+        <f>Drivers!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="23" t="str">
+        <f>Drivers!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="23" t="str">
+        <f>Drivers!F6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="23" t="str">
+        <f>Drivers!G6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="23">
+        <f>Drivers!C7</f>
+        <v>1191000</v>
+      </c>
+      <c r="D7" s="23">
+        <f>Drivers!D7</f>
+        <v>1995250</v>
+      </c>
+      <c r="E7" s="23">
+        <f>Drivers!E7</f>
+        <v>3043400</v>
+      </c>
+      <c r="F7" s="23">
+        <f>Drivers!F7</f>
+        <v>4113050</v>
+      </c>
+      <c r="G7" s="23">
+        <f>Drivers!G7</f>
+        <v>5234700</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" s="23">
+        <f>Drivers!C8</f>
+        <v>48000</v>
+      </c>
+      <c r="D8" s="23">
+        <f>Drivers!D8</f>
+        <v>82400</v>
+      </c>
+      <c r="E8" s="23">
+        <f>Drivers!E8</f>
+        <v>127308</v>
+      </c>
+      <c r="F8" s="23">
+        <f>Drivers!F8</f>
+        <v>174836.32</v>
+      </c>
+      <c r="G8" s="23">
+        <f>Drivers!G8</f>
+        <v>225101.762</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="23">
+        <f>Drivers!C9</f>
+        <v>175000</v>
+      </c>
+      <c r="D9" s="23">
+        <f>Drivers!D9</f>
+        <v>175000</v>
+      </c>
+      <c r="E9" s="23">
+        <f>Drivers!E9</f>
+        <v>175000</v>
+      </c>
+      <c r="F9" s="23">
+        <f>Drivers!F9</f>
+        <v>175000</v>
+      </c>
+      <c r="G9" s="23">
+        <f>Drivers!G9</f>
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="25">
+        <f>Drivers!C10</f>
+        <v>1414000</v>
+      </c>
+      <c r="D10" s="25">
+        <f>Drivers!D10</f>
+        <v>2252650</v>
+      </c>
+      <c r="E10" s="25">
+        <f>Drivers!E10</f>
+        <v>3345708</v>
+      </c>
+      <c r="F10" s="25">
+        <f>Drivers!F10</f>
+        <v>4462886.32</v>
+      </c>
+      <c r="G10" s="25">
+        <f>Drivers!G10</f>
+        <v>5634801.762</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="23">
+        <f>Drivers!C16</f>
+        <v>985486.28571429</v>
+      </c>
+      <c r="D12" s="23">
+        <f>Drivers!D16</f>
+        <v>1350450.86314286</v>
+      </c>
+      <c r="E12" s="23">
+        <f>Drivers!E16</f>
+        <v>1851580.37373429</v>
+      </c>
+      <c r="F12" s="23">
+        <f>Drivers!F16</f>
+        <v>2322257.94115461</v>
+      </c>
+      <c r="G12" s="23">
+        <f>Drivers!G16</f>
+        <v>2880593.17755445</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="23">
+        <f>Drivers!C22</f>
+        <v>604000</v>
+      </c>
+      <c r="D13" s="23">
+        <f>Drivers!D22</f>
+        <v>864193.33333333</v>
+      </c>
+      <c r="E13" s="23">
+        <f>Drivers!E22</f>
+        <v>1385772.81659125</v>
+      </c>
+      <c r="F13" s="23">
+        <f>Drivers!F22</f>
+        <v>2380453.44662647</v>
+      </c>
+      <c r="G13" s="23">
+        <f>Drivers!G22</f>
+        <v>4269943.71265761</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="25">
+        <f>C12+C13</f>
+        <v>1589486.28571429</v>
+      </c>
+      <c r="D15" s="25">
+        <f>D12+D13</f>
+        <v>2214644.19647619</v>
+      </c>
+      <c r="E15" s="25">
+        <f>E12+E13</f>
+        <v>3237353.19032554</v>
+      </c>
+      <c r="F15" s="25">
+        <f>F12+F13</f>
+        <v>4702711.38778109</v>
+      </c>
+      <c r="G15" s="25">
+        <f>G12+G13</f>
+        <v>7150536.89021206</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="26">
+        <f>C10-C15</f>
         <v>-175486.28571429</v>
       </c>
-      <c r="D4" s="21">
-        <f>'5-Year P&amp;L'!D16</f>
+      <c r="D16" s="27">
+        <f>D10-D15</f>
         <v>38005.80352381</v>
       </c>
-      <c r="E4" s="21">
-        <f>'5-Year P&amp;L'!E16</f>
+      <c r="E16" s="27">
+        <f>E10-E15</f>
         <v>108354.80967446</v>
       </c>
-      <c r="F4" s="21">
-        <f>'5-Year P&amp;L'!F16</f>
+      <c r="F16" s="26">
+        <f>F10-F15</f>
         <v>-239825.06778109</v>
       </c>
-      <c r="G4" s="21">
-        <f>'5-Year P&amp;L'!G16</f>
+      <c r="G16" s="26">
+        <f>G10-G15</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="21">
-        <f>Assumptions!D58</f>
-        <v>60000</v>
-      </c>
-      <c r="D6" s="21">
-        <f>Assumptions!D58</f>
-        <v>60000</v>
-      </c>
-      <c r="E6" s="21">
-        <f>Assumptions!D58</f>
-        <v>60000</v>
-      </c>
-      <c r="F6" s="21">
-        <f>Assumptions!D58</f>
-        <v>60000</v>
-      </c>
-      <c r="G6" s="21">
-        <f>Assumptions!D58</f>
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="21">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>46628.61081549</v>
-      </c>
-      <c r="D7" s="21">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>46628.61081549</v>
-      </c>
-      <c r="E7" s="21">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>46628.61081549</v>
-      </c>
-      <c r="F7" s="21">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>46628.61081549</v>
-      </c>
-      <c r="G7" s="21">
-        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
-        <v>46628.61081549</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="23">
-        <f>C6+C7</f>
-        <v>106628.61081549</v>
-      </c>
-      <c r="D8" s="23">
-        <f>D6+D7</f>
-        <v>106628.61081549</v>
-      </c>
-      <c r="E8" s="23">
-        <f>E6+E7</f>
-        <v>106628.61081549</v>
-      </c>
-      <c r="F8" s="23">
-        <f>F6+F7</f>
-        <v>106628.61081549</v>
-      </c>
-      <c r="G8" s="23">
-        <f>G6+G7</f>
-        <v>106628.61081549</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="27">
-        <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
-        <v>-1.6457711</v>
-      </c>
-      <c r="D10" s="27">
-        <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
-        <v>0.35643157</v>
-      </c>
-      <c r="E10" s="28">
-        <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
-        <v>1.01618889</v>
-      </c>
-      <c r="F10" s="27">
-        <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
-        <v>-2.24916245</v>
-      </c>
-      <c r="G10" s="27">
-        <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
-        <v>-14.2150884</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="21">
-        <f>C4-C8</f>
-        <v>-282114.89652978</v>
-      </c>
-      <c r="D12" s="21">
-        <f>D4-D8</f>
-        <v>-68622.80729168</v>
-      </c>
-      <c r="E12" s="21">
-        <f>E4-E8</f>
-        <v>1726.19885897</v>
-      </c>
-      <c r="F12" s="21">
-        <f>F4-F8</f>
-        <v>-346453.67859658</v>
-      </c>
-      <c r="G12" s="21">
-        <f>G4-G8</f>
-        <v>-1622363.73902756</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="29">
-        <f>Assumptions!D57+C12</f>
-        <v>-282114.89652978</v>
-      </c>
-      <c r="D14" s="29">
-        <f>C14+D12</f>
-        <v>-350737.70382146</v>
-      </c>
-      <c r="E14" s="29">
-        <f>D14+E12</f>
-        <v>-349011.50496249</v>
-      </c>
-      <c r="F14" s="29">
-        <f>E14+F12</f>
-        <v>-695465.18355908</v>
-      </c>
-      <c r="G14" s="29">
-        <f>F14+G12</f>
-        <v>-2317828.92258663</v>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="28">
+        <f>IF(C10&gt;0,C16/C10,0)</f>
+        <v>-0.12410628</v>
+      </c>
+      <c r="D17" s="28">
+        <f>IF(D10&gt;0,D16/D10,0)</f>
+        <v>0.0168716</v>
+      </c>
+      <c r="E17" s="28">
+        <f>IF(E10&gt;0,E16/E10,0)</f>
+        <v>0.03238621</v>
+      </c>
+      <c r="F17" s="28">
+        <f>IF(F10&gt;0,F16/F10,0)</f>
+        <v>-0.05373766</v>
+      </c>
+      <c r="G17" s="28">
+        <f>IF(G10&gt;0,G16/G10,0)</f>
+        <v>-0.26899529</v>
       </c>
     </row>
   </sheetData>
@@ -2680,10 +3236,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G6"/>
+  <dimension ref="B1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2692,106 +3248,206 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="17"/>
-      <c r="C3" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>87</v>
+      <c r="B3" s="19"/>
+      <c r="C3" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" s="20">
-        <f>Drivers!C12</f>
-        <v>10</v>
-      </c>
-      <c r="D4" s="20">
-        <f>Drivers!D12</f>
-        <v>16</v>
-      </c>
-      <c r="E4" s="20">
-        <f>Drivers!E12</f>
-        <v>24</v>
-      </c>
-      <c r="F4" s="20">
-        <f>Drivers!F12</f>
-        <v>31</v>
-      </c>
-      <c r="G4" s="20">
-        <f>Drivers!G12</f>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="20">
-        <f>Assumptions!D35</f>
-        <v>5</v>
-      </c>
-      <c r="D5" s="20">
-        <f>Assumptions!D36</f>
-        <v>5</v>
-      </c>
-      <c r="E5" s="20">
-        <f>Assumptions!D37</f>
-        <v>5</v>
-      </c>
-      <c r="F5" s="20">
-        <f>Assumptions!D38</f>
-        <v>5</v>
-      </c>
-      <c r="G5" s="20">
-        <f>Assumptions!D39</f>
-        <v>5</v>
+      <c r="B4" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="23">
+        <f>'5-Year P&amp;L'!C16</f>
+        <v>-175486.28571429</v>
+      </c>
+      <c r="D4" s="23">
+        <f>'5-Year P&amp;L'!D16</f>
+        <v>38005.80352381</v>
+      </c>
+      <c r="E4" s="23">
+        <f>'5-Year P&amp;L'!E16</f>
+        <v>108354.80967446</v>
+      </c>
+      <c r="F4" s="23">
+        <f>'5-Year P&amp;L'!F16</f>
+        <v>-239825.06778109</v>
+      </c>
+      <c r="G4" s="23">
+        <f>'5-Year P&amp;L'!G16</f>
+        <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="30">
-        <f>C4+C5</f>
-        <v>15</v>
-      </c>
-      <c r="D6" s="30">
-        <f>D4+D5</f>
-        <v>21</v>
-      </c>
-      <c r="E6" s="30">
-        <f>E4+E5</f>
-        <v>29</v>
-      </c>
-      <c r="F6" s="30">
-        <f>F4+F5</f>
-        <v>36</v>
-      </c>
-      <c r="G6" s="30">
-        <f>G4+G5</f>
-        <v>44</v>
+      <c r="B6" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="23">
+        <f>Assumptions!D58</f>
+        <v>60000</v>
+      </c>
+      <c r="D6" s="23">
+        <f>Assumptions!D58</f>
+        <v>60000</v>
+      </c>
+      <c r="E6" s="23">
+        <f>Assumptions!D58</f>
+        <v>60000</v>
+      </c>
+      <c r="F6" s="23">
+        <f>Assumptions!D58</f>
+        <v>60000</v>
+      </c>
+      <c r="G6" s="23">
+        <f>Assumptions!D58</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="23">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>46628.61081549</v>
+      </c>
+      <c r="D7" s="23">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>46628.61081549</v>
+      </c>
+      <c r="E7" s="23">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>46628.61081549</v>
+      </c>
+      <c r="F7" s="23">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>46628.61081549</v>
+      </c>
+      <c r="G7" s="23">
+        <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
+        <v>46628.61081549</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="25">
+        <f>C6+C7</f>
+        <v>106628.61081549</v>
+      </c>
+      <c r="D8" s="25">
+        <f>D6+D7</f>
+        <v>106628.61081549</v>
+      </c>
+      <c r="E8" s="25">
+        <f>E6+E7</f>
+        <v>106628.61081549</v>
+      </c>
+      <c r="F8" s="25">
+        <f>F6+F7</f>
+        <v>106628.61081549</v>
+      </c>
+      <c r="G8" s="25">
+        <f>G6+G7</f>
+        <v>106628.61081549</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="29">
+        <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
+        <v>-1.6457711</v>
+      </c>
+      <c r="D10" s="29">
+        <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
+        <v>0.35643157</v>
+      </c>
+      <c r="E10" s="30">
+        <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
+        <v>1.01618889</v>
+      </c>
+      <c r="F10" s="29">
+        <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
+        <v>-2.24916245</v>
+      </c>
+      <c r="G10" s="29">
+        <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
+        <v>-14.2150884</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="23">
+        <f>C4-C8</f>
+        <v>-282114.89652978</v>
+      </c>
+      <c r="D12" s="23">
+        <f>D4-D8</f>
+        <v>-68622.80729168</v>
+      </c>
+      <c r="E12" s="23">
+        <f>E4-E8</f>
+        <v>1726.19885897</v>
+      </c>
+      <c r="F12" s="23">
+        <f>F4-F8</f>
+        <v>-346453.67859658</v>
+      </c>
+      <c r="G12" s="23">
+        <f>G4-G8</f>
+        <v>-1622363.73902756</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="31">
+        <f>Assumptions!D57+C12</f>
+        <v>-282114.89652978</v>
+      </c>
+      <c r="D14" s="31">
+        <f>C14+D12</f>
+        <v>-350737.70382146</v>
+      </c>
+      <c r="E14" s="31">
+        <f>D14+E12</f>
+        <v>-349011.50496249</v>
+      </c>
+      <c r="F14" s="31">
+        <f>E14+F12</f>
+        <v>-695465.18355908</v>
+      </c>
+      <c r="G14" s="31">
+        <f>F14+G12</f>
+        <v>-2317828.92258663</v>
       </c>
     </row>
   </sheetData>
@@ -2809,6 +3465,135 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="19"/>
+      <c r="C3" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="22">
+        <f>Drivers!C12</f>
+        <v>10</v>
+      </c>
+      <c r="D4" s="22">
+        <f>Drivers!D12</f>
+        <v>16</v>
+      </c>
+      <c r="E4" s="22">
+        <f>Drivers!E12</f>
+        <v>24</v>
+      </c>
+      <c r="F4" s="22">
+        <f>Drivers!F12</f>
+        <v>31</v>
+      </c>
+      <c r="G4" s="22">
+        <f>Drivers!G12</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C5" s="22">
+        <f>Assumptions!D35</f>
+        <v>5</v>
+      </c>
+      <c r="D5" s="22">
+        <f>Assumptions!D36</f>
+        <v>5</v>
+      </c>
+      <c r="E5" s="22">
+        <f>Assumptions!D37</f>
+        <v>5</v>
+      </c>
+      <c r="F5" s="22">
+        <f>Assumptions!D38</f>
+        <v>5</v>
+      </c>
+      <c r="G5" s="22">
+        <f>Assumptions!D39</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="32">
+        <f>C4+C5</f>
+        <v>15</v>
+      </c>
+      <c r="D6" s="32">
+        <f>D4+D5</f>
+        <v>21</v>
+      </c>
+      <c r="E6" s="32">
+        <f>E4+E5</f>
+        <v>29</v>
+      </c>
+      <c r="F6" s="32">
+        <f>F4+F5</f>
+        <v>36</v>
+      </c>
+      <c r="G6" s="32">
+        <f>G4+G5</f>
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2821,52 +3606,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="21">
+      <c r="B3" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="23">
         <f>Assumptions!D59</f>
         <v>350000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="26">
+      <c r="B4" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="28">
         <f>Assumptions!D60</f>
         <v>0.06</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="20">
+      <c r="B5" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="22">
         <f>Assumptions!D61</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="31">
+      <c r="B6" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="33">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="27">
+      <c r="B8" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="29">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.6457711</v>
       </c>
@@ -2883,7 +3668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -2898,77 +3683,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C1" s="7"/>
+      <c r="B1" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="19" t="str">
+      <c r="B3" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="21" t="str">
         <f>Assumptions!D5</f>
         <v>Heritage Academy Charter</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="19" t="str">
+      <c r="B4" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="21" t="str">
         <f>Assumptions!D7</f>
         <v>Charter School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="19" t="str">
+      <c r="B5" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="21" t="str">
         <f>Assumptions!D6</f>
         <v>AZ</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="19">
+      <c r="B6" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="21">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="B8" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="22">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="21">
+      <c r="B9" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="23">
         <f>Drivers!G10</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="29">
+      <c r="B10" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="31">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="203">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -133,6 +133,9 @@
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
+    <t>Blue cells are editable inputs</t>
+  </si>
+  <si>
     <t>SCHOOL PROFILE</t>
   </si>
   <si>
@@ -518,6 +521,27 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Revenue per Student</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>0 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -617,7 +641,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -671,6 +695,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <color rgb="FF666666"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -682,7 +712,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF1E293B"/>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -699,13 +729,13 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFDC2626"/>
+      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF16A34A"/>
+      <color rgb="FFDC2626"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -725,12 +755,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
     <fill>
@@ -814,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -825,29 +855,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -857,46 +889,57 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="166" fontId="14" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -908,7 +951,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1365,7 +1408,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1376,7 +1419,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1395,355 +1438,481 @@
       <c r="G3" s="6"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="35" t="s">
+      <c r="B5" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="D5" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="E5" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="F5" s="37" t="s">
         <v>110</v>
       </c>
+      <c r="G5" s="37" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="22">
+      <c r="B6" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="24">
         <v>120</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="24">
         <v>200</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="24">
         <v>300</v>
       </c>
-      <c r="F6" s="22">
+      <c r="F6" s="24">
         <v>400</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="24">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="23">
+      <c r="B7" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="25">
         <v>1414000</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="25">
         <v>2252650</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="25">
         <v>3345708</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="25">
         <v>4462886.32</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="25">
         <v>5634801.762</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="C8" s="23">
+      <c r="B8" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="25">
         <v>985486.2857142857</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="25">
         <v>1350450.8631428573</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="25">
         <v>1851580.3737342858</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="25">
         <v>2322257.9411546146</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="25">
         <v>2880593.1775544523</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" s="23">
+      <c r="B9" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="25">
         <v>604000</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="25">
         <v>864193.3333333334</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="25">
         <v>1385772.8165912519</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="25">
         <v>2380453.4466264746</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="25">
         <v>4269943.712657611</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="23">
+      <c r="B10" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="25">
         <v>106628.6108154935</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="25">
         <v>106628.6108154935</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="25">
         <v>106628.6108154935</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="25">
         <v>106628.6108154935</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="25">
         <v>106628.6108154935</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="26">
+      <c r="B11" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="28">
         <v>-282114.8965297792</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="28">
         <v>-68622.80729168432</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="29">
         <v>1726.1988589687971</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="28">
         <v>-346453.6785965824</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="28">
         <v>-1622363.739027556</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="26">
+      <c r="B12" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="28">
         <v>-282114.8965297792</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="28">
         <v>-350737.7038214635</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="28">
         <v>-349011.5049624947</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="28">
         <v>-695465.1835590771</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="28">
         <v>-2317828.922586633</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="C13" s="36">
+      <c r="B13" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="38">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="38">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="39">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="38">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="38">
         <v>-0.2879185120528036</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C15" s="34" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="C14" s="25">
+        <v>11783.333333333334</v>
+      </c>
+      <c r="D14" s="25">
+        <v>11263.25</v>
+      </c>
+      <c r="E14" s="25">
+        <v>11152.36</v>
+      </c>
+      <c r="F14" s="25">
+        <v>11157.2158</v>
+      </c>
+      <c r="G14" s="25">
+        <v>11269.603524</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34" t="s">
+      <c r="C15" s="38">
+        <v>0.6969492826833703</v>
+      </c>
+      <c r="D15" s="39">
+        <v>0.5994943125398341</v>
+      </c>
+      <c r="E15" s="39">
+        <v>0.5534195972076122</v>
+      </c>
+      <c r="F15" s="40">
+        <v>0.5203488896294841</v>
+      </c>
+      <c r="G15" s="40">
+        <v>0.5112146441389667</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="G15" s="34"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="38" t="s">
+      <c r="C16" s="40">
+        <v>0.12814710042432814</v>
+      </c>
+      <c r="D16" s="40">
+        <v>0.11509022706590016</v>
+      </c>
+      <c r="E16" s="40">
+        <v>0.12425825713940832</v>
+      </c>
+      <c r="F16" s="39">
+        <v>0.1600166311177611</v>
+      </c>
+      <c r="G16" s="39">
+        <v>0.227334193446872</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="38">
+        <v>-0.12410628409779752</v>
+      </c>
+      <c r="D17" s="39">
+        <v>0.016871597240498658</v>
+      </c>
+      <c r="E17" s="39">
+        <v>0.03238621232769336</v>
+      </c>
+      <c r="F17" s="38">
+        <v>-0.0537376600220211</v>
+      </c>
+      <c r="G17" s="38">
+        <v>-0.26899528896187336</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C18" s="41">
+        <v>-1.645771096258031</v>
+      </c>
+      <c r="D18" s="41">
+        <v>0.35643157341300485</v>
+      </c>
+      <c r="E18" s="42">
+        <v>1.0161888900715002</v>
+      </c>
+      <c r="F18" s="41">
+        <v>-2.2491624522434597</v>
+      </c>
+      <c r="G18" s="41">
+        <v>-14.215088395316705</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="D16" s="40" t="s">
+      <c r="C19" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="E16" s="40"/>
-      <c r="F16" s="41" t="s">
+      <c r="C20" s="44" t="s">
         <v>173</v>
       </c>
-      <c r="G16" s="41"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="38" t="s">
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="D17" s="40" t="s">
+      <c r="C22" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41" t="s">
+      <c r="D22" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="G17" s="41"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="38" t="s">
+      <c r="E22" s="36"/>
+      <c r="F22" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="G22" s="36"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="40" t="s">
+      <c r="C23" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="41" t="s">
+      <c r="D23" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="G18" s="41"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="38" t="s">
+      <c r="E23" s="47"/>
+      <c r="F23" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="C19" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="D19" s="40" t="s">
+      <c r="G23" s="48"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="F19" s="41" t="s">
+      <c r="C24" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="D24" s="47" t="s">
         <v>183</v>
       </c>
-      <c r="G19" s="41"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="38" t="s">
+      <c r="E24" s="47"/>
+      <c r="F24" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="C20" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="D20" s="40" t="s">
+      <c r="G24" s="48"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="E20" s="40"/>
-      <c r="F20" s="41" t="s">
+      <c r="C25" s="49" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="41"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="38" t="s">
+      <c r="D25" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="C21" s="42" t="s">
-        <v>178</v>
-      </c>
-      <c r="D21" s="40" t="s">
+      <c r="E25" s="47"/>
+      <c r="F25" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="41" t="s">
+      <c r="G25" s="48"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="45" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="41"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="38" t="s">
+      <c r="C26" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="47" t="s">
         <v>190</v>
       </c>
-      <c r="C22" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="D22" s="40" t="s">
+      <c r="E26" s="47"/>
+      <c r="F26" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="41" t="s">
+      <c r="G26" s="48"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="G22" s="41"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="38" t="s">
+      <c r="C27" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="E27" s="47"/>
+      <c r="F27" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="G27" s="48"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>196</v>
+      </c>
+      <c r="E28" s="47"/>
+      <c r="F28" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="G28" s="48"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="G29" s="48"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="43" t="s">
-        <v>194</v>
-      </c>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
+      <c r="C31" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1931,483 +2100,491 @@
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
     </row>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
+      <c r="B3" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="12" t="s">
+      <c r="C5" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="14" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>42</v>
       </c>
+      <c r="D7" s="14" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C8" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="14">
         <v>2026</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="13">
+      <c r="C12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="15">
         <v>120</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="13">
+      <c r="C13" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="15">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="13">
+      <c r="C14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="15">
         <v>300</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="15">
         <v>400</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="C16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="15">
         <v>500</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+      <c r="B18" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="C21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="14">
+      <c r="C24" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="16">
         <v>400</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="17">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="16">
         <v>175000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
+      <c r="B30" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D32" s="13">
+      <c r="C32" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="15">
         <v>13</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="14">
+      <c r="C33" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D33" s="16">
         <v>43667</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="15">
+      <c r="C34" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="13">
+      <c r="C35" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" s="13">
+      <c r="C36" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D37" s="13">
+      <c r="C37" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D38" s="13">
+      <c r="C38" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D38" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" s="13">
+      <c r="C39" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="15">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="14">
+      <c r="C40" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="16">
         <v>71250</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="15">
+      <c r="C41" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D42" s="15">
+      <c r="C42" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="17">
         <v>0.24285714285714285</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
+      <c r="B44" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D46" s="14">
+      <c r="C46" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D46" s="16">
         <v>322000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D47" s="15">
+      <c r="C47" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D47" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="14">
+      <c r="C48" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" s="15">
+      <c r="C49" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D49" s="17">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D50" s="14">
+      <c r="C50" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="16">
         <v>650</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D51" s="15">
+      <c r="C51" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D51" s="17">
         <v>0.717948717948718</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D52" s="14">
+      <c r="C52" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D52" s="16">
         <v>204000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D53" s="15">
+      <c r="C53" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D53" s="17">
         <v>0.515686274509804</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
+      <c r="B55" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D57" s="14">
+      <c r="C57" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D57" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D58" s="14">
+      <c r="C58" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D58" s="16">
         <v>60000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D59" s="14">
+      <c r="C59" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D59" s="16">
         <v>350000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" s="15">
+      <c r="C60" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" s="17">
         <v>0.06</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D61" s="13">
+      <c r="C61" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D61" s="15">
         <v>10</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B64" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
+      <c r="B64" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D66" s="12" t="s">
+      <c r="C66" s="13" t="s">
         <v>89</v>
       </c>
+      <c r="D66" s="14" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="67" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C67" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D67" s="12" t="s">
+      <c r="C67" s="13" t="s">
         <v>91</v>
       </c>
+      <c r="D67" s="14" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="68" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C68" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D68" s="13">
+      <c r="C68" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D68" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C69" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D69" s="13">
+      <c r="C69" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C70" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D70" s="16">
+      <c r="C70" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D70" s="18">
         <v>0.95</v>
       </c>
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C71" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D71" s="14">
+      <c r="C71" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D71" s="16">
         <v>8200</v>
       </c>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C72" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D72" s="14">
+      <c r="C72" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D72" s="16">
         <v>9100</v>
       </c>
     </row>
     <row r="73" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C73" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D73" s="14">
+      <c r="C73" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73" s="16">
         <v>10500</v>
       </c>
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C75" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D75" s="17"/>
+      <c r="C75" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D75" s="19"/>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C76" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D76" s="18" t="s">
+      <c r="C76" s="13" t="s">
         <v>100</v>
       </c>
+      <c r="D76" s="20" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C77" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D77" s="18" t="s">
+      <c r="C77" s="13" t="s">
         <v>102</v>
       </c>
+      <c r="D77" s="20" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="78" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C78" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D78" s="18" t="s">
+      <c r="C78" s="13" t="s">
         <v>104</v>
+      </c>
+      <c r="D78" s="20" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2446,7 +2623,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2455,439 +2632,439 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="19"/>
-      <c r="C3" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="22" t="s">
         <v>110</v>
       </c>
+      <c r="G3" s="22" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="22">
+      <c r="B4" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="24">
         <f>Assumptions!D12</f>
         <v>120</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="24">
         <f>Assumptions!D13</f>
         <v>200</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="24">
         <f>Assumptions!D14</f>
         <v>300</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="24">
         <f>Assumptions!D15</f>
         <v>400</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="24">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="23" t="str">
+      <c r="B5" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="25" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="23" t="str">
+      <c r="D5" s="25" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="23" t="str">
+      <c r="E5" s="25" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="23" t="str">
+      <c r="F5" s="25" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="23" t="str">
+      <c r="G5" s="25" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="23" t="str">
+      <c r="B6" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="25" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="23" t="str">
+      <c r="D6" s="25" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="23" t="str">
+      <c r="E6" s="25" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="str">
+      <c r="F6" s="25" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="23" t="str">
+      <c r="G6" s="25" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="23">
+      <c r="B7" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="25">
         <v>1191000</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="25">
         <v>1995250</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="25">
         <v>3043400</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="25">
         <v>4113050</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="25">
         <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="23">
+      <c r="B8" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="25">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>48000</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="25">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>82400</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="25">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>127308</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="25">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>174836.32</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="25">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>225101.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="23">
+      <c r="B9" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="25">
         <f>Assumptions!D27</f>
         <v>175000</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="25">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>175000</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="25">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>175000</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="25">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>175000</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="25">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>175000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="25">
+      <c r="B10" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="27">
         <f>C6+C7+C8+C9</f>
         <v>1414000</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="27">
         <f>D6+D7+D8+D9</f>
         <v>2252650</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="27">
         <f>E6+E7+E8+E9</f>
         <v>3345708</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="27">
         <f>F6+F7+F8+F9</f>
         <v>4462886.32</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="27">
         <f>G6+G7+G8+G9</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="22">
+      <c r="B12" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="24">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="24">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>16</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="24">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>24</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="24">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>31</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="24">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="C13" s="23">
+      <c r="B13" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="25">
         <f>C12*Assumptions!D33</f>
         <v>436670</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="25">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>719632.16</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="25">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>1111831.6872</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="25">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>1479199.407179</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="25">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>1916756.13504453</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="23">
+      <c r="B14" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="25">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>356250</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="25">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>366937.5</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="25">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>377945.625</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="25">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>389283.99375</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="25">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>400962.5135625</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="23">
+      <c r="B15" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="25">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>192566.28571429</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="25">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>263881.20314286</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="25">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>361803.06153429</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="25">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>453774.54022561</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="25">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>562874.52894742</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="25">
+      <c r="B16" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="27">
         <f>C13+C14+C15</f>
         <v>985486.28571429</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="27">
         <f>D13+D14+D15</f>
         <v>1350450.86314286</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="27">
         <f>E13+E14+E15</f>
         <v>1851580.37373429</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="27">
         <f>F13+F14+F15</f>
         <v>2322257.94115461</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="27">
         <f>G13+G14+G15</f>
         <v>2880593.17755445</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="23">
+      <c r="B18" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" s="25">
         <f>Assumptions!D46</f>
         <v>322000</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="25">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>331660</v>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="25">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>341609.8</v>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="25">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>351858.094</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="25">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>362413.83682</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C19" s="23" t="str">
+      <c r="B19" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="25" t="str">
         <f>Assumptions!D48</f>
         <v>0</v>
       </c>
-      <c r="D19" s="23" t="str">
+      <c r="D19" s="25" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="23" t="str">
+      <c r="E19" s="25" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>0</v>
       </c>
-      <c r="F19" s="23" t="str">
+      <c r="F19" s="25" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>0</v>
       </c>
-      <c r="G19" s="23" t="str">
+      <c r="G19" s="25" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="23">
+      <c r="B20" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" s="25">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>78000</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="25">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>223333.33333333</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E20" s="25">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>575512.82051282</v>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="25">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>1318268.68288407</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="25">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>2830897.49209079</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="23">
+      <c r="B21" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="25">
         <f>Assumptions!D52</f>
         <v>204000</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="25">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>309200</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="25">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>468650.19607843</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="25">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>710326.66974241</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="25">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>1076632.38374682</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="25">
+      <c r="B22" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="27">
         <f>C18+C19+C20+C21</f>
         <v>604000</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="27">
         <f>D18+D19+D20+D21</f>
         <v>864193.33333333</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="27">
         <f>E18+E19+E20+E21</f>
         <v>1385772.81659125</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="27">
         <f>F18+F19+F20+F21</f>
         <v>2380453.44662647</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="27">
         <f>G18+G19+G20+G21</f>
         <v>4269943.71265761</v>
       </c>
@@ -2920,7 +3097,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2929,294 +3106,294 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="19"/>
-      <c r="C3" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="22" t="s">
         <v>110</v>
       </c>
+      <c r="G3" s="22" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="22">
+      <c r="B5" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="24">
         <f>Drivers!C4</f>
         <v>120</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="24">
         <f>Drivers!D4</f>
         <v>200</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="24">
         <f>Drivers!E4</f>
         <v>300</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="24">
         <f>Drivers!F4</f>
         <v>400</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="24">
         <f>Drivers!G4</f>
         <v>500</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="23" t="str">
+      <c r="B6" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="25" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="23" t="str">
+      <c r="D6" s="25" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="23" t="str">
+      <c r="E6" s="25" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="str">
+      <c r="F6" s="25" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="23" t="str">
+      <c r="G6" s="25" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="23">
+      <c r="B7" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C7" s="25">
         <f>Drivers!C7</f>
         <v>1191000</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="25">
         <f>Drivers!D7</f>
         <v>1995250</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="25">
         <f>Drivers!E7</f>
         <v>3043400</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="25">
         <f>Drivers!F7</f>
         <v>4113050</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="25">
         <f>Drivers!G7</f>
         <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="C8" s="23">
+      <c r="B8" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="25">
         <f>Drivers!C8</f>
         <v>48000</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="25">
         <f>Drivers!D8</f>
         <v>82400</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="25">
         <f>Drivers!E8</f>
         <v>127308</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="25">
         <f>Drivers!F8</f>
         <v>174836.32</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="25">
         <f>Drivers!G8</f>
         <v>225101.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="23">
+      <c r="B9" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="25">
         <f>Drivers!C9</f>
         <v>175000</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="25">
         <f>Drivers!D9</f>
         <v>175000</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="25">
         <f>Drivers!E9</f>
         <v>175000</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="25">
         <f>Drivers!F9</f>
         <v>175000</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="25">
         <f>Drivers!G9</f>
         <v>175000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="25">
+      <c r="B10" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="27">
         <f>Drivers!C10</f>
         <v>1414000</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="27">
         <f>Drivers!D10</f>
         <v>2252650</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="27">
         <f>Drivers!E10</f>
         <v>3345708</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="27">
         <f>Drivers!F10</f>
         <v>4462886.32</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="27">
         <f>Drivers!G10</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="23">
+      <c r="B12" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="25">
         <f>Drivers!C16</f>
         <v>985486.28571429</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="25">
         <f>Drivers!D16</f>
         <v>1350450.86314286</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="25">
         <f>Drivers!E16</f>
         <v>1851580.37373429</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="25">
         <f>Drivers!F16</f>
         <v>2322257.94115461</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="25">
         <f>Drivers!G16</f>
         <v>2880593.17755445</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="23">
+      <c r="B13" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="25">
         <f>Drivers!C22</f>
         <v>604000</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="25">
         <f>Drivers!D22</f>
         <v>864193.33333333</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="25">
         <f>Drivers!E22</f>
         <v>1385772.81659125</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="25">
         <f>Drivers!F22</f>
         <v>2380453.44662647</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="25">
         <f>Drivers!G22</f>
         <v>4269943.71265761</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="B15" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="27">
         <f>C12+C13</f>
         <v>1589486.28571429</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="27">
         <f>D12+D13</f>
         <v>2214644.19647619</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="27">
         <f>E12+E13</f>
         <v>3237353.19032554</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="27">
         <f>F12+F13</f>
         <v>4702711.38778109</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="27">
         <f>G12+G13</f>
         <v>7150536.89021206</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="26">
+      <c r="B16" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="28">
         <f>C10-C15</f>
         <v>-175486.28571429</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="29">
         <f>D10-D15</f>
         <v>38005.80352381</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="29">
         <f>E10-E15</f>
         <v>108354.80967446</v>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="28">
         <f>F10-F15</f>
         <v>-239825.06778109</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="28">
         <f>G10-G15</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="28">
+      <c r="B17" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="30">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.12410628</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="30">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>0.0168716</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="30">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>0.03238621</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="30">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>-0.05373766</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="30">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>-0.26899529</v>
       </c>
@@ -3249,7 +3426,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3258,194 +3435,194 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="19"/>
-      <c r="C3" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="22" t="s">
         <v>110</v>
       </c>
+      <c r="G3" s="22" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="23">
+      <c r="B4" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="25">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-175486.28571429</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="25">
         <f>'5-Year P&amp;L'!D16</f>
         <v>38005.80352381</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="25">
         <f>'5-Year P&amp;L'!E16</f>
         <v>108354.80967446</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="25">
         <f>'5-Year P&amp;L'!F16</f>
         <v>-239825.06778109</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="25">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="23">
+      <c r="B6" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="25">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="25">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="25">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="25">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="25">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="23">
+      <c r="B7" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="25">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="25">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="25">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="25">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="25">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="25">
+      <c r="B8" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="27">
         <f>C6+C7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="27">
         <f>D6+D7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="27">
         <f>E6+E7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="27">
         <f>F6+F7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="27">
         <f>G6+G7</f>
         <v>106628.61081549</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="29">
+      <c r="B10" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="31">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.6457711</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="31">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.35643157</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="32">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>1.01618889</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="31">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>-2.24916245</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="31">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>-14.2150884</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="23">
+      <c r="B12" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="25">
         <f>C4-C8</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="25">
         <f>D4-D8</f>
         <v>-68622.80729168</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="25">
         <f>E4-E8</f>
         <v>1726.19885897</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="25">
         <f>F4-F8</f>
         <v>-346453.67859658</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="25">
         <f>G4-G8</f>
         <v>-1622363.73902756</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="31">
+      <c r="B14" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="33">
         <f>Assumptions!D57+C12</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="33">
         <f>C14+D12</f>
         <v>-350737.70382146</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="33">
         <f>D14+E12</f>
         <v>-349011.50496249</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="33">
         <f>E14+F12</f>
         <v>-695465.18355908</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="33">
         <f>F14+G12</f>
         <v>-2317828.92258663</v>
       </c>
@@ -3478,7 +3655,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3487,94 +3664,94 @@
       <c r="G1" s="9"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="19"/>
-      <c r="C3" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="B3" s="21"/>
+      <c r="C3" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="22" t="s">
         <v>110</v>
       </c>
+      <c r="G3" s="22" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C4" s="22">
+      <c r="B4" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="24">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="24">
         <f>Drivers!D12</f>
         <v>16</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="24">
         <f>Drivers!E12</f>
         <v>24</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="24">
         <f>Drivers!F12</f>
         <v>31</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="24">
         <f>Drivers!G12</f>
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C5" s="22">
+      <c r="B5" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" s="24">
         <f>Assumptions!D35</f>
         <v>5</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="24">
         <f>Assumptions!D36</f>
         <v>5</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="24">
         <f>Assumptions!D37</f>
         <v>5</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="24">
         <f>Assumptions!D38</f>
         <v>5</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="24">
         <f>Assumptions!D39</f>
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="32">
+      <c r="B6" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="34">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="32">
+      <c r="D6" s="34">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="34">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="34">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="32">
+      <c r="G6" s="34">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -3607,51 +3784,51 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="23">
+      <c r="B3" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="25">
         <f>Assumptions!D59</f>
         <v>350000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" s="28">
+      <c r="B4" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="30">
         <f>Assumptions!D60</f>
         <v>0.06</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="22">
+      <c r="B5" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="24">
         <f>Assumptions!D61</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="33">
+      <c r="B6" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="35">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="29">
+      <c r="B8" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="31">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.6457711</v>
       </c>
@@ -3684,76 +3861,76 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C1" s="9"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="21" t="str">
+      <c r="B3" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="23" t="str">
         <f>Assumptions!D5</f>
         <v>Heritage Academy Charter</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="21" t="str">
+      <c r="B4" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="23" t="str">
         <f>Assumptions!D7</f>
         <v>Charter School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="21" t="str">
+      <c r="B5" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="23" t="str">
         <f>Assumptions!D6</f>
         <v>AZ</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="21" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="21">
+      <c r="B6" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="23">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="22">
+      <c r="B8" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="24">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="23">
+      <c r="B9" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="25">
         <f>Drivers!G10</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="31">
+      <c r="B10" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="33">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="208">
   <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
@@ -67,13 +67,13 @@
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t>Green cells are key outputs and summary metrics.</t>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
   </si>
   <si>
     <t/>
@@ -119,6 +119,21 @@
   </si>
   <si>
     <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
   </si>
   <si>
     <t>Disclaimer</t>
@@ -641,7 +656,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -685,6 +700,22 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E293B"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -708,11 +739,6 @@
     </font>
     <font>
       <color rgb="FF374151"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -760,17 +786,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -844,7 +870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -852,113 +878,265 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="21">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1406,6 +1584,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:G33"/>
@@ -1419,7 +1598,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -1438,456 +1617,456 @@
       <c r="G3" s="6"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="E5" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="37" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="37" t="s">
-        <v>111</v>
+      <c r="B5" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="24">
+      <c r="B6" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="28">
         <v>120</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="28">
         <v>200</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="28">
         <v>300</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="28">
         <v>400</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="28">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7" s="25">
+      <c r="B7" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="29">
         <v>1414000</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>2252650</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <v>3345708</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <v>4462886.32</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="29">
         <v>5634801.762</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="C8" s="25">
+      <c r="B8" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="29">
         <v>985486.2857142857</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="29">
         <v>1350450.8631428573</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="29">
         <v>1851580.3737342858</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="29">
         <v>2322257.9411546146</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="29">
         <v>2880593.1775544523</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="25">
+      <c r="B9" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="29">
         <v>604000</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="29">
         <v>864193.3333333334</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="29">
         <v>1385772.8165912519</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="29">
         <v>2380453.4466264746</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="29">
         <v>4269943.712657611</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" s="25">
+      <c r="B10" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="29">
         <v>106628.6108154935</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="29">
         <v>106628.6108154935</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="29">
         <v>106628.6108154935</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="29">
         <v>106628.6108154935</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="29">
         <v>106628.6108154935</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="28">
+      <c r="B11" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="32">
         <v>-282114.8965297792</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="32">
         <v>-68622.80729168432</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="33">
         <v>1726.1988589687971</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="32">
         <v>-346453.6785965824</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="32">
         <v>-1622363.739027556</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" s="28">
+      <c r="B12" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="32">
         <v>-282114.8965297792</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="32">
         <v>-350737.7038214635</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="32">
         <v>-349011.5049624947</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="32">
         <v>-695465.1835590771</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="32">
         <v>-2317828.922586633</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="26" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="38">
+      <c r="B13" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="42">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="42">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="43">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="42">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="42">
         <v>-0.2879185120528036</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="C14" s="25">
+      <c r="B14" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" s="29">
         <v>11783.333333333334</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="29">
         <v>11263.25</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="29">
         <v>11152.36</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="29">
         <v>11157.2158</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="29">
         <v>11269.603524</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
-        <v>168</v>
-      </c>
-      <c r="C15" s="38">
+      <c r="B15" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="42">
         <v>0.6969492826833703</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="43">
         <v>0.5994943125398341</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="43">
         <v>0.5534195972076122</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="44">
         <v>0.5203488896294841</v>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="44">
         <v>0.5112146441389667</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="C16" s="40">
+      <c r="B16" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="44">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="44">
         <v>0.11509022706590016</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="44">
         <v>0.12425825713940832</v>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="43">
         <v>0.1600166311177611</v>
       </c>
-      <c r="G16" s="39">
+      <c r="G16" s="43">
         <v>0.227334193446872</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="38">
+      <c r="B17" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="42">
         <v>-0.12410628409779752</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="43">
         <v>0.016871597240498658</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="43">
         <v>0.03238621232769336</v>
       </c>
-      <c r="F17" s="38">
+      <c r="F17" s="42">
         <v>-0.0537376600220211</v>
       </c>
-      <c r="G17" s="38">
+      <c r="G17" s="42">
         <v>-0.26899528896187336</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="C18" s="41">
+      <c r="B18" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" s="45">
         <v>-1.645771096258031</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="45">
         <v>0.35643157341300485</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="46">
         <v>1.0161888900715002</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="45">
         <v>-2.2491624522434597</v>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="45">
         <v>-14.215088395316705</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
+      <c r="B19" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
+      <c r="B20" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="36" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36" t="s">
-        <v>177</v>
-      </c>
-      <c r="G22" s="36"/>
+      <c r="B22" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="G22" s="40"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="45" t="s">
-        <v>178</v>
-      </c>
-      <c r="C23" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="D23" s="47" t="s">
-        <v>180</v>
-      </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="G23" s="48"/>
+      <c r="B23" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="E23" s="51"/>
+      <c r="F23" s="52" t="s">
+        <v>186</v>
+      </c>
+      <c r="G23" s="52"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="C24" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="48" t="s">
+      <c r="B24" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="G24" s="48"/>
+      <c r="D24" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="E24" s="51"/>
+      <c r="F24" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="G24" s="52"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="C25" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="47" t="s">
-        <v>187</v>
-      </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="48" t="s">
-        <v>188</v>
-      </c>
-      <c r="G25" s="48"/>
+      <c r="B25" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" s="51"/>
+      <c r="F25" s="52" t="s">
+        <v>193</v>
+      </c>
+      <c r="G25" s="52"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>190</v>
-      </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48" t="s">
+      <c r="B26" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="E26" s="51"/>
+      <c r="F26" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" s="52"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" s="51"/>
+      <c r="F27" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27" s="52"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="G26" s="48"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="45" t="s">
-        <v>192</v>
-      </c>
-      <c r="C27" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="47" t="s">
-        <v>193</v>
-      </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="48" t="s">
-        <v>194</v>
-      </c>
-      <c r="G27" s="48"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="D28" s="47" t="s">
-        <v>196</v>
-      </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="G28" s="48"/>
+      <c r="D28" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="E28" s="51"/>
+      <c r="F28" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="G28" s="52"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="45" t="s">
-        <v>198</v>
-      </c>
-      <c r="C29" s="46" t="s">
-        <v>179</v>
-      </c>
-      <c r="D29" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48" t="s">
-        <v>200</v>
-      </c>
-      <c r="G29" s="48"/>
+      <c r="B29" s="49" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" s="51"/>
+      <c r="F29" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="G29" s="52"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
+      <c r="C31" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
+      <c r="B33" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -1914,6 +2093,83 @@
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="B33:G33"/>
   </mergeCells>
+  <conditionalFormatting sqref="C11:G11">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>C11&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>C11&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>C11&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:G12">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C12&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C12&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C12&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>C13&gt;=0.05</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="3">
+      <formula>C13&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15:G15">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>C15&lt;=0.55</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="2">
+      <formula>C15&lt;=0.65</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="3">
+      <formula>C15&gt;0.65</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G16">
+    <cfRule type="expression" dxfId="12" priority="1">
+      <formula>C16&lt;=0.15</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="2">
+      <formula>C16&lt;=0.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>C16&gt;0.25</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17:G17">
+    <cfRule type="expression" dxfId="15" priority="1">
+      <formula>C17&gt;=0.10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>C17&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="3">
+      <formula>C17&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18:G18">
+    <cfRule type="expression" dxfId="18" priority="1">
+      <formula>C18&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="2">
+      <formula>C18&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="3">
+      <formula>C18&lt;1.0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -1925,9 +2181,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B29"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1939,134 +2196,174 @@
         <v>13</v>
       </c>
     </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="8" t="s">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="8" t="s">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="8" t="s">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="12" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="8" t="s">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="8" t="s">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="8" t="s">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="8" t="s">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="8" t="s">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="11" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="8" t="s">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="8" t="s">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="8" t="s">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="8" t="s">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="8" t="s">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="11" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2094,497 +2391,497 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>37</v>
+      <c r="C2" s="15" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
+      <c r="B3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>41</v>
+      <c r="C6" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>43</v>
+      <c r="C7" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="14">
+      <c r="C8" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="18">
         <v>2026</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="B10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="15">
+      <c r="C12" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="19">
         <v>120</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="C13" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="19">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="15">
+      <c r="C14" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="19">
         <v>300</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="19">
         <v>400</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="19">
         <v>500</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+      <c r="B18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="16">
+      <c r="C20" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="17">
+      <c r="C21" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="16">
+      <c r="C22" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="17">
+      <c r="C23" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="16">
+      <c r="C24" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="20">
         <v>400</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="17">
+      <c r="C25" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D26" s="17">
+      <c r="C26" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="21">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="16">
+      <c r="C27" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="20">
         <v>175000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="17">
+      <c r="C28" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
+      <c r="B30" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="15">
+      <c r="C32" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="19">
         <v>13</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="16">
+      <c r="C33" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="20">
         <v>43667</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="17">
+      <c r="C34" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="15">
+      <c r="C35" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="15">
+      <c r="C36" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D37" s="15">
+      <c r="C37" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="15">
+      <c r="C38" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D39" s="15">
+      <c r="C39" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="D39" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="16">
+      <c r="C40" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="20">
         <v>71250</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D41" s="17">
+      <c r="C41" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D41" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="17">
+      <c r="C42" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D42" s="21">
         <v>0.24285714285714285</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
+      <c r="B44" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D46" s="16">
+      <c r="C46" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="20">
         <v>322000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="17">
+      <c r="C47" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" s="16">
+      <c r="C48" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D49" s="17">
+      <c r="C49" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="21">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D50" s="16">
+      <c r="C50" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="20">
         <v>650</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" s="17">
+      <c r="C51" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="21">
         <v>0.717948717948718</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="16">
+      <c r="C52" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" s="20">
         <v>204000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D53" s="17">
+      <c r="C53" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" s="21">
         <v>0.515686274509804</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
+      <c r="B55" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D57" s="16">
+      <c r="C57" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D58" s="16">
+      <c r="C58" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="20">
         <v>60000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D59" s="16">
+      <c r="C59" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D59" s="20">
         <v>350000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D60" s="17">
+      <c r="C60" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D60" s="21">
         <v>0.06</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D61" s="15">
+      <c r="C61" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D61" s="19">
         <v>10</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B64" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
+      <c r="B64" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>90</v>
+      <c r="C66" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C67" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>92</v>
+      <c r="C67" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C68" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D68" s="15">
+      <c r="C68" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D68" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C69" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D69" s="15">
+      <c r="C69" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="D69" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C70" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D70" s="18">
+      <c r="C70" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D70" s="22">
         <v>0.95</v>
       </c>
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C71" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D71" s="16">
+      <c r="C71" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D71" s="20">
         <v>8200</v>
       </c>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C72" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D72" s="16">
+      <c r="C72" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D72" s="20">
         <v>9100</v>
       </c>
     </row>
     <row r="73" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C73" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D73" s="16">
+      <c r="C73" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D73" s="20">
         <v>10500</v>
       </c>
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C75" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D75" s="19"/>
+      <c r="C75" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="D75" s="23"/>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C76" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D76" s="20" t="s">
-        <v>101</v>
+      <c r="C76" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D76" s="24" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C77" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="D77" s="20" t="s">
-        <v>103</v>
+      <c r="C77" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="D77" s="24" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C78" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="D78" s="20" t="s">
-        <v>105</v>
+      <c r="C78" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D78" s="24" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2622,449 +2919,449 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>111</v>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="24">
+      <c r="B4" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="28">
         <f>Assumptions!D12</f>
         <v>120</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="28">
         <f>Assumptions!D13</f>
         <v>200</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="28">
         <f>Assumptions!D14</f>
         <v>300</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="28">
         <f>Assumptions!D15</f>
         <v>400</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="28">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="25" t="str">
+      <c r="B5" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="29" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="25" t="str">
+      <c r="D5" s="29" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="25" t="str">
+      <c r="E5" s="29" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="25" t="str">
+      <c r="F5" s="29" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="25" t="str">
+      <c r="G5" s="29" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="25" t="str">
+      <c r="B6" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="29" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="25" t="str">
+      <c r="D6" s="29" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="25" t="str">
+      <c r="E6" s="29" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="25" t="str">
+      <c r="F6" s="29" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="25" t="str">
+      <c r="G6" s="29" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="25">
+      <c r="B7" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="29">
         <v>1191000</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <v>1995250</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <v>3043400</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <v>4113050</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="29">
         <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="25">
+      <c r="B8" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="29">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>48000</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="29">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>82400</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="29">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>127308</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="29">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>174836.32</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="29">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>225101.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="25">
+      <c r="B9" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="29">
         <f>Assumptions!D27</f>
         <v>175000</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="29">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>175000</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="29">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>175000</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="29">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>175000</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="29">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>175000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="27">
+      <c r="B10" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="31">
         <f>C6+C7+C8+C9</f>
         <v>1414000</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="31">
         <f>D6+D7+D8+D9</f>
         <v>2252650</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="31">
         <f>E6+E7+E8+E9</f>
         <v>3345708</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="31">
         <f>F6+F7+F8+F9</f>
         <v>4462886.32</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="31">
         <f>G6+G7+G8+G9</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="24">
+      <c r="B12" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C12" s="28">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="28">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>16</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="28">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>24</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="28">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>31</v>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="28">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="25">
+      <c r="B13" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="29">
         <f>C12*Assumptions!D33</f>
         <v>436670</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="29">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>719632.16</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="29">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>1111831.6872</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="29">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>1479199.407179</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="29">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>1916756.13504453</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="25">
+      <c r="B14" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="29">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>356250</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="29">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>366937.5</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="29">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>377945.625</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="29">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>389283.99375</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="29">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>400962.5135625</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="B15" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="29">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>192566.28571429</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="29">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>263881.20314286</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="29">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>361803.06153429</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="29">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>453774.54022561</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="29">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>562874.52894742</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="27">
+      <c r="B16" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="31">
         <f>C13+C14+C15</f>
         <v>985486.28571429</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="31">
         <f>D13+D14+D15</f>
         <v>1350450.86314286</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="31">
         <f>E13+E14+E15</f>
         <v>1851580.37373429</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="31">
         <f>F13+F14+F15</f>
         <v>2322257.94115461</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="31">
         <f>G13+G14+G15</f>
         <v>2880593.17755445</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="25">
+      <c r="B18" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="29">
         <f>Assumptions!D46</f>
         <v>322000</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="29">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>331660</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="29">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>341609.8</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="29">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>351858.094</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="29">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>362413.83682</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="25" t="str">
+      <c r="B19" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="29" t="str">
         <f>Assumptions!D48</f>
         <v>0</v>
       </c>
-      <c r="D19" s="25" t="str">
+      <c r="D19" s="29" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="25" t="str">
+      <c r="E19" s="29" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>0</v>
       </c>
-      <c r="F19" s="25" t="str">
+      <c r="F19" s="29" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>0</v>
       </c>
-      <c r="G19" s="25" t="str">
+      <c r="G19" s="29" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" s="25">
+      <c r="B20" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="29">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>78000</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="29">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>223333.33333333</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="29">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>575512.82051282</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="29">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>1318268.68288407</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="29">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>2830897.49209079</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" s="25">
+      <c r="B21" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="29">
         <f>Assumptions!D52</f>
         <v>204000</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="29">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>309200</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="29">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>468650.19607843</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="29">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>710326.66974241</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="29">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>1076632.38374682</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" s="27">
+      <c r="B22" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" s="31">
         <f>C18+C19+C20+C21</f>
         <v>604000</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="31">
         <f>D18+D19+D20+D21</f>
         <v>864193.33333333</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="31">
         <f>E18+E19+E20+E21</f>
         <v>1385772.81659125</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="31">
         <f>F18+F19+F20+F21</f>
         <v>2380453.44662647</v>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="31">
         <f>G18+G19+G20+G21</f>
         <v>4269943.71265761</v>
       </c>
@@ -3096,304 +3393,304 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>111</v>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="24">
+      <c r="B5" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="28">
         <f>Drivers!C4</f>
         <v>120</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="28">
         <f>Drivers!D4</f>
         <v>200</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="28">
         <f>Drivers!E4</f>
         <v>300</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="28">
         <f>Drivers!F4</f>
         <v>400</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="28">
         <f>Drivers!G4</f>
         <v>500</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="25" t="str">
+      <c r="B6" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="29" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="25" t="str">
+      <c r="D6" s="29" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="25" t="str">
+      <c r="E6" s="29" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="25" t="str">
+      <c r="F6" s="29" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="25" t="str">
+      <c r="G6" s="29" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="25">
+      <c r="B7" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="29">
         <f>Drivers!C7</f>
         <v>1191000</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <f>Drivers!D7</f>
         <v>1995250</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <f>Drivers!E7</f>
         <v>3043400</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <f>Drivers!F7</f>
         <v>4113050</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="29">
         <f>Drivers!G7</f>
         <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="25">
+      <c r="B8" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="29">
         <f>Drivers!C8</f>
         <v>48000</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="29">
         <f>Drivers!D8</f>
         <v>82400</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="29">
         <f>Drivers!E8</f>
         <v>127308</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="29">
         <f>Drivers!F8</f>
         <v>174836.32</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="29">
         <f>Drivers!G8</f>
         <v>225101.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="25">
+      <c r="B9" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="29">
         <f>Drivers!C9</f>
         <v>175000</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="29">
         <f>Drivers!D9</f>
         <v>175000</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="29">
         <f>Drivers!E9</f>
         <v>175000</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="29">
         <f>Drivers!F9</f>
         <v>175000</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="29">
         <f>Drivers!G9</f>
         <v>175000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="27">
+      <c r="B10" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="31">
         <f>Drivers!C10</f>
         <v>1414000</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="31">
         <f>Drivers!D10</f>
         <v>2252650</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="31">
         <f>Drivers!E10</f>
         <v>3345708</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="31">
         <f>Drivers!F10</f>
         <v>4462886.32</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="31">
         <f>Drivers!G10</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="25">
+      <c r="B12" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="29">
         <f>Drivers!C16</f>
         <v>985486.28571429</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="29">
         <f>Drivers!D16</f>
         <v>1350450.86314286</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="29">
         <f>Drivers!E16</f>
         <v>1851580.37373429</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="29">
         <f>Drivers!F16</f>
         <v>2322257.94115461</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="29">
         <f>Drivers!G16</f>
         <v>2880593.17755445</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" s="25">
+      <c r="B13" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="29">
         <f>Drivers!C22</f>
         <v>604000</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="29">
         <f>Drivers!D22</f>
         <v>864193.33333333</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="29">
         <f>Drivers!E22</f>
         <v>1385772.81659125</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="29">
         <f>Drivers!F22</f>
         <v>2380453.44662647</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="29">
         <f>Drivers!G22</f>
         <v>4269943.71265761</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="27">
+      <c r="B15" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="31">
         <f>C12+C13</f>
         <v>1589486.28571429</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="31">
         <f>D12+D13</f>
         <v>2214644.19647619</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="31">
         <f>E12+E13</f>
         <v>3237353.19032554</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="31">
         <f>F12+F13</f>
         <v>4702711.38778109</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="31">
         <f>G12+G13</f>
         <v>7150536.89021206</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="28">
+      <c r="B16" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="32">
         <f>C10-C15</f>
         <v>-175486.28571429</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="33">
         <f>D10-D15</f>
         <v>38005.80352381</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="33">
         <f>E10-E15</f>
         <v>108354.80967446</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="32">
         <f>F10-F15</f>
         <v>-239825.06778109</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="32">
         <f>G10-G15</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="30">
+      <c r="B17" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="34">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.12410628</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="34">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>0.0168716</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="34">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>0.03238621</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="34">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>-0.05373766</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="34">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>-0.26899529</v>
       </c>
@@ -3425,204 +3722,204 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>111</v>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="B4" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="29">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-175486.28571429</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="29">
         <f>'5-Year P&amp;L'!D16</f>
         <v>38005.80352381</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="29">
         <f>'5-Year P&amp;L'!E16</f>
         <v>108354.80967446</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="29">
         <f>'5-Year P&amp;L'!F16</f>
         <v>-239825.06778109</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="29">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="25">
+      <c r="B6" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="29">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="29">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="29">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="29">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="29">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="25">
+      <c r="B7" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C7" s="29">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="29">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="29">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="29">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="29">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="27">
+      <c r="B8" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="31">
         <f>C6+C7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="31">
         <f>D6+D7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="31">
         <f>E6+E7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="31">
         <f>F6+F7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="31">
         <f>G6+G7</f>
         <v>106628.61081549</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="31">
+      <c r="B10" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="35">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.6457711</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="35">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.35643157</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="36">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>1.01618889</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="35">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>-2.24916245</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="35">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>-14.2150884</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" s="25">
+      <c r="B12" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="29">
         <f>C4-C8</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="29">
         <f>D4-D8</f>
         <v>-68622.80729168</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="29">
         <f>E4-E8</f>
         <v>1726.19885897</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="29">
         <f>F4-F8</f>
         <v>-346453.67859658</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="29">
         <f>G4-G8</f>
         <v>-1622363.73902756</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="C14" s="33">
+      <c r="B14" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="37">
         <f>Assumptions!D57+C12</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="37">
         <f>C14+D12</f>
         <v>-350737.70382146</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="37">
         <f>D14+E12</f>
         <v>-349011.50496249</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="37">
         <f>E14+F12</f>
         <v>-695465.18355908</v>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="37">
         <f>F14+G12</f>
         <v>-2317828.92258663</v>
       </c>
@@ -3654,104 +3951,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>111</v>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="24">
+      <c r="B4" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="28">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="28">
         <f>Drivers!D12</f>
         <v>16</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="28">
         <f>Drivers!E12</f>
         <v>24</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="28">
         <f>Drivers!F12</f>
         <v>31</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="28">
         <f>Drivers!G12</f>
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C5" s="24">
+      <c r="B5" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="C5" s="28">
         <f>Assumptions!D35</f>
         <v>5</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="28">
         <f>Assumptions!D36</f>
         <v>5</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="28">
         <f>Assumptions!D37</f>
         <v>5</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="28">
         <f>Assumptions!D38</f>
         <v>5</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="28">
         <f>Assumptions!D39</f>
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="34">
+      <c r="B6" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="38">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="34">
+      <c r="D6" s="38">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="38">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="38">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="38">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -3783,52 +4080,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="25">
+      <c r="B3" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="29">
         <f>Assumptions!D59</f>
         <v>350000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C4" s="30">
+      <c r="B4" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="34">
         <f>Assumptions!D60</f>
         <v>0.06</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="24">
+      <c r="B5" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="28">
         <f>Assumptions!D61</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="35">
+      <c r="B6" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="39">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="C8" s="31">
+      <c r="B8" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="35">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.6457711</v>
       </c>
@@ -3860,77 +4157,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C1" s="9"/>
+      <c r="B1" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="23" t="str">
+      <c r="B3" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="27" t="str">
         <f>Assumptions!D5</f>
         <v>Heritage Academy Charter</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="23" t="str">
+      <c r="B4" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="27" t="str">
         <f>Assumptions!D7</f>
         <v>Charter School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="23" t="str">
+      <c r="B5" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="27" t="str">
         <f>Assumptions!D6</f>
         <v>AZ</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="23">
+      <c r="B6" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="27">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="24">
+      <c r="B8" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="28">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="25">
+      <c r="B9" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C9" s="29">
         <f>Drivers!G10</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="C10" s="33">
+      <c r="B10" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="37">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C12" s="6"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -4,8 +4,8 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Cover" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Instructions" state="visible" r:id="rId5"/>
+    <sheet sheetId="1" name="Instructions" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Cover" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Assumptions" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
@@ -22,15 +22,102 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="208">
   <si>
+    <t>How to Use This Workbook</t>
+  </si>
+  <si>
+    <t>Heritage Academy Charter</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
+  </si>
+  <si>
+    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
     <t>SCHOOLSTACK BUDGET</t>
   </si>
   <si>
     <t>Lender-Ready Pro Forma</t>
   </si>
   <si>
-    <t>Heritage Academy Charter</t>
-  </si>
-  <si>
     <t>TABLE OF CONTENTS</t>
   </si>
   <si>
@@ -55,94 +142,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
-  </si>
-  <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
-  </si>
-  <si>
-    <t>How to Use This Workbook</t>
-  </si>
-  <si>
-    <t>Cell Color Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
-  </si>
-  <si>
-    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
-  </si>
-  <si>
-    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
-  </si>
-  <si>
-    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
-  </si>
-  <si>
-    <t>Debt Service Convention</t>
-  </si>
-  <si>
-    <t>operating expense on the Operating Statement. This is a standard</t>
-  </si>
-  <si>
-    <t>simplification used in school financial underwriting that ensures internal</t>
-  </si>
-  <si>
-    <t>consistency across all tabs.</t>
-  </si>
-  <si>
-    <t>Tips</t>
-  </si>
-  <si>
-    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
-  </si>
-  <si>
-    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
-  </si>
-  <si>
-    <t>Next Steps</t>
-  </si>
-  <si>
-    <t>2. Verify enrollment and revenue projections match your plan.</t>
-  </si>
-  <si>
-    <t>3. Check the Financial Health dashboard for risk signals.</t>
-  </si>
-  <si>
-    <t>4. Share this workbook with your lender or financial advisor.</t>
-  </si>
-  <si>
-    <t>5. Update inputs as your school's plan evolves.</t>
-  </si>
-  <si>
-    <t>Disclaimer</t>
-  </si>
-  <si>
-    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
-  </si>
-  <si>
-    <t>user-provided assumptions and should be independently verified.</t>
   </si>
   <si>
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
@@ -667,36 +667,7 @@
     <font>
       <b/>
       <color rgb="FF1E293B"/>
-      <sz val="22"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF328555"/>
-      <sz val="14"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E293B"/>
       <sz val="16"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1E293B"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF6B7280"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -711,11 +682,40 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="22"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF328555"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -875,15 +875,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -891,32 +891,32 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -929,7 +929,7 @@
     <xf numFmtId="165" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -972,10 +972,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1472,107 +1472,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF1E293B"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C19"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="1" t="s">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="4"/>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>4</v>
+      <c r="B9" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>5</v>
+      <c r="B10" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>6</v>
+      <c r="B11" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>9</v>
+      <c r="B14" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="6"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B9" r:id="rId1" location="#'Assumptions'!A1"/>
-    <hyperlink ref="B10" r:id="rId2" location="#'Drivers'!A1"/>
-    <hyperlink ref="B11" r:id="rId3" location="#'5-Year P&amp;L'!A1"/>
-    <hyperlink ref="B12" r:id="rId4" location="#'Cash Flow &amp; DSCR'!A1"/>
-    <hyperlink ref="B13" r:id="rId5" location="#'Staffing'!A1"/>
-    <hyperlink ref="B14" r:id="rId6" location="#'Loan Snapshot'!A1"/>
-    <hyperlink ref="B15" r:id="rId7" location="#'Summary'!A1"/>
-  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -1597,24 +1682,24 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
+      <c r="B3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="40" t="s">
@@ -2050,7 +2135,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="49" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C31" s="30" t="s">
         <v>206</v>
@@ -2181,192 +2266,107 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF328555"/>
+    <tabColor rgb="FF1E293B"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B37"/>
+  <dimension ref="B3:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="80" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
-        <v>16</v>
-      </c>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="8"/>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="9"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="10"/>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
-        <v>17</v>
+      <c r="B9" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="9" t="s">
-        <v>19</v>
+      <c r="B11" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="11" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="11" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="9" t="s">
-        <v>21</v>
+      <c r="B14" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="11" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="12"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
         <v>40</v>
       </c>
+      <c r="C19" s="12"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B9" r:id="rId1" location="#'Assumptions'!A1"/>
+    <hyperlink ref="B10" r:id="rId2" location="#'Drivers'!A1"/>
+    <hyperlink ref="B11" r:id="rId3" location="#'5-Year P&amp;L'!A1"/>
+    <hyperlink ref="B12" r:id="rId4" location="#'Cash Flow &amp; DSCR'!A1"/>
+    <hyperlink ref="B13" r:id="rId5" location="#'Staffing'!A1"/>
+    <hyperlink ref="B14" r:id="rId6" location="#'Loan Snapshot'!A1"/>
+    <hyperlink ref="B15" r:id="rId7" location="#'Summary'!A1"/>
+  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>42</v>
@@ -2417,7 +2417,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
@@ -4226,10 +4226,10 @@
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="209">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -28,118 +28,121 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
+    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+  </si>
+  <si>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
+  </si>
+  <si>
+    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
+  </si>
+  <si>
+    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
+  </si>
+  <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs.</t>
+  </si>
+  <si>
+    <t>Tips</t>
+  </si>
+  <si>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>2. Verify enrollment and revenue projections match your plan.</t>
+  </si>
+  <si>
+    <t>3. Check the Financial Health dashboard for risk signals.</t>
+  </si>
+  <si>
+    <t>4. Share this workbook with your lender or financial advisor.</t>
+  </si>
+  <si>
+    <t>5. Update inputs as your school's plan evolves.</t>
+  </si>
+  <si>
+    <t>Disclaimer</t>
+  </si>
+  <si>
+    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
+  </si>
+  <si>
+    <t>user-provided assumptions and should be independently verified.</t>
+  </si>
+  <si>
+    <t>SCHOOLSTACK BUDGET</t>
+  </si>
+  <si>
+    <t>Lender-Ready Pro Forma</t>
+  </si>
+  <si>
+    <t>TABLE OF CONTENTS</t>
+  </si>
+  <si>
+    <t>Assumptions</t>
+  </si>
+  <si>
+    <t>Drivers</t>
+  </si>
+  <si>
+    <t>5-Year P&amp;L</t>
+  </si>
+  <si>
+    <t>Cash Flow &amp; DSCR</t>
+  </si>
+  <si>
+    <t>Staffing</t>
+  </si>
+  <si>
+    <t>Loan Snapshot</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
     <t>Generated March 26, 2026</t>
-  </si>
-  <si>
-    <t>Cell Color Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Blue cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  White cells contain formulas — do not edit (they recalculate automatically).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Green cells are key outputs and summary metrics.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Navigation</t>
-  </si>
-  <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
-  </si>
-  <si>
-    <t>Structure</t>
-  </si>
-  <si>
-    <t>Assumptions &amp; Drivers: Model inputs and calculations</t>
-  </si>
-  <si>
-    <t>5-Year P&amp;L &amp; Cash Flow: Financial projections</t>
-  </si>
-  <si>
-    <t>Staffing &amp; Loan Snapshot: Personnel and debt detail</t>
-  </si>
-  <si>
-    <t>Summary &amp; Financial Health: Key metrics dashboard</t>
-  </si>
-  <si>
-    <t>Debt Service Convention</t>
-  </si>
-  <si>
-    <t>operating expense on the Operating Statement. This is a standard</t>
-  </si>
-  <si>
-    <t>simplification used in school financial underwriting that ensures internal</t>
-  </si>
-  <si>
-    <t>consistency across all tabs.</t>
-  </si>
-  <si>
-    <t>Tips</t>
-  </si>
-  <si>
-    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
-  </si>
-  <si>
-    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
-  </si>
-  <si>
-    <t>Next Steps</t>
-  </si>
-  <si>
-    <t>2. Verify enrollment and revenue projections match your plan.</t>
-  </si>
-  <si>
-    <t>3. Check the Financial Health dashboard for risk signals.</t>
-  </si>
-  <si>
-    <t>4. Share this workbook with your lender or financial advisor.</t>
-  </si>
-  <si>
-    <t>5. Update inputs as your school's plan evolves.</t>
-  </si>
-  <si>
-    <t>Disclaimer</t>
-  </si>
-  <si>
-    <t>a loan commitment, or a guarantee of funding. All projections are based on</t>
-  </si>
-  <si>
-    <t>user-provided assumptions and should be independently verified.</t>
-  </si>
-  <si>
-    <t>SCHOOLSTACK BUDGET</t>
-  </si>
-  <si>
-    <t>Lender-Ready Pro Forma</t>
-  </si>
-  <si>
-    <t>TABLE OF CONTENTS</t>
-  </si>
-  <si>
-    <t>Assumptions</t>
-  </si>
-  <si>
-    <t>Drivers</t>
-  </si>
-  <si>
-    <t>5-Year P&amp;L</t>
-  </si>
-  <si>
-    <t>Cash Flow &amp; DSCR</t>
-  </si>
-  <si>
-    <t>Staffing</t>
-  </si>
-  <si>
-    <t>Loan Snapshot</t>
-  </si>
-  <si>
-    <t>Summary</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -1683,7 +1686,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1693,7 +1696,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -1703,27 +1706,27 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G5" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C6" s="28">
         <v>120</v>
@@ -1743,7 +1746,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C7" s="29">
         <v>1414000</v>
@@ -1763,7 +1766,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C8" s="29">
         <v>985486.2857142857</v>
@@ -1783,7 +1786,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C9" s="29">
         <v>604000</v>
@@ -1803,7 +1806,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="27" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C10" s="29">
         <v>106628.6108154935</v>
@@ -1823,7 +1826,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C11" s="32">
         <v>-282114.8965297792</v>
@@ -1843,7 +1846,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C12" s="32">
         <v>-282114.8965297792</v>
@@ -1863,7 +1866,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" s="42">
         <v>-0.19951548552318188</v>
@@ -1883,7 +1886,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="30" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="29">
         <v>11783.333333333334</v>
@@ -1903,7 +1906,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="42">
         <v>0.6969492826833703</v>
@@ -1923,7 +1926,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="44">
         <v>0.12814710042432814</v>
@@ -1943,7 +1946,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="42">
         <v>-0.12410628409779752</v>
@@ -1963,7 +1966,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C18" s="45">
         <v>-1.645771096258031</v>
@@ -1983,10 +1986,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D19" s="47"/>
       <c r="E19" s="47"/>
@@ -1995,10 +1998,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C20" s="48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D20" s="48"/>
       <c r="E20" s="48"/>
@@ -2007,129 +2010,129 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="40" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D22" s="40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E22" s="40"/>
       <c r="F22" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G22" s="40"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="49" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C23" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" s="51"/>
       <c r="F23" s="52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G23" s="52"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C24" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E24" s="51"/>
       <c r="F24" s="52" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G24" s="52"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="49" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C25" s="53" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E25" s="51"/>
       <c r="F25" s="52" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G25" s="52"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="49" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E26" s="51"/>
       <c r="F26" s="52" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G26" s="52"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E27" s="51"/>
       <c r="F27" s="52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G27" s="52"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D28" s="51" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E28" s="51"/>
       <c r="F28" s="52" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G28" s="52"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="49" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E29" s="51"/>
       <c r="F29" s="52" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G29" s="52"/>
     </row>
@@ -2138,14 +2141,14 @@
         <v>39</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D31" s="30"/>
       <c r="E31" s="30"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="54" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C33" s="54"/>
       <c r="D33" s="54"/>
@@ -2339,13 +2342,13 @@
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C18" s="12"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B19" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="12"/>
     </row>
@@ -2392,7 +2395,7 @@
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2402,19 +2405,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C5" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>1</v>
@@ -2422,23 +2425,23 @@
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C6" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C7" s="17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C8" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="18">
         <v>2026</v>
@@ -2446,14 +2449,14 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C12" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12" s="19">
         <v>120</v>
@@ -2461,7 +2464,7 @@
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C13" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="19">
         <v>200</v>
@@ -2469,7 +2472,7 @@
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C14" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" s="19">
         <v>300</v>
@@ -2477,7 +2480,7 @@
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C15" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" s="19">
         <v>400</v>
@@ -2485,7 +2488,7 @@
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C16" s="17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="19">
         <v>500</v>
@@ -2493,14 +2496,14 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C20" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="20">
         <v>0</v>
@@ -2508,7 +2511,7 @@
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C21" s="17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" s="21">
         <v>0.03</v>
@@ -2516,7 +2519,7 @@
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C22" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="20">
         <v>0</v>
@@ -2524,7 +2527,7 @@
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C23" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" s="21">
         <v>0</v>
@@ -2532,7 +2535,7 @@
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C24" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" s="20">
         <v>400</v>
@@ -2540,7 +2543,7 @@
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C25" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D25" s="21">
         <v>0.03</v>
@@ -2548,7 +2551,7 @@
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C26" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D26" s="21">
         <v>0.95</v>
@@ -2556,7 +2559,7 @@
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C27" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D27" s="20">
         <v>175000</v>
@@ -2564,7 +2567,7 @@
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C28" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D28" s="21">
         <v>0</v>
@@ -2572,14 +2575,14 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C32" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D32" s="19">
         <v>13</v>
@@ -2587,7 +2590,7 @@
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C33" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D33" s="20">
         <v>43667</v>
@@ -2595,7 +2598,7 @@
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C34" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D34" s="21">
         <v>0.03</v>
@@ -2603,7 +2606,7 @@
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C35" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D35" s="19">
         <v>5</v>
@@ -2611,7 +2614,7 @@
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C36" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D36" s="19">
         <v>5</v>
@@ -2619,7 +2622,7 @@
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C37" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="19">
         <v>5</v>
@@ -2627,7 +2630,7 @@
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C38" s="17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D38" s="19">
         <v>5</v>
@@ -2635,7 +2638,7 @@
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C39" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D39" s="19">
         <v>5</v>
@@ -2643,7 +2646,7 @@
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C40" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D40" s="20">
         <v>71250</v>
@@ -2651,7 +2654,7 @@
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C41" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D41" s="21">
         <v>0.03</v>
@@ -2659,7 +2662,7 @@
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C42" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D42" s="21">
         <v>0.24285714285714285</v>
@@ -2667,14 +2670,14 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B44" s="16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C46" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D46" s="20">
         <v>322000</v>
@@ -2682,7 +2685,7 @@
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C47" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D47" s="21">
         <v>0.03</v>
@@ -2690,7 +2693,7 @@
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C48" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D48" s="20">
         <v>0</v>
@@ -2698,7 +2701,7 @@
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C49" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D49" s="21">
         <v>0.03</v>
@@ -2706,7 +2709,7 @@
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C50" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D50" s="20">
         <v>650</v>
@@ -2714,7 +2717,7 @@
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C51" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D51" s="21">
         <v>0.717948717948718</v>
@@ -2722,7 +2725,7 @@
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C52" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D52" s="20">
         <v>204000</v>
@@ -2730,7 +2733,7 @@
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C53" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D53" s="21">
         <v>0.515686274509804</v>
@@ -2738,14 +2741,14 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C57" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D57" s="20">
         <v>0</v>
@@ -2753,7 +2756,7 @@
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C58" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D58" s="20">
         <v>60000</v>
@@ -2761,7 +2764,7 @@
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C59" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D59" s="20">
         <v>350000</v>
@@ -2769,7 +2772,7 @@
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C60" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D60" s="21">
         <v>0.06</v>
@@ -2777,7 +2780,7 @@
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C61" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D61" s="19">
         <v>10</v>
@@ -2785,30 +2788,30 @@
     </row>
     <row r="64" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64" s="16"/>
       <c r="D64" s="16"/>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C66" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C67" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C68" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D68" s="19">
         <v>0</v>
@@ -2816,7 +2819,7 @@
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C69" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D69" s="19">
         <v>0</v>
@@ -2824,7 +2827,7 @@
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C70" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D70" s="22">
         <v>0.95</v>
@@ -2832,7 +2835,7 @@
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C71" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D71" s="20">
         <v>8200</v>
@@ -2840,7 +2843,7 @@
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C72" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D72" s="20">
         <v>9100</v>
@@ -2848,7 +2851,7 @@
     </row>
     <row r="73" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C73" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D73" s="20">
         <v>10500</v>
@@ -2856,32 +2859,32 @@
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C75" s="23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D75" s="23"/>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C76" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C77" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="78" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C78" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D78" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2920,7 +2923,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2931,24 +2934,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="25"/>
       <c r="C3" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" s="28">
         <f>Assumptions!D12</f>
@@ -2973,7 +2976,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="29" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
@@ -2998,7 +3001,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C6" s="29" t="str">
         <f>C5*Assumptions!D26</f>
@@ -3023,7 +3026,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="29">
         <v>1191000</v>
@@ -3043,7 +3046,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="29">
         <f>Assumptions!D12*Assumptions!D24</f>
@@ -3068,7 +3071,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="29">
         <f>Assumptions!D27</f>
@@ -3093,7 +3096,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C10" s="31">
         <f>C6+C7+C8+C9</f>
@@ -3118,7 +3121,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C12" s="28">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
@@ -3143,7 +3146,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="29">
         <f>C12*Assumptions!D33</f>
@@ -3168,7 +3171,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" s="29">
         <f>Assumptions!D35*Assumptions!D40</f>
@@ -3193,7 +3196,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C15" s="29">
         <f>(C13+C14)*Assumptions!D42</f>
@@ -3218,7 +3221,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C16" s="31">
         <f>C13+C14+C15</f>
@@ -3243,7 +3246,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C18" s="29">
         <f>Assumptions!D46</f>
@@ -3268,7 +3271,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C19" s="29" t="str">
         <f>Assumptions!D48</f>
@@ -3293,7 +3296,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" s="29">
         <f>Assumptions!D12*Assumptions!D50</f>
@@ -3318,7 +3321,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C21" s="29">
         <f>Assumptions!D52</f>
@@ -3343,7 +3346,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C22" s="31">
         <f>C18+C19+C20+C21</f>
@@ -3394,7 +3397,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3405,24 +3408,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="25"/>
       <c r="C3" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5" s="28">
         <f>Drivers!C4</f>
@@ -3447,7 +3450,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" s="29" t="str">
         <f>Drivers!C6</f>
@@ -3472,7 +3475,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C7" s="29">
         <f>Drivers!C7</f>
@@ -3497,7 +3500,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C8" s="29">
         <f>Drivers!C8</f>
@@ -3522,7 +3525,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="29">
         <f>Drivers!C9</f>
@@ -3547,7 +3550,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C10" s="31">
         <f>Drivers!C10</f>
@@ -3572,7 +3575,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C12" s="29">
         <f>Drivers!C16</f>
@@ -3597,7 +3600,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="29">
         <f>Drivers!C22</f>
@@ -3622,7 +3625,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C15" s="31">
         <f>C12+C13</f>
@@ -3647,7 +3650,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="32">
         <f>C10-C15</f>
@@ -3672,7 +3675,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="34">
         <f>IF(C10&gt;0,C16/C10,0)</f>
@@ -3723,7 +3726,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3734,24 +3737,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="25"/>
       <c r="C3" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" s="29">
         <f>'5-Year P&amp;L'!C16</f>
@@ -3776,7 +3779,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C6" s="29">
         <f>Assumptions!D58</f>
@@ -3801,7 +3804,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="27" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="29">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -3826,7 +3829,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="31">
         <f>C6+C7</f>
@@ -3851,7 +3854,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C10" s="35">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
@@ -3876,7 +3879,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="29">
         <f>C4-C8</f>
@@ -3901,7 +3904,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C14" s="37">
         <f>Assumptions!D57+C12</f>
@@ -3952,7 +3955,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3963,24 +3966,24 @@
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="25"/>
       <c r="C3" s="26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F3" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" s="26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="28">
         <f>Drivers!C12</f>
@@ -4005,7 +4008,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" s="28">
         <f>Assumptions!D35</f>
@@ -4030,7 +4033,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C6" s="38">
         <f>C4+C5</f>
@@ -4081,13 +4084,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C3" s="29">
         <f>Assumptions!D59</f>
@@ -4096,7 +4099,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C4" s="34">
         <f>Assumptions!D60</f>
@@ -4105,7 +4108,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="28">
         <f>Assumptions!D61</f>
@@ -4114,7 +4117,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C6" s="39">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4123,7 +4126,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C8" s="35">
         <f>'Cash Flow &amp; DSCR'!C10</f>
@@ -4158,13 +4161,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="27" t="str">
         <f>Assumptions!D5</f>
@@ -4173,7 +4176,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="27" t="str">
         <f>Assumptions!D7</f>
@@ -4182,7 +4185,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C5" s="27" t="str">
         <f>Assumptions!D6</f>
@@ -4191,7 +4194,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C6" s="27">
         <f>Assumptions!D8</f>
@@ -4200,7 +4203,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C8" s="28">
         <f>Assumptions!D16</f>
@@ -4209,7 +4212,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C9" s="29">
         <f>Drivers!G10</f>
@@ -4218,7 +4221,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C10" s="37">
         <f>'5-Year P&amp;L'!G16</f>
@@ -4227,7 +4230,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C12" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -659,7 +659,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -727,6 +727,9 @@
       <color rgb="FF1E293B"/>
       <sz val="14"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
     </font>
     <font>
       <i/>
@@ -888,31 +891,31 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -922,57 +925,57 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -981,10 +984,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="210">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -151,7 +151,10 @@
     <t>SchoolStack Budget - Lender Pro Forma Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -778,7 +781,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -793,6 +796,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -816,7 +824,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -830,6 +838,15 @@
       <top/>
       <bottom style="medium">
         <color rgb="FF328555"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -876,7 +893,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -893,98 +910,99 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="12" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1689,7 +1707,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1708,456 +1726,456 @@
       <c r="G3" s="12"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="D5" s="41" t="s">
+      <c r="B5" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="D5" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="E5" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="F5" s="42" t="s">
         <v>117</v>
       </c>
+      <c r="G5" s="42" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="28">
+      <c r="B6" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="29">
         <v>120</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <v>200</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="29">
         <v>300</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="29">
         <v>400</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="29">
         <v>500</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="29">
+      <c r="B7" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="30">
         <v>1414000</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>2252650</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>3345708</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>4462886.32</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <v>5634801.762</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="C8" s="29">
+      <c r="B8" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" s="30">
         <v>985486.2857142857</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <v>1350450.8631428573</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>1851580.3737342858</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>2322257.9411546146</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="30">
         <v>2880593.1775544523</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="29">
+      <c r="B9" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" s="30">
         <v>604000</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>864193.3333333334</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>1385772.8165912519</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>2380453.4466264746</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <v>4269943.712657611</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="29">
+      <c r="B10" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="30">
         <v>106628.6108154935</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <v>106628.6108154935</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>106628.6108154935</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>106628.6108154935</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <v>106628.6108154935</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="32">
+      <c r="B11" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="33">
         <v>-282114.8965297792</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <v>-68622.80729168432</v>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="34">
         <v>1726.1988589687971</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <v>-346453.6785965824</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="33">
         <v>-1622363.739027556</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="C12" s="32">
+      <c r="B12" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="33">
         <v>-282114.8965297792</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="33">
         <v>-350737.7038214635</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="33">
         <v>-349011.5049624947</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="33">
         <v>-695465.1835590771</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="33">
         <v>-2317828.922586633</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="30" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" s="42">
+      <c r="B13" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" s="43">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D13" s="42">
+      <c r="D13" s="43">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="44">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F13" s="42">
+      <c r="F13" s="43">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="43">
         <v>-0.2879185120528036</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="C14" s="29">
+      <c r="B14" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" s="30">
         <v>11783.333333333334</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>11263.25</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>11152.36</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>11157.2158</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <v>11269.603524</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" s="42">
+      <c r="B15" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" s="43">
         <v>0.6969492826833703</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="44">
         <v>0.5994943125398341</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="44">
         <v>0.5534195972076122</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F15" s="45">
         <v>0.5203488896294841</v>
       </c>
-      <c r="G15" s="44">
+      <c r="G15" s="45">
         <v>0.5112146441389667</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="30" t="s">
-        <v>175</v>
-      </c>
-      <c r="C16" s="44">
+      <c r="B16" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="45">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="45">
         <v>0.11509022706590016</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="45">
         <v>0.12425825713940832</v>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="44">
         <v>0.1600166311177611</v>
       </c>
-      <c r="G16" s="43">
+      <c r="G16" s="44">
         <v>0.227334193446872</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="42">
+      <c r="B17" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="43">
         <v>-0.12410628409779752</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="44">
         <v>0.016871597240498658</v>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="44">
         <v>0.03238621232769336</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="43">
         <v>-0.0537376600220211</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="43">
         <v>-0.26899528896187336</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="45">
+      <c r="B18" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="46">
         <v>-1.645771096258031</v>
       </c>
-      <c r="D18" s="45">
+      <c r="D18" s="46">
         <v>0.35643157341300485</v>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="47">
         <v>1.0161888900715002</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="46">
         <v>-2.2491624522434597</v>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="46">
         <v>-14.215088395316705</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="30" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
+      <c r="B19" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="48" t="s">
+      <c r="B20" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
+      <c r="C20" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="C22" s="40" t="s">
+      <c r="B22" s="41" t="s">
         <v>181</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="C22" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40" t="s">
+      <c r="D22" s="41" t="s">
         <v>183</v>
       </c>
-      <c r="G22" s="40"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" s="41"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="C23" s="50" t="s">
+      <c r="B23" s="50" t="s">
         <v>185</v>
       </c>
-      <c r="D23" s="51" t="s">
+      <c r="C23" s="51" t="s">
         <v>186</v>
       </c>
-      <c r="E23" s="51"/>
-      <c r="F23" s="52" t="s">
+      <c r="D23" s="52" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="G23" s="53"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="C24" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="D24" s="51" t="s">
+      <c r="B24" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="52" t="s">
+      <c r="C24" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="G24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="G24" s="53"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="53" t="s">
+      <c r="B25" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="D25" s="51" t="s">
+      <c r="C25" s="54" t="s">
         <v>193</v>
       </c>
-      <c r="E25" s="51"/>
-      <c r="F25" s="52" t="s">
+      <c r="D25" s="52" t="s">
         <v>194</v>
       </c>
-      <c r="G25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="G25" s="53"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="D26" s="51" t="s">
+      <c r="B26" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="E26" s="51"/>
-      <c r="F26" s="52" t="s">
+      <c r="C26" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="D26" s="52" t="s">
         <v>197</v>
       </c>
-      <c r="G26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="G26" s="53"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="C27" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="D27" s="51" t="s">
+      <c r="B27" s="50" t="s">
         <v>199</v>
       </c>
-      <c r="E27" s="51"/>
-      <c r="F27" s="52" t="s">
+      <c r="C27" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="D27" s="52" t="s">
         <v>200</v>
       </c>
-      <c r="G27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="G27" s="53"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="C28" s="53" t="s">
-        <v>192</v>
-      </c>
-      <c r="D28" s="51" t="s">
+      <c r="B28" s="50" t="s">
         <v>202</v>
       </c>
-      <c r="E28" s="51"/>
-      <c r="F28" s="52" t="s">
+      <c r="C28" s="54" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="52" t="s">
         <v>203</v>
       </c>
-      <c r="G28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="G28" s="53"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="D29" s="51" t="s">
+      <c r="B29" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="E29" s="51"/>
-      <c r="F29" s="52" t="s">
+      <c r="C29" s="51" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="52" t="s">
         <v>206</v>
       </c>
-      <c r="G29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="G29" s="53"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="30" t="s">
-        <v>207</v>
-      </c>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
+      <c r="C31" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="54" t="s">
-        <v>208</v>
-      </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
-      <c r="F33" s="54"/>
-      <c r="G33" s="54"/>
+      <c r="B33" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -2403,491 +2421,494 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>43</v>
       </c>
+      <c r="D2" s="16" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
+      <c r="B3" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="C5" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="18" t="s">
+      <c r="C6" s="18" t="s">
         <v>47</v>
       </c>
+      <c r="D6" s="19" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="C7" s="18" t="s">
         <v>49</v>
       </c>
+      <c r="D7" s="19" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="18">
+      <c r="C8" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="19">
         <v>2026</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="19">
+      <c r="C12" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="20">
         <v>120</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="19">
+      <c r="C13" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="20">
         <v>200</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="19">
+      <c r="C14" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="20">
         <v>300</v>
       </c>
     </row>
     <row r="15" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="19">
+      <c r="C15" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="20">
         <v>400</v>
       </c>
     </row>
     <row r="16" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C16" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="19">
+      <c r="C16" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="20">
         <v>500</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="B18" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="20">
+      <c r="C20" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="21">
+      <c r="C21" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="20">
+      <c r="C22" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="21">
+      <c r="C23" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="20">
+      <c r="C24" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="21">
         <v>400</v>
       </c>
     </row>
     <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="21">
+      <c r="C25" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" s="21">
+      <c r="C26" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" s="22">
         <v>0.95</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="20">
+      <c r="C27" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="21">
         <v>175000</v>
       </c>
     </row>
     <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="21">
+      <c r="C28" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B30" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
+      <c r="B30" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
     </row>
     <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="19">
+      <c r="C32" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="20">
         <v>13</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D33" s="20">
+      <c r="C33" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="21">
         <v>43667</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="21">
+      <c r="C34" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="19">
+      <c r="C35" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="19">
+      <c r="C36" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="19">
+      <c r="C37" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D38" s="19">
+      <c r="C38" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" s="19">
+      <c r="C39" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="20">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" s="20">
+      <c r="C40" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D40" s="21">
         <v>71250</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="D41" s="21">
+      <c r="C41" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" s="21">
+      <c r="C42" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="22">
         <v>0.24285714285714285</v>
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="16"/>
+      <c r="B44" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="20">
+      <c r="C46" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D46" s="21">
         <v>322000</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="21">
+      <c r="C47" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D48" s="20">
+      <c r="C48" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D49" s="21">
+      <c r="C49" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="22">
         <v>0.03</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="D50" s="20">
+      <c r="C50" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D50" s="21">
         <v>650</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" s="21">
+      <c r="C51" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D51" s="22">
         <v>0.717948717948718</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D52" s="20">
+      <c r="C52" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" s="21">
         <v>204000</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="D53" s="21">
+      <c r="C53" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D53" s="22">
         <v>0.515686274509804</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
+      <c r="B55" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C55" s="17"/>
+      <c r="D55" s="17"/>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57" s="20">
+      <c r="C57" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D57" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D58" s="20">
+      <c r="C58" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="21">
         <v>60000</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="D59" s="20">
+      <c r="C59" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59" s="21">
         <v>350000</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60" s="21">
+      <c r="C60" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60" s="22">
         <v>0.06</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D61" s="19">
+      <c r="C61" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61" s="20">
         <v>10</v>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B64" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
+      <c r="B64" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D66" s="18" t="s">
+      <c r="C66" s="18" t="s">
         <v>96</v>
       </c>
+      <c r="D66" s="19" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="67" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C67" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D67" s="18" t="s">
+      <c r="C67" s="18" t="s">
         <v>98</v>
       </c>
+      <c r="D67" s="19" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="68" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C68" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D68" s="19">
+      <c r="C68" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C69" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D69" s="19">
+      <c r="C69" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D69" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C70" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="D70" s="22">
+      <c r="C70" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D70" s="23">
         <v>0.95</v>
       </c>
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C71" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D71" s="20">
+      <c r="C71" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D71" s="21">
         <v>8200</v>
       </c>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C72" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="D72" s="20">
+      <c r="C72" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D72" s="21">
         <v>9100</v>
       </c>
     </row>
     <row r="73" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C73" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D73" s="20">
+      <c r="C73" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" s="21">
         <v>10500</v>
       </c>
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C75" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D75" s="23"/>
+      <c r="C75" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D75" s="24"/>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C76" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="D76" s="24" t="s">
+      <c r="C76" s="18" t="s">
         <v>107</v>
       </c>
+      <c r="D76" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C77" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="D77" s="24" t="s">
+      <c r="C77" s="18" t="s">
         <v>109</v>
       </c>
+      <c r="D77" s="25" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="78" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C78" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="D78" s="24" t="s">
+      <c r="C78" s="18" t="s">
         <v>111</v>
+      </c>
+      <c r="D78" s="25" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2926,7 +2947,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2935,439 +2956,439 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="25"/>
-      <c r="C3" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="26" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="F3" s="27" t="s">
         <v>117</v>
       </c>
+      <c r="G3" s="27" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="28">
+      <c r="B4" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="29">
         <f>Assumptions!D12</f>
         <v>120</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <f>Assumptions!D13</f>
         <v>200</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="29">
         <f>Assumptions!D14</f>
         <v>300</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <f>Assumptions!D15</f>
         <v>400</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="29">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="29" t="str">
+      <c r="B5" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="30" t="str">
         <f>Assumptions!D12*Assumptions!D20</f>
         <v>0</v>
       </c>
-      <c r="D5" s="29" t="str">
+      <c r="D5" s="30" t="str">
         <f>Assumptions!D13*Assumptions!D20*(1+Assumptions!D21)^1</f>
         <v>0</v>
       </c>
-      <c r="E5" s="29" t="str">
+      <c r="E5" s="30" t="str">
         <f>Assumptions!D14*Assumptions!D20*(1+Assumptions!D21)^2</f>
         <v>0</v>
       </c>
-      <c r="F5" s="29" t="str">
+      <c r="F5" s="30" t="str">
         <f>Assumptions!D15*Assumptions!D20*(1+Assumptions!D21)^3</f>
         <v>0</v>
       </c>
-      <c r="G5" s="29" t="str">
+      <c r="G5" s="30" t="str">
         <f>Assumptions!D16*Assumptions!D20*(1+Assumptions!D21)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="29" t="str">
+      <c r="B6" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="30" t="str">
         <f>C5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="D6" s="29" t="str">
+      <c r="D6" s="30" t="str">
         <f>D5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="E6" s="29" t="str">
+      <c r="E6" s="30" t="str">
         <f>E5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="F6" s="29" t="str">
+      <c r="F6" s="30" t="str">
         <f>F5*Assumptions!D26</f>
         <v>0</v>
       </c>
-      <c r="G6" s="29" t="str">
+      <c r="G6" s="30" t="str">
         <f>G5*Assumptions!D26</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="29">
+      <c r="B7" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="30">
         <v>1191000</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <v>1995250</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>3043400</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>4113050</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="29">
+      <c r="B8" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="30">
         <f>Assumptions!D12*Assumptions!D24</f>
         <v>48000</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>Assumptions!D13*Assumptions!D24*(1+Assumptions!D25)^1</f>
         <v>82400</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>Assumptions!D14*Assumptions!D24*(1+Assumptions!D25)^2</f>
         <v>127308</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>Assumptions!D15*Assumptions!D24*(1+Assumptions!D25)^3</f>
         <v>174836.32</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="30">
         <f>Assumptions!D16*Assumptions!D24*(1+Assumptions!D25)^4</f>
         <v>225101.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="29">
+      <c r="B9" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="30">
         <f>Assumptions!D27</f>
         <v>175000</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>Assumptions!D27*(1+Assumptions!D28)^1</f>
         <v>175000</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>Assumptions!D27*(1+Assumptions!D28)^2</f>
         <v>175000</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>Assumptions!D27*(1+Assumptions!D28)^3</f>
         <v>175000</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <f>Assumptions!D27*(1+Assumptions!D28)^4</f>
         <v>175000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="31">
+      <c r="B10" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="32">
         <f>C6+C7+C8+C9</f>
         <v>1414000</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>D6+D7+D8+D9</f>
         <v>2252650</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>E6+E7+E8+E9</f>
         <v>3345708</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>F6+F7+F8+F9</f>
         <v>4462886.32</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>G6+G7+G8+G9</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="28">
+      <c r="B12" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="29">
         <f>CEILING(Assumptions!D12/Assumptions!D32,1)</f>
         <v>10</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <f>CEILING(Assumptions!D13/Assumptions!D32,1)</f>
         <v>16</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>CEILING(Assumptions!D14/Assumptions!D32,1)</f>
         <v>24</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <f>CEILING(Assumptions!D15/Assumptions!D32,1)</f>
         <v>31</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="29">
         <f>CEILING(Assumptions!D16/Assumptions!D32,1)</f>
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="29">
+      <c r="B13" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C13" s="30">
         <f>C12*Assumptions!D33</f>
         <v>436670</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>D12*Assumptions!D33*(1+Assumptions!D34)^1</f>
         <v>719632.16</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>E12*Assumptions!D33*(1+Assumptions!D34)^2</f>
         <v>1111831.6872</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>F12*Assumptions!D33*(1+Assumptions!D34)^3</f>
         <v>1479199.407179</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>G12*Assumptions!D33*(1+Assumptions!D34)^4</f>
         <v>1916756.13504453</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="29">
+      <c r="B14" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="30">
         <f>Assumptions!D35*Assumptions!D40</f>
         <v>356250</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <f>Assumptions!D36*Assumptions!D40*(1+Assumptions!D41)^1</f>
         <v>366937.5</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <f>Assumptions!D37*Assumptions!D40*(1+Assumptions!D41)^2</f>
         <v>377945.625</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <f>Assumptions!D38*Assumptions!D40*(1+Assumptions!D41)^3</f>
         <v>389283.99375</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="30">
         <f>Assumptions!D39*Assumptions!D40*(1+Assumptions!D41)^4</f>
         <v>400962.5135625</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="29">
+      <c r="B15" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="30">
         <f>(C13+C14)*Assumptions!D42</f>
         <v>192566.28571429</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>(D13+D14)*Assumptions!D42</f>
         <v>263881.20314286</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>(E13+E14)*Assumptions!D42</f>
         <v>361803.06153429</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>(F13+F14)*Assumptions!D42</f>
         <v>453774.54022561</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="30">
         <f>(G13+G14)*Assumptions!D42</f>
         <v>562874.52894742</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="31">
+      <c r="B16" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="32">
         <f>C13+C14+C15</f>
         <v>985486.28571429</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>D13+D14+D15</f>
         <v>1350450.86314286</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="32">
         <f>E13+E14+E15</f>
         <v>1851580.37373429</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="32">
         <f>F13+F14+F15</f>
         <v>2322257.94115461</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="32">
         <f>G13+G14+G15</f>
         <v>2880593.17755445</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="29">
+      <c r="B18" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="30">
         <f>Assumptions!D46</f>
         <v>322000</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>Assumptions!D46*(1+Assumptions!D47)^1</f>
         <v>331660</v>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>Assumptions!D46*(1+Assumptions!D47)^2</f>
         <v>341609.8</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="30">
         <f>Assumptions!D46*(1+Assumptions!D47)^3</f>
         <v>351858.094</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="30">
         <f>Assumptions!D46*(1+Assumptions!D47)^4</f>
         <v>362413.83682</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" s="29" t="str">
+      <c r="B19" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="30" t="str">
         <f>Assumptions!D48</f>
         <v>0</v>
       </c>
-      <c r="D19" s="29" t="str">
+      <c r="D19" s="30" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^1</f>
         <v>0</v>
       </c>
-      <c r="E19" s="29" t="str">
+      <c r="E19" s="30" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^2</f>
         <v>0</v>
       </c>
-      <c r="F19" s="29" t="str">
+      <c r="F19" s="30" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^3</f>
         <v>0</v>
       </c>
-      <c r="G19" s="29" t="str">
+      <c r="G19" s="30" t="str">
         <f>Assumptions!D48*(1+Assumptions!D49)^4</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C20" s="29">
+      <c r="B20" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="30">
         <f>Assumptions!D12*Assumptions!D50</f>
         <v>78000</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>Assumptions!D13*Assumptions!D50*(1+Assumptions!D51)^1</f>
         <v>223333.33333333</v>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>Assumptions!D14*Assumptions!D50*(1+Assumptions!D51)^2</f>
         <v>575512.82051282</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="30">
         <f>Assumptions!D15*Assumptions!D50*(1+Assumptions!D51)^3</f>
         <v>1318268.68288407</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="30">
         <f>Assumptions!D16*Assumptions!D50*(1+Assumptions!D51)^4</f>
         <v>2830897.49209079</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C21" s="29">
+      <c r="B21" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="30">
         <f>Assumptions!D52</f>
         <v>204000</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <f>Assumptions!D52*(1+Assumptions!D53)^1</f>
         <v>309200</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <f>Assumptions!D52*(1+Assumptions!D53)^2</f>
         <v>468650.19607843</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <f>Assumptions!D52*(1+Assumptions!D53)^3</f>
         <v>710326.66974241</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <f>Assumptions!D52*(1+Assumptions!D53)^4</f>
         <v>1076632.38374682</v>
       </c>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="31">
+      <c r="B22" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="32">
         <f>C18+C19+C20+C21</f>
         <v>604000</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <f>D18+D19+D20+D21</f>
         <v>864193.33333333</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <f>E18+E19+E20+E21</f>
         <v>1385772.81659125</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <f>F18+F19+F20+F21</f>
         <v>2380453.44662647</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <f>G18+G19+G20+G21</f>
         <v>4269943.71265761</v>
       </c>
@@ -3400,7 +3421,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3409,294 +3430,294 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="25"/>
-      <c r="C3" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="26" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="F3" s="27" t="s">
         <v>117</v>
       </c>
+      <c r="G3" s="27" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="28">
+      <c r="B5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="29">
         <f>Drivers!C4</f>
         <v>120</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <f>Drivers!D4</f>
         <v>200</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <f>Drivers!E4</f>
         <v>300</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>Drivers!F4</f>
         <v>400</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <f>Drivers!G4</f>
         <v>500</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="29" t="str">
+      <c r="B6" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="30" t="str">
         <f>Drivers!C6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="29" t="str">
+      <c r="D6" s="30" t="str">
         <f>Drivers!D6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="29" t="str">
+      <c r="E6" s="30" t="str">
         <f>Drivers!E6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="29" t="str">
+      <c r="F6" s="30" t="str">
         <f>Drivers!F6</f>
         <v>0</v>
       </c>
-      <c r="G6" s="29" t="str">
+      <c r="G6" s="30" t="str">
         <f>Drivers!G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="29">
+      <c r="B7" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="30">
         <f>Drivers!C7</f>
         <v>1191000</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>Drivers!D7</f>
         <v>1995250</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>Drivers!E7</f>
         <v>3043400</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>Drivers!F7</f>
         <v>4113050</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <f>Drivers!G7</f>
         <v>5234700</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" s="29">
+      <c r="B8" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="30">
         <f>Drivers!C8</f>
         <v>48000</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>Drivers!D8</f>
         <v>82400</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>Drivers!E8</f>
         <v>127308</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>Drivers!F8</f>
         <v>174836.32</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="30">
         <f>Drivers!G8</f>
         <v>225101.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="29">
+      <c r="B9" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="30">
         <f>Drivers!C9</f>
         <v>175000</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>Drivers!D9</f>
         <v>175000</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <f>Drivers!E9</f>
         <v>175000</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <f>Drivers!F9</f>
         <v>175000</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <f>Drivers!G9</f>
         <v>175000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="31">
+      <c r="B10" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="32">
         <f>Drivers!C10</f>
         <v>1414000</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>Drivers!D10</f>
         <v>2252650</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>Drivers!E10</f>
         <v>3345708</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>Drivers!F10</f>
         <v>4462886.32</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>Drivers!G10</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="29">
+      <c r="B12" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="30">
         <f>Drivers!C16</f>
         <v>985486.28571429</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>Drivers!D16</f>
         <v>1350450.86314286</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>Drivers!E16</f>
         <v>1851580.37373429</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>Drivers!F16</f>
         <v>2322257.94115461</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="30">
         <f>Drivers!G16</f>
         <v>2880593.17755445</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="29">
+      <c r="B13" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="30">
         <f>Drivers!C22</f>
         <v>604000</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="30">
         <f>Drivers!D22</f>
         <v>864193.33333333</v>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>Drivers!E22</f>
         <v>1385772.81659125</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="30">
         <f>Drivers!F22</f>
         <v>2380453.44662647</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>Drivers!G22</f>
         <v>4269943.71265761</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="31">
+      <c r="B15" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="32">
         <f>C12+C13</f>
         <v>1589486.28571429</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>D12+D13</f>
         <v>2214644.19647619</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>E12+E13</f>
         <v>3237353.19032554</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>F12+F13</f>
         <v>4702711.38778109</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="32">
         <f>G12+G13</f>
         <v>7150536.89021206</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="32">
+      <c r="B16" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" s="33">
         <f>C10-C15</f>
         <v>-175486.28571429</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="34">
         <f>D10-D15</f>
         <v>38005.80352381</v>
       </c>
-      <c r="E16" s="33">
+      <c r="E16" s="34">
         <f>E10-E15</f>
         <v>108354.80967446</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="33">
         <f>F10-F15</f>
         <v>-239825.06778109</v>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="33">
         <f>G10-G15</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="C17" s="34">
+      <c r="B17" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="35">
         <f>IF(C10&gt;0,C16/C10,0)</f>
         <v>-0.12410628</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="35">
         <f>IF(D10&gt;0,D16/D10,0)</f>
         <v>0.0168716</v>
       </c>
-      <c r="E17" s="34">
+      <c r="E17" s="35">
         <f>IF(E10&gt;0,E16/E10,0)</f>
         <v>0.03238621</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="35">
         <f>IF(F10&gt;0,F16/F10,0)</f>
         <v>-0.05373766</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="35">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>-0.26899529</v>
       </c>
@@ -3729,7 +3750,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3738,194 +3759,194 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="25"/>
-      <c r="C3" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="26" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="F3" s="27" t="s">
         <v>117</v>
       </c>
+      <c r="G3" s="27" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="29">
+      <c r="B4" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="30">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-175486.28571429</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <f>'5-Year P&amp;L'!D16</f>
         <v>38005.80352381</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <f>'5-Year P&amp;L'!E16</f>
         <v>108354.80967446</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <f>'5-Year P&amp;L'!F16</f>
         <v>-239825.06778109</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="30">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="29">
+      <c r="B6" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="29">
+      <c r="B7" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" s="31">
+      <c r="B8" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="32">
         <f>C6+C7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>D6+D7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>E6+E7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>F6+F7</f>
         <v>106628.61081549</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>G6+G7</f>
         <v>106628.61081549</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="C10" s="35">
+      <c r="B10" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="36">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.6457711</v>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="36">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.35643157</v>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>1.01618889</v>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="36">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>-2.24916245</v>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="36">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>-14.2150884</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="29">
+      <c r="B12" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="30">
         <f>C4-C8</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>D4-D8</f>
         <v>-68622.80729168</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>E4-E8</f>
         <v>1726.19885897</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>F4-F8</f>
         <v>-346453.67859658</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="30">
         <f>G4-G8</f>
         <v>-1622363.73902756</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="C14" s="37">
+      <c r="B14" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="38">
         <f>Assumptions!D57+C12</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="38">
         <f>C14+D12</f>
         <v>-350737.70382146</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="38">
         <f>D14+E12</f>
         <v>-349011.50496249</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="38">
         <f>E14+F12</f>
         <v>-695465.18355908</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="38">
         <f>F14+G12</f>
         <v>-2317828.92258663</v>
       </c>
@@ -3958,7 +3979,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3967,94 +3988,94 @@
       <c r="G1" s="13"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="25"/>
-      <c r="C3" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="26" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="D3" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="F3" s="27" t="s">
         <v>117</v>
       </c>
+      <c r="G3" s="27" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="28">
+      <c r="B4" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="29">
         <f>Drivers!C12</f>
         <v>10</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <f>Drivers!D12</f>
         <v>16</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="29">
         <f>Drivers!E12</f>
         <v>24</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <f>Drivers!F12</f>
         <v>31</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="29">
         <f>Drivers!G12</f>
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="28">
+      <c r="B5" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="29">
         <f>Assumptions!D35</f>
         <v>5</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <f>Assumptions!D36</f>
         <v>5</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <f>Assumptions!D37</f>
         <v>5</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>Assumptions!D38</f>
         <v>5</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <f>Assumptions!D39</f>
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="38">
+      <c r="B6" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="39">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="39">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="39">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="39">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="39">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -4087,51 +4108,51 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="C3" s="29">
+      <c r="B3" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="30">
         <f>Assumptions!D59</f>
         <v>350000</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="C4" s="34">
+      <c r="B4" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="35">
         <f>Assumptions!D60</f>
         <v>0.06</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="28">
+      <c r="B5" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="29">
         <f>Assumptions!D61</f>
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="39">
+      <c r="B6" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="40">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C8" s="35">
+      <c r="B8" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="36">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.6457711</v>
       </c>
@@ -4164,76 +4185,76 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="27" t="str">
+      <c r="B3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="28" t="str">
         <f>Assumptions!D5</f>
         <v>Heritage Academy Charter</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="27" t="str">
+      <c r="B4" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="28" t="str">
         <f>Assumptions!D7</f>
         <v>Charter School</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="27" t="str">
+      <c r="B5" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="28" t="str">
         <f>Assumptions!D6</f>
         <v>AZ</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="C6" s="27">
+      <c r="B6" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="28">
         <f>Assumptions!D8</f>
         <v>2026</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="28">
+      <c r="B8" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="29">
         <f>Assumptions!D16</f>
         <v>500</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="C9" s="29">
+      <c r="B9" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="30">
         <f>Drivers!G10</f>
         <v>5634801.762</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="37">
+      <c r="B10" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="38">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C12" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="210">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -910,7 +910,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2405,7 +2405,7 @@
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D78"/>
+  <dimension ref="B1:E78"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -2421,7 +2421,7 @@
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="14" t="s">
         <v>7</v>
       </c>
@@ -2429,6 +2429,9 @@
         <v>43</v>
       </c>
       <c r="D2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>44</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="222">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -520,9 +520,21 @@
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
     <t>Revenue</t>
   </si>
   <si>
@@ -547,15 +559,36 @@
     <t>Revenue per Student</t>
   </si>
   <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
     <t>DSCR</t>
   </si>
   <si>
+    <t>≥ 1.25x</t>
+  </si>
+  <si>
     <t>Break-even Year</t>
   </si>
   <si>
@@ -563,6 +596,9 @@
   </si>
   <si>
     <t>0 months</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -662,7 +698,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -765,6 +801,12 @@
     <font>
       <b/>
       <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -893,7 +935,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -971,6 +1013,9 @@
     <xf numFmtId="165" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -981,9 +1026,14 @@
     <xf numFmtId="166" fontId="17" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -991,9 +1041,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1005,14 +1055,35 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1693,19 +1764,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>165</v>
       </c>
@@ -1714,8 +1786,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>40</v>
       </c>
@@ -1724,559 +1797,632 @@
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="41" t="s">
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="D4" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D6" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E6" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F6" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G6" s="45" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="29">
-        <v>120</v>
-      </c>
-      <c r="D6" s="29">
-        <v>200</v>
-      </c>
-      <c r="E6" s="29">
-        <v>300</v>
-      </c>
-      <c r="F6" s="29">
-        <v>400</v>
-      </c>
-      <c r="G6" s="29">
-        <v>500</v>
+      <c r="H6" s="45" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="C7" s="30">
-        <v>1414000</v>
-      </c>
-      <c r="D7" s="30">
-        <v>2252650</v>
-      </c>
-      <c r="E7" s="30">
-        <v>3345708</v>
-      </c>
-      <c r="F7" s="30">
-        <v>4462886.32</v>
-      </c>
-      <c r="G7" s="30">
-        <v>5634801.762</v>
+        <v>119</v>
+      </c>
+      <c r="C7" s="29">
+        <v>120</v>
+      </c>
+      <c r="D7" s="29">
+        <v>200</v>
+      </c>
+      <c r="E7" s="29">
+        <v>300</v>
+      </c>
+      <c r="F7" s="29">
+        <v>400</v>
+      </c>
+      <c r="G7" s="29">
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C8" s="30">
-        <v>985486.2857142857</v>
+        <v>1414000</v>
       </c>
       <c r="D8" s="30">
-        <v>1350450.8631428573</v>
+        <v>2252650</v>
       </c>
       <c r="E8" s="30">
-        <v>1851580.3737342858</v>
+        <v>3345708</v>
       </c>
       <c r="F8" s="30">
-        <v>2322257.9411546146</v>
+        <v>4462886.32</v>
       </c>
       <c r="G8" s="30">
-        <v>2880593.1775544523</v>
+        <v>5634801.762</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C9" s="30">
-        <v>604000</v>
+        <v>985486.2857142857</v>
       </c>
       <c r="D9" s="30">
-        <v>864193.3333333334</v>
+        <v>1350450.8631428573</v>
       </c>
       <c r="E9" s="30">
-        <v>1385772.8165912519</v>
+        <v>1851580.3737342858</v>
       </c>
       <c r="F9" s="30">
-        <v>2380453.4466264746</v>
+        <v>2322257.9411546146</v>
       </c>
       <c r="G9" s="30">
-        <v>4269943.712657611</v>
+        <v>2880593.1775544523</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C10" s="30">
+        <v>604000</v>
+      </c>
+      <c r="D10" s="30">
+        <v>864193.3333333334</v>
+      </c>
+      <c r="E10" s="30">
+        <v>1385772.8165912519</v>
+      </c>
+      <c r="F10" s="30">
+        <v>2380453.4466264746</v>
+      </c>
+      <c r="G10" s="30">
+        <v>4269943.712657611</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="30">
         <v>106628.6108154935</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D11" s="30">
         <v>106628.6108154935</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E11" s="30">
         <v>106628.6108154935</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F11" s="30">
         <v>106628.6108154935</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G11" s="30">
         <v>106628.6108154935</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="C11" s="33">
-        <v>-282114.8965297792</v>
-      </c>
-      <c r="D11" s="33">
-        <v>-68622.80729168432</v>
-      </c>
-      <c r="E11" s="34">
-        <v>1726.1988589687971</v>
-      </c>
-      <c r="F11" s="33">
-        <v>-346453.6785965824</v>
-      </c>
-      <c r="G11" s="33">
-        <v>-1622363.739027556</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C12" s="33">
         <v>-282114.8965297792</v>
       </c>
       <c r="D12" s="33">
-        <v>-350737.7038214635</v>
-      </c>
-      <c r="E12" s="33">
-        <v>-349011.5049624947</v>
+        <v>-68622.80729168432</v>
+      </c>
+      <c r="E12" s="34">
+        <v>1726.1988589687971</v>
       </c>
       <c r="F12" s="33">
-        <v>-695465.1835590771</v>
+        <v>-346453.6785965824</v>
       </c>
       <c r="G12" s="33">
-        <v>-2317828.922586633</v>
+        <v>-1622363.739027556</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="C13" s="43">
-        <v>-0.19951548552318188</v>
-      </c>
-      <c r="D13" s="43">
-        <v>-0.03046314664581019</v>
-      </c>
-      <c r="E13" s="44">
-        <v>0.0005159442661968101</v>
-      </c>
-      <c r="F13" s="43">
-        <v>-0.07762995822770193</v>
-      </c>
-      <c r="G13" s="43">
-        <v>-0.2879185120528036</v>
+        <v>176</v>
+      </c>
+      <c r="C13" s="33">
+        <v>-282114.8965297792</v>
+      </c>
+      <c r="D13" s="33">
+        <v>-350737.7038214635</v>
+      </c>
+      <c r="E13" s="33">
+        <v>-349011.5049624947</v>
+      </c>
+      <c r="F13" s="33">
+        <v>-695465.1835590771</v>
+      </c>
+      <c r="G13" s="33">
+        <v>-2317828.922586633</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="C14" s="30">
+        <v>177</v>
+      </c>
+      <c r="C14" s="46">
+        <v>-0.19951548552318188</v>
+      </c>
+      <c r="D14" s="46">
+        <v>-0.03046314664581019</v>
+      </c>
+      <c r="E14" s="47">
+        <v>0.0005159442661968101</v>
+      </c>
+      <c r="F14" s="46">
+        <v>-0.07762995822770193</v>
+      </c>
+      <c r="G14" s="46">
+        <v>-0.2879185120528036</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="C15" s="48">
         <v>11783.333333333334</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D15" s="48">
         <v>11263.25</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E15" s="48">
         <v>11152.36</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F15" s="48">
         <v>11157.2158</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G15" s="48">
         <v>11269.603524</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="43">
+      <c r="H15" s="49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" s="46">
         <v>0.6969492826833703</v>
       </c>
-      <c r="D15" s="44">
+      <c r="D16" s="47">
         <v>0.5994943125398341</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E16" s="47">
         <v>0.5534195972076122</v>
       </c>
-      <c r="F15" s="45">
+      <c r="F16" s="50">
         <v>0.5203488896294841</v>
       </c>
-      <c r="G15" s="45">
+      <c r="G16" s="50">
         <v>0.5112146441389667</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" s="45">
+      <c r="H16" s="49" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" s="50">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D17" s="50">
         <v>0.11509022706590016</v>
       </c>
-      <c r="E16" s="45">
+      <c r="E17" s="50">
         <v>0.12425825713940832</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F17" s="47">
         <v>0.1600166311177611</v>
       </c>
-      <c r="G16" s="44">
+      <c r="G17" s="47">
         <v>0.227334193446872</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="31" t="s">
+      <c r="H17" s="49" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C18" s="46">
         <v>-0.12410628409779752</v>
       </c>
-      <c r="D17" s="44">
+      <c r="D18" s="47">
         <v>0.016871597240498658</v>
       </c>
-      <c r="E17" s="44">
+      <c r="E18" s="47">
         <v>0.03238621232769336</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F18" s="46">
         <v>-0.0537376600220211</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G18" s="46">
         <v>-0.26899528896187336</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="C18" s="46">
+      <c r="H18" s="49" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="C19" s="51">
+        <v>1</v>
+      </c>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="49" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="52">
         <v>-1.645771096258031</v>
       </c>
-      <c r="D18" s="46">
+      <c r="D20" s="52">
         <v>0.35643157341300485</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E20" s="53">
         <v>1.0161888900715002</v>
       </c>
-      <c r="F18" s="46">
+      <c r="F20" s="52">
         <v>-2.2491624522434597</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G20" s="52">
         <v>-14.215088395316705</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="48" t="s">
+      <c r="H20" s="49" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="D19" s="48"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="48"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="C20" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>182</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>183</v>
-      </c>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="G22" s="41"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="52"/>
-      <c r="F23" s="53" t="s">
-        <v>188</v>
-      </c>
-      <c r="G23" s="53"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="50" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="D24" s="52" t="s">
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="49" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="E24" s="52"/>
-      <c r="F24" s="53" t="s">
+      <c r="C22" s="55" t="s">
         <v>191</v>
       </c>
-      <c r="G24" s="53"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="50" t="s">
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="C25" s="54" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="C24" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="E25" s="52"/>
-      <c r="F25" s="53" t="s">
+      <c r="D24" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="G25" s="53"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="50" t="s">
+      <c r="E24" s="44"/>
+      <c r="F24" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="C26" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="D26" s="52" t="s">
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="56" t="s">
         <v>197</v>
       </c>
-      <c r="E26" s="52"/>
-      <c r="F26" s="53" t="s">
+      <c r="C25" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="G26" s="53"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="50" t="s">
+      <c r="D25" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="C27" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="D27" s="52" t="s">
+      <c r="E25" s="58"/>
+      <c r="F25" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="E27" s="52"/>
-      <c r="F27" s="53" t="s">
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="56" t="s">
         <v>201</v>
       </c>
-      <c r="G27" s="53"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="s">
+      <c r="C26" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="58" t="s">
         <v>202</v>
       </c>
-      <c r="C28" s="54" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="52" t="s">
+      <c r="E26" s="58"/>
+      <c r="F26" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="E28" s="52"/>
-      <c r="F28" s="53" t="s">
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="G28" s="53"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="50" t="s">
+      <c r="C27" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="C29" s="51" t="s">
-        <v>186</v>
-      </c>
-      <c r="D29" s="52" t="s">
+      <c r="D27" s="58" t="s">
         <v>206</v>
       </c>
-      <c r="E29" s="52"/>
-      <c r="F29" s="53" t="s">
+      <c r="E27" s="58"/>
+      <c r="F27" s="59" t="s">
         <v>207</v>
       </c>
-      <c r="G29" s="53"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="50" t="s">
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="56" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="E28" s="58"/>
+      <c r="F28" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="56" t="s">
+        <v>211</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D29" s="58" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" s="58"/>
+      <c r="F29" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="E30" s="58"/>
+      <c r="F30" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="56" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D31" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="E31" s="58"/>
+      <c r="F31" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="55" t="s">
-        <v>209</v>
-      </c>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="55"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="55"/>
+      <c r="C33" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="61" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" s="61"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=1.25</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=1.0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;1.0</formula>
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="225">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -451,6 +451,12 @@
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>Cumulative Net Income</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
     <t>Cash Flow &amp; Debt Service Coverage</t>
   </si>
   <si>
@@ -592,6 +598,9 @@
     <t>Break-even Year</t>
   </si>
   <si>
+    <t>Not reached</t>
+  </si>
+  <si>
     <t>Cash Runway</t>
   </si>
   <si>
@@ -619,7 +628,7 @@
     <t>○ Needs attention</t>
   </si>
   <si>
-    <t>Year 5 margin of -29% signals the model is not yet on a sustainable path.</t>
+    <t>The model does not reach break-even within 5 years. This needs to be addressed before approaching lenders.</t>
   </si>
   <si>
     <t>Revisit revenue assumptions and cost structure to build a clear path to break-even.</t>
@@ -998,6 +1007,12 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="167" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1008,9 +1023,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1033,14 +1045,13 @@
     <xf numFmtId="166" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1779,7 +1790,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1800,37 +1811,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="F4" s="43" t="s">
+      <c r="B4" s="42" t="s">
         <v>168</v>
       </c>
+      <c r="D4" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="44" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="45" t="s">
+      <c r="B6" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="45" t="s">
+      <c r="D6" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="45" t="s">
+      <c r="E6" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="45" t="s">
+      <c r="G6" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="45" t="s">
-        <v>170</v>
+      <c r="H6" s="46" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1855,7 +1866,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C8" s="30">
         <v>1414000</v>
@@ -1875,7 +1886,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C9" s="30">
         <v>985486.2857142857</v>
@@ -1895,7 +1906,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C10" s="30">
         <v>604000</v>
@@ -1915,7 +1926,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C11" s="30">
         <v>106628.6108154935</v>
@@ -1935,7 +1946,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C12" s="33">
         <v>-282114.8965297792</v>
@@ -1955,7 +1966,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C13" s="33">
         <v>-282114.8965297792</v>
@@ -1975,316 +1986,316 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="46">
+        <v>179</v>
+      </c>
+      <c r="C14" s="47">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="47">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="48">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="47">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="47">
         <v>-0.2879185120528036</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="C15" s="48">
+        <v>180</v>
+      </c>
+      <c r="C15" s="49">
         <v>11783.333333333334</v>
       </c>
-      <c r="D15" s="48">
+      <c r="D15" s="49">
         <v>11263.25</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="49">
         <v>11152.36</v>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="49">
         <v>11157.2158</v>
       </c>
-      <c r="G15" s="48">
+      <c r="G15" s="49">
         <v>11269.603524</v>
       </c>
-      <c r="H15" s="49" t="s">
-        <v>179</v>
+      <c r="H15" s="50" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16" s="46">
+        <v>182</v>
+      </c>
+      <c r="C16" s="47">
         <v>0.6969492826833703</v>
       </c>
-      <c r="D16" s="47">
+      <c r="D16" s="48">
         <v>0.5994943125398341</v>
       </c>
-      <c r="E16" s="47">
+      <c r="E16" s="48">
         <v>0.5534195972076122</v>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="51">
         <v>0.5203488896294841</v>
       </c>
-      <c r="G16" s="50">
+      <c r="G16" s="51">
         <v>0.5112146441389667</v>
       </c>
-      <c r="H16" s="49" t="s">
-        <v>181</v>
+      <c r="H16" s="50" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" s="50">
+        <v>184</v>
+      </c>
+      <c r="C17" s="51">
         <v>0.12814710042432814</v>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="51">
         <v>0.11509022706590016</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="51">
         <v>0.12425825713940832</v>
       </c>
-      <c r="F17" s="47">
+      <c r="F17" s="48">
         <v>0.1600166311177611</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="48">
         <v>0.227334193446872</v>
       </c>
-      <c r="H17" s="49" t="s">
-        <v>183</v>
+      <c r="H17" s="50" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="46">
+      <c r="C18" s="47">
         <v>-0.12410628409779752</v>
       </c>
-      <c r="D18" s="47">
+      <c r="D18" s="48">
         <v>0.016871597240498658</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="48">
         <v>0.03238621232769336</v>
       </c>
-      <c r="F18" s="46">
+      <c r="F18" s="47">
         <v>-0.0537376600220211</v>
       </c>
-      <c r="G18" s="46">
+      <c r="G18" s="47">
         <v>-0.26899528896187336</v>
       </c>
-      <c r="H18" s="49" t="s">
-        <v>184</v>
+      <c r="H18" s="50" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="C19" s="51">
-        <v>1</v>
-      </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="49" t="s">
-        <v>186</v>
+        <v>187</v>
+      </c>
+      <c r="C19" s="52">
+        <v>3</v>
+      </c>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="50" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="C20" s="52">
+        <v>189</v>
+      </c>
+      <c r="C20" s="53">
         <v>-1.645771096258031</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="53">
         <v>0.35643157341300485</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="54">
         <v>1.0161888900715002</v>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="53">
         <v>-2.2491624522434597</v>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="53">
         <v>-14.215088395316705</v>
       </c>
-      <c r="H20" s="49" t="s">
-        <v>188</v>
+      <c r="H20" s="50" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C21" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
-      <c r="F21" s="54"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>192</v>
+      </c>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="55"/>
+      <c r="H21" s="50" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="31" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D22" s="55"/>
       <c r="E22" s="55"/>
       <c r="F22" s="55"/>
       <c r="G22" s="55"/>
-      <c r="H22" s="49" t="s">
-        <v>192</v>
+      <c r="H22" s="50" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="44" t="s">
-        <v>193</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="D24" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="E24" s="44"/>
-      <c r="F24" s="44" t="s">
+      <c r="B24" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="G24" s="44"/>
-      <c r="H24" s="44"/>
+      <c r="C24" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="56" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D25" s="58" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E25" s="58"/>
       <c r="F25" s="59" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G25" s="59"/>
       <c r="H25" s="59"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="C26" s="57" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="57" t="s">
-        <v>198</v>
-      </c>
       <c r="D26" s="58" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E26" s="58"/>
       <c r="F26" s="59" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G26" s="59"/>
       <c r="H26" s="59"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="56" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D27" s="58" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E27" s="58"/>
       <c r="F27" s="59" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G27" s="59"/>
       <c r="H27" s="59"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="56" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D28" s="58" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E28" s="58"/>
       <c r="F28" s="59" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G28" s="59"/>
       <c r="H28" s="59"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="56" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D29" s="58" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E29" s="58"/>
       <c r="F29" s="59" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G29" s="59"/>
       <c r="H29" s="59"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="56" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C30" s="60" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D30" s="58" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E30" s="58"/>
       <c r="F30" s="59" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G30" s="59"/>
       <c r="H30" s="59"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="56" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C31" s="57" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D31" s="58" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E31" s="58"/>
       <c r="F31" s="59" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="G31" s="59"/>
       <c r="H31" s="59"/>
@@ -2294,7 +2305,7 @@
         <v>39</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
@@ -2302,7 +2313,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="61" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C35" s="61"/>
       <c r="D35" s="61"/>
@@ -3560,7 +3571,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G17"/>
+  <dimension ref="B1:G20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3869,6 +3880,51 @@
       <c r="G17" s="35">
         <f>IF(G10&gt;0,G16/G10,0)</f>
         <v>-0.26899529</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="36">
+        <f>C16</f>
+        <v>-175486.28571429</v>
+      </c>
+      <c r="D19" s="36">
+        <f>C19+D16</f>
+        <v>-137480.48219048</v>
+      </c>
+      <c r="E19" s="36">
+        <f>D19+E16</f>
+        <v>-29125.67251601</v>
+      </c>
+      <c r="F19" s="36">
+        <f>E19+F16</f>
+        <v>-268950.7402971</v>
+      </c>
+      <c r="G19" s="36">
+        <f>F19+G16</f>
+        <v>-1784685.86850917</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3899,7 +3955,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -3927,7 +3983,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C4" s="30">
         <f>'5-Year P&amp;L'!C16</f>
@@ -3952,7 +4008,7 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C6" s="30">
         <f>Assumptions!D58</f>
@@ -3977,7 +4033,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C7" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4002,7 +4058,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C8" s="32">
         <f>C6+C7</f>
@@ -4027,32 +4083,32 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" s="36">
+        <v>150</v>
+      </c>
+      <c r="C10" s="38">
         <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
         <v>-1.6457711</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="38">
         <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
         <v>0.35643157</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="39">
         <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
         <v>1.01618889</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="38">
         <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
         <v>-2.24916245</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="38">
         <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
         <v>-14.2150884</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C12" s="30">
         <f>C4-C8</f>
@@ -4077,25 +4133,25 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="38">
+        <v>152</v>
+      </c>
+      <c r="C14" s="40">
         <f>Assumptions!D57+C12</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="40">
         <f>C14+D12</f>
         <v>-350737.70382146</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="40">
         <f>D14+E12</f>
         <v>-349011.50496249</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="40">
         <f>E14+F12</f>
         <v>-695465.18355908</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="40">
         <f>F14+G12</f>
         <v>-2317828.92258663</v>
       </c>
@@ -4128,7 +4184,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4156,7 +4212,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C4" s="29">
         <f>Drivers!C12</f>
@@ -4181,7 +4237,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C5" s="29">
         <f>Assumptions!D35</f>
@@ -4206,25 +4262,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="39">
+        <v>156</v>
+      </c>
+      <c r="C6" s="41">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="41">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="41">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="41">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="41">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -4257,13 +4313,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C3" s="30">
         <f>Assumptions!D59</f>
@@ -4272,7 +4328,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C4" s="35">
         <f>Assumptions!D60</f>
@@ -4290,18 +4346,18 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="40">
+        <v>160</v>
+      </c>
+      <c r="C6" s="36">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="36">
+        <v>161</v>
+      </c>
+      <c r="C8" s="38">
         <f>'Cash Flow &amp; DSCR'!C10</f>
         <v>-1.6457711</v>
       </c>
@@ -4334,7 +4390,7 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C1" s="13"/>
     </row>
@@ -4367,7 +4423,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C6" s="28">
         <f>Assumptions!D8</f>
@@ -4385,7 +4441,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C9" s="30">
         <f>Drivers!G10</f>
@@ -4394,16 +4450,16 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" s="38">
+        <v>165</v>
+      </c>
+      <c r="C10" s="40">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C12" s="12"/>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -2430,10 +2430,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="224">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -596,9 +596,6 @@
   </si>
   <si>
     <t>Break-even Year</t>
-  </si>
-  <si>
-    <t>Not reached</t>
   </si>
   <si>
     <t>Cash Runway</t>
@@ -944,7 +941,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1051,6 +1048,9 @@
     </xf>
     <xf numFmtId="167" fontId="17" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2066,7 +2066,7 @@
       <c r="F17" s="48">
         <v>0.1600166311177611</v>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="47">
         <v>0.227334193446872</v>
       </c>
       <c r="H17" s="50" t="s">
@@ -2138,196 +2138,208 @@
       <c r="B21" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="C21" s="55" t="s">
-        <v>192</v>
-      </c>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="55"/>
+      <c r="C21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!C19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!D19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!E19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!F19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="55" t="str">
+        <f>IF('5-Year P&amp;L'!G19&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="50" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="31" t="s">
+        <v>192</v>
+      </c>
+      <c r="C22" s="56" t="s">
         <v>193</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="56"/>
+      <c r="H22" s="50" t="s">
         <v>194</v>
-      </c>
-      <c r="D22" s="55"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="50" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="D24" s="45" t="s">
         <v>197</v>
-      </c>
-      <c r="D24" s="45" t="s">
-        <v>198</v>
       </c>
       <c r="E24" s="45"/>
       <c r="F24" s="45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G24" s="45"/>
       <c r="H24" s="45"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="56" t="s">
+      <c r="B25" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="D25" s="59" t="s">
         <v>201</v>
       </c>
-      <c r="D25" s="58" t="s">
+      <c r="E25" s="59"/>
+      <c r="F25" s="60" t="s">
         <v>202</v>
       </c>
-      <c r="E25" s="58"/>
-      <c r="F25" s="59" t="s">
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="57" t="s">
         <v>203</v>
       </c>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="56" t="s">
+      <c r="C26" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="D26" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D26" s="58" t="s">
+      <c r="E26" s="59"/>
+      <c r="F26" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="E26" s="58"/>
-      <c r="F26" s="59" t="s">
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="57" t="s">
         <v>206</v>
       </c>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="56" t="s">
+      <c r="C27" s="61" t="s">
         <v>207</v>
       </c>
-      <c r="C27" s="60" t="s">
+      <c r="D27" s="59" t="s">
         <v>208</v>
       </c>
-      <c r="D27" s="58" t="s">
+      <c r="E27" s="59"/>
+      <c r="F27" s="60" t="s">
         <v>209</v>
       </c>
-      <c r="E27" s="58"/>
-      <c r="F27" s="59" t="s">
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="57" t="s">
         <v>210</v>
       </c>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="56" t="s">
+      <c r="C28" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="D28" s="59" t="s">
         <v>211</v>
       </c>
-      <c r="C28" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D28" s="58" t="s">
+      <c r="E28" s="59"/>
+      <c r="F28" s="60" t="s">
         <v>212</v>
       </c>
-      <c r="E28" s="58"/>
-      <c r="F28" s="59" t="s">
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="57" t="s">
         <v>213</v>
       </c>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="56" t="s">
+      <c r="C29" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="C29" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D29" s="58" t="s">
+      <c r="E29" s="59"/>
+      <c r="F29" s="60" t="s">
         <v>215</v>
       </c>
-      <c r="E29" s="58"/>
-      <c r="F29" s="59" t="s">
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="57" t="s">
         <v>216</v>
       </c>
-      <c r="G29" s="59"/>
-      <c r="H29" s="59"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="56" t="s">
+      <c r="C30" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="D30" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="C30" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="D30" s="58" t="s">
+      <c r="E30" s="59"/>
+      <c r="F30" s="60" t="s">
         <v>218</v>
       </c>
-      <c r="E30" s="58"/>
-      <c r="F30" s="59" t="s">
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="G30" s="59"/>
-      <c r="H30" s="59"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="56" t="s">
+      <c r="C31" s="58" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="C31" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D31" s="58" t="s">
+      <c r="E31" s="59"/>
+      <c r="F31" s="60" t="s">
         <v>221</v>
       </c>
-      <c r="E31" s="58"/>
-      <c r="F31" s="59" t="s">
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="31" t="s">
         <v>222</v>
-      </c>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="56" t="s">
-        <v>39</v>
-      </c>
-      <c r="C33" s="31" t="s">
-        <v>223</v>
       </c>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
       <c r="F33" s="31"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="61" t="s">
-        <v>224</v>
-      </c>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
+      <c r="B35" s="62" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -2408,10 +2420,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="223">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -598,13 +598,10 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>0 months</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1042,7 +1039,9 @@
     <xf numFmtId="166" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1052,7 +1051,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2103,10 +2104,18 @@
       <c r="C19" s="52">
         <v>3</v>
       </c>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
+      <c r="D19" s="52">
+        <v>3</v>
+      </c>
+      <c r="E19" s="52">
+        <v>3</v>
+      </c>
+      <c r="F19" s="52">
+        <v>3</v>
+      </c>
+      <c r="G19" s="52">
+        <v>3</v>
+      </c>
       <c r="H19" s="50" t="s">
         <v>188</v>
       </c>
@@ -2143,19 +2152,19 @@
         <v>0</v>
       </c>
       <c r="D21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!D19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!D19&gt;=0,'5-Year P&amp;L'!C19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!E19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!E19&gt;=0,'5-Year P&amp;L'!D19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!F19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!F19&gt;=0,'5-Year P&amp;L'!E19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!G19&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year P&amp;L'!G19&gt;=0,'5-Year P&amp;L'!F19&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="50" t="s">
@@ -2166,149 +2175,157 @@
       <c r="B22" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="56">
+        <v>-2</v>
+      </c>
+      <c r="D22" s="56">
+        <v>-2</v>
+      </c>
+      <c r="E22" s="56">
+        <v>-1</v>
+      </c>
+      <c r="F22" s="56">
+        <v>-2</v>
+      </c>
+      <c r="G22" s="56">
+        <v>-4</v>
+      </c>
+      <c r="H22" s="50" t="s">
         <v>193</v>
-      </c>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="50" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="C24" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="D24" s="45" t="s">
         <v>196</v>
-      </c>
-      <c r="D24" s="45" t="s">
-        <v>197</v>
       </c>
       <c r="E24" s="45"/>
       <c r="F24" s="45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G24" s="45"/>
       <c r="H24" s="45"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="C25" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="D25" s="59" t="s">
         <v>200</v>
-      </c>
-      <c r="D25" s="59" t="s">
-        <v>201</v>
       </c>
       <c r="E25" s="59"/>
       <c r="F25" s="60" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G25" s="60"/>
       <c r="H25" s="60"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="57" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="59" t="s">
         <v>203</v>
-      </c>
-      <c r="C26" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="D26" s="59" t="s">
-        <v>204</v>
       </c>
       <c r="E26" s="59"/>
       <c r="F26" s="60" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G26" s="60"/>
       <c r="H26" s="60"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="C27" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="D27" s="59" t="s">
         <v>207</v>
-      </c>
-      <c r="D27" s="59" t="s">
-        <v>208</v>
       </c>
       <c r="E27" s="59"/>
       <c r="F27" s="60" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G27" s="60"/>
       <c r="H27" s="60"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="57" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D28" s="59" t="s">
         <v>210</v>
-      </c>
-      <c r="C28" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="D28" s="59" t="s">
-        <v>211</v>
       </c>
       <c r="E28" s="59"/>
       <c r="F28" s="60" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G28" s="60"/>
       <c r="H28" s="60"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" s="59" t="s">
         <v>213</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="D29" s="59" t="s">
-        <v>214</v>
       </c>
       <c r="E29" s="59"/>
       <c r="F29" s="60" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G29" s="60"/>
       <c r="H29" s="60"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="57" t="s">
+        <v>215</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="59" t="s">
         <v>216</v>
-      </c>
-      <c r="C30" s="61" t="s">
-        <v>207</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>217</v>
       </c>
       <c r="E30" s="59"/>
       <c r="F30" s="60" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G30" s="60"/>
       <c r="H30" s="60"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="C31" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="D31" s="59" t="s">
         <v>219</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="D31" s="59" t="s">
-        <v>220</v>
       </c>
       <c r="E31" s="59"/>
       <c r="F31" s="60" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G31" s="60"/>
       <c r="H31" s="60"/>
@@ -2318,7 +2335,7 @@
         <v>39</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
@@ -2326,7 +2343,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="62" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C35" s="62"/>
       <c r="D35" s="62"/>
@@ -2336,11 +2353,9 @@
       <c r="H35" s="62"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -652,10 +652,10 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 23% of revenue are high. Fixed costs this size create rigidity in your budget.</t>
-  </si>
-  <si>
-    <t>Explore shared space, renegotiate terms, or consider a smaller facility.</t>
+    <t>Facility costs at 6% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
   </si>
   <si>
     <t>Debt Affordability</t>
@@ -685,7 +685,7 @@
     <t>Prioritize building reserves — even a small surplus each year compounds into meaningful protection.</t>
   </si>
   <si>
-    <t>2 Healthy  |  0 Watch  |  5 Needs Attention</t>
+    <t>3 Healthy  |  0 Watch  |  4 Needs Attention</t>
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -2055,20 +2055,20 @@
       <c r="B17" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="C17" s="51">
-        <v>0.12814710042432814</v>
+      <c r="C17" s="47">
+        <v>0.22772277227722773</v>
       </c>
       <c r="D17" s="51">
-        <v>0.11509022706590016</v>
+        <v>0.14723103899851286</v>
       </c>
       <c r="E17" s="51">
-        <v>0.12425825713940832</v>
-      </c>
-      <c r="F17" s="48">
-        <v>0.1600166311177611</v>
-      </c>
-      <c r="G17" s="47">
-        <v>0.227334193446872</v>
+        <v>0.10210388952054393</v>
+      </c>
+      <c r="F17" s="51">
+        <v>0.07884092687353057</v>
+      </c>
+      <c r="G17" s="51">
+        <v>0.06431705180190153</v>
       </c>
       <c r="H17" s="50" t="s">
         <v>185</v>
@@ -2266,8 +2266,8 @@
       <c r="B28" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="58" t="s">
-        <v>199</v>
+      <c r="C28" s="61" t="s">
+        <v>206</v>
       </c>
       <c r="D28" s="59" t="s">
         <v>210</v>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="232">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -451,6 +451,15 @@
     <t>Operating Margin</t>
   </si>
   <si>
+    <t>Capital &amp; Debt Service</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
+  </si>
+  <si>
     <t>Cumulative Net Income</t>
   </si>
   <si>
@@ -460,6 +469,9 @@
     <t>Cash Flow &amp; Debt Service Coverage</t>
   </si>
   <si>
+    <t>Beginning Cash</t>
+  </si>
+  <si>
     <t>Net Operating Income</t>
   </si>
   <si>
@@ -478,7 +490,10 @@
     <t>Net Income After Debt</t>
   </si>
   <si>
-    <t>Cumulative Cash</t>
+    <t>Net Cash Flow</t>
+  </si>
+  <si>
+    <t>Ending Cash</t>
   </si>
   <si>
     <t>Staffing Detail</t>
@@ -520,6 +535,27 @@
     <t>Year 5 NOI</t>
   </si>
   <si>
+    <t>KEY RATIOS</t>
+  </si>
+  <si>
+    <t>Net Margin (Year 5)</t>
+  </si>
+  <si>
+    <t>Personnel % of Revenue (Year 5)</t>
+  </si>
+  <si>
+    <t>Revenue per Student (Year 5)</t>
+  </si>
+  <si>
+    <t>Expense per Student (Year 5)</t>
+  </si>
+  <si>
+    <t>DSCR (Year 1)</t>
+  </si>
+  <si>
+    <t>DSCR (Year 5)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -551,15 +587,6 @@
   </si>
   <si>
     <t>Debt Service</t>
-  </si>
-  <si>
-    <t>Net Income</t>
-  </si>
-  <si>
-    <t>Ending Cash</t>
-  </si>
-  <si>
-    <t>Net Margin</t>
   </si>
   <si>
     <t>Revenue per Student</t>
@@ -938,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1013,10 +1040,14 @@
     <xf numFmtId="167" fontId="17" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1791,7 +1822,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1812,37 +1843,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="42" t="s">
-        <v>168</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>169</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>170</v>
+      <c r="B4" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="46" t="s">
+      <c r="B6" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="46" t="s">
+      <c r="D6" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="46" t="s">
+      <c r="G6" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="46" t="s">
-        <v>172</v>
+      <c r="H6" s="48" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1867,7 +1898,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C8" s="30">
         <v>1414000</v>
@@ -1887,7 +1918,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C9" s="30">
         <v>985486.2857142857</v>
@@ -1907,7 +1938,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C10" s="30">
         <v>604000</v>
@@ -1927,7 +1958,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="C11" s="30">
         <v>106628.6108154935</v>
@@ -1947,7 +1978,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
-        <v>177</v>
+        <v>144</v>
       </c>
       <c r="C12" s="33">
         <v>-282114.8965297792</v>
@@ -1967,7 +1998,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="C13" s="33">
         <v>-282114.8965297792</v>
@@ -1987,370 +2018,370 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="C14" s="47">
+        <v>145</v>
+      </c>
+      <c r="C14" s="49">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="49">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E14" s="48">
+      <c r="E14" s="50">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="49">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="49">
         <v>-0.2879185120528036</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="C15" s="49">
+        <v>189</v>
+      </c>
+      <c r="C15" s="51">
         <v>11783.333333333334</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="51">
         <v>11263.25</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="51">
         <v>11152.36</v>
       </c>
-      <c r="F15" s="49">
+      <c r="F15" s="51">
         <v>11157.2158</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="51">
         <v>11269.603524</v>
       </c>
-      <c r="H15" s="50" t="s">
-        <v>181</v>
+      <c r="H15" s="52" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="C16" s="47">
+        <v>191</v>
+      </c>
+      <c r="C16" s="49">
         <v>0.6969492826833703</v>
       </c>
-      <c r="D16" s="48">
+      <c r="D16" s="50">
         <v>0.5994943125398341</v>
       </c>
-      <c r="E16" s="48">
+      <c r="E16" s="50">
         <v>0.5534195972076122</v>
       </c>
-      <c r="F16" s="51">
+      <c r="F16" s="53">
         <v>0.5203488896294841</v>
       </c>
-      <c r="G16" s="51">
+      <c r="G16" s="53">
         <v>0.5112146441389667</v>
       </c>
-      <c r="H16" s="50" t="s">
-        <v>183</v>
+      <c r="H16" s="52" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="C17" s="47">
+        <v>193</v>
+      </c>
+      <c r="C17" s="49">
         <v>0.22772277227722773</v>
       </c>
-      <c r="D17" s="51">
+      <c r="D17" s="53">
         <v>0.14723103899851286</v>
       </c>
-      <c r="E17" s="51">
+      <c r="E17" s="53">
         <v>0.10210388952054393</v>
       </c>
-      <c r="F17" s="51">
+      <c r="F17" s="53">
         <v>0.07884092687353057</v>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="53">
         <v>0.06431705180190153</v>
       </c>
-      <c r="H17" s="50" t="s">
-        <v>185</v>
+      <c r="H17" s="52" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="47">
+      <c r="C18" s="49">
         <v>-0.12410628409779752</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="50">
         <v>0.016871597240498658</v>
       </c>
-      <c r="E18" s="48">
+      <c r="E18" s="50">
         <v>0.03238621232769336</v>
       </c>
-      <c r="F18" s="47">
+      <c r="F18" s="49">
         <v>-0.0537376600220211</v>
       </c>
-      <c r="G18" s="47">
+      <c r="G18" s="49">
         <v>-0.26899528896187336</v>
       </c>
-      <c r="H18" s="50" t="s">
-        <v>186</v>
+      <c r="H18" s="52" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="C19" s="52">
+        <v>196</v>
+      </c>
+      <c r="C19" s="54">
         <v>3</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="54">
         <v>3</v>
       </c>
-      <c r="E19" s="52">
+      <c r="E19" s="54">
         <v>3</v>
       </c>
-      <c r="F19" s="52">
+      <c r="F19" s="54">
         <v>3</v>
       </c>
-      <c r="G19" s="52">
+      <c r="G19" s="54">
         <v>3</v>
       </c>
-      <c r="H19" s="50" t="s">
-        <v>188</v>
+      <c r="H19" s="52" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="53">
+        <v>198</v>
+      </c>
+      <c r="C20" s="55">
         <v>-1.645771096258031</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="55">
         <v>0.35643157341300485</v>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="56">
         <v>1.0161888900715002</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="55">
         <v>-2.2491624522434597</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="55">
         <v>-14.215088395316705</v>
       </c>
-      <c r="H20" s="50" t="s">
-        <v>190</v>
+      <c r="H20" s="52" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" s="55" t="str">
-        <f>IF('5-Year P&amp;L'!C19&gt;=0,"✓ Break-even","")</f>
+        <v>200</v>
+      </c>
+      <c r="C21" s="57" t="str">
+        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="55" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D19&gt;=0,'5-Year P&amp;L'!C19&lt;0),"✓ Break-even","")</f>
+      <c r="D21" s="57" t="str">
+        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="55" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E19&gt;=0,'5-Year P&amp;L'!D19&lt;0),"✓ Break-even","")</f>
+      <c r="E21" s="57" t="str">
+        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="55" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F19&gt;=0,'5-Year P&amp;L'!E19&lt;0),"✓ Break-even","")</f>
+      <c r="F21" s="57" t="str">
+        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="55" t="str">
-        <f>IF(AND('5-Year P&amp;L'!G19&gt;=0,'5-Year P&amp;L'!F19&lt;0),"✓ Break-even","")</f>
+      <c r="G21" s="57" t="str">
+        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="50" t="s">
+      <c r="H21" s="52" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="C22" s="56">
+        <v>201</v>
+      </c>
+      <c r="C22" s="58">
         <v>-2</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="58">
         <v>-2</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="58">
         <v>-1</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="58">
         <v>-2</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="58">
         <v>-4</v>
       </c>
-      <c r="H22" s="50" t="s">
-        <v>193</v>
+      <c r="H22" s="52" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="45" t="s">
-        <v>194</v>
-      </c>
-      <c r="C24" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="45" t="s">
-        <v>196</v>
-      </c>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
+      <c r="B24" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>204</v>
+      </c>
+      <c r="D24" s="47" t="s">
+        <v>205</v>
+      </c>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="57" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="D25" s="59" t="s">
-        <v>200</v>
-      </c>
-      <c r="E25" s="59"/>
-      <c r="F25" s="60" t="s">
-        <v>201</v>
-      </c>
-      <c r="G25" s="60"/>
-      <c r="H25" s="60"/>
+      <c r="B25" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D25" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="E25" s="61"/>
+      <c r="F25" s="62" t="s">
+        <v>210</v>
+      </c>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="C26" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="D26" s="59" t="s">
-        <v>203</v>
-      </c>
-      <c r="E26" s="59"/>
-      <c r="F26" s="60" t="s">
-        <v>204</v>
-      </c>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
+      <c r="B26" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="E26" s="61"/>
+      <c r="F26" s="62" t="s">
+        <v>213</v>
+      </c>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="57" t="s">
-        <v>205</v>
-      </c>
-      <c r="C27" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="D27" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="E27" s="59"/>
-      <c r="F27" s="60" t="s">
+      <c r="B27" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="C27" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="E27" s="61"/>
+      <c r="F27" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="59" t="s">
+        <v>218</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="61" t="s">
+        <v>219</v>
+      </c>
+      <c r="E28" s="61"/>
+      <c r="F28" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="59" t="s">
+        <v>221</v>
+      </c>
+      <c r="C29" s="60" t="s">
         <v>208</v>
       </c>
-      <c r="G27" s="60"/>
-      <c r="H27" s="60"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="57" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="D28" s="59" t="s">
-        <v>210</v>
-      </c>
-      <c r="E28" s="59"/>
-      <c r="F28" s="60" t="s">
-        <v>211</v>
-      </c>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="57" t="s">
-        <v>212</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="D29" s="59" t="s">
-        <v>213</v>
-      </c>
-      <c r="E29" s="59"/>
-      <c r="F29" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
+      <c r="D29" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="E29" s="61"/>
+      <c r="F29" s="62" t="s">
+        <v>223</v>
+      </c>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="57" t="s">
+      <c r="B30" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="C30" s="63" t="s">
         <v>215</v>
       </c>
-      <c r="C30" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="E30" s="59"/>
-      <c r="F30" s="60" t="s">
-        <v>217</v>
-      </c>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
+      <c r="D30" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
+        <v>226</v>
+      </c>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="C31" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="D31" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="E31" s="59"/>
-      <c r="F31" s="60" t="s">
-        <v>220</v>
-      </c>
-      <c r="G31" s="60"/>
-      <c r="H31" s="60"/>
+      <c r="B31" s="59" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>228</v>
+      </c>
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
+        <v>229</v>
+      </c>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="57" t="s">
+      <c r="B33" s="59" t="s">
         <v>39</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D33" s="31"/>
       <c r="E33" s="31"/>
       <c r="F33" s="31"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="62" t="s">
-        <v>222</v>
-      </c>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="62"/>
-      <c r="G35" s="62"/>
-      <c r="H35" s="62"/>
+      <c r="B35" s="64" t="s">
+        <v>231</v>
+      </c>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="64"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3598,7 +3629,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G20"/>
+  <dimension ref="B1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3910,47 +3941,122 @@
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="C19" s="36">
-        <f>C16</f>
-        <v>-175486.28571429</v>
-      </c>
-      <c r="D19" s="36">
-        <f>C19+D16</f>
-        <v>-137480.48219048</v>
-      </c>
-      <c r="E19" s="36">
-        <f>D19+E16</f>
-        <v>-29125.67251601</v>
-      </c>
-      <c r="F19" s="36">
-        <f>E19+F16</f>
-        <v>-268950.7402971</v>
-      </c>
-      <c r="G19" s="36">
-        <f>F19+G16</f>
-        <v>-1784685.86850917</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="31" t="s">
+      <c r="C19" s="30">
+        <f>'Cash Flow &amp; DSCR'!C9</f>
+        <v>106628.61081549</v>
+      </c>
+      <c r="D19" s="30">
+        <f>'Cash Flow &amp; DSCR'!D9</f>
+        <v>106628.61081549</v>
+      </c>
+      <c r="E19" s="30">
+        <f>'Cash Flow &amp; DSCR'!E9</f>
+        <v>106628.61081549</v>
+      </c>
+      <c r="F19" s="30">
+        <f>'Cash Flow &amp; DSCR'!F9</f>
+        <v>106628.61081549</v>
+      </c>
+      <c r="G19" s="30">
+        <f>'Cash Flow &amp; DSCR'!G9</f>
+        <v>106628.61081549</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C21" s="33">
+        <f>C16-C19</f>
+        <v>-282114.89652978</v>
+      </c>
+      <c r="D21" s="33">
+        <f>D16-D19</f>
+        <v>-68622.80729168</v>
+      </c>
+      <c r="E21" s="34">
+        <f>E16-E19</f>
+        <v>1726.19885897</v>
+      </c>
+      <c r="F21" s="33">
+        <f>F16-F19</f>
+        <v>-346453.67859658</v>
+      </c>
+      <c r="G21" s="33">
+        <f>G16-G19</f>
+        <v>-1622363.73902756</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="35">
+        <f>IF(C10&gt;0,C21/C10,0)</f>
+        <v>-0.19951549</v>
+      </c>
+      <c r="D22" s="35">
+        <f>IF(D10&gt;0,D21/D10,0)</f>
+        <v>-0.03046315</v>
+      </c>
+      <c r="E22" s="35">
+        <f>IF(E10&gt;0,E21/E10,0)</f>
+        <v>0.00051594</v>
+      </c>
+      <c r="F22" s="35">
+        <f>IF(F10&gt;0,F21/F10,0)</f>
+        <v>-0.07762996</v>
+      </c>
+      <c r="G22" s="35">
+        <f>IF(G10&gt;0,G21/G10,0)</f>
+        <v>-0.28791851</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="36">
+        <f>C21</f>
+        <v>-282114.89652978</v>
+      </c>
+      <c r="D24" s="36">
+        <f>C24+D21</f>
+        <v>-350737.70382146</v>
+      </c>
+      <c r="E24" s="36">
+        <f>D24+E21</f>
+        <v>-349011.50496249</v>
+      </c>
+      <c r="F24" s="36">
+        <f>E24+F21</f>
+        <v>-695465.18355908</v>
+      </c>
+      <c r="G24" s="36">
+        <f>F24+G21</f>
+        <v>-2317828.92258663</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="37" t="s">
+      <c r="D25" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E25" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="37" t="s">
+      <c r="F25" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G20" s="37" t="s">
+      <c r="G25" s="37" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3972,7 +4078,7 @@
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G14"/>
+  <dimension ref="B1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3982,7 +4088,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4009,177 +4115,227 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="30">
+      <c r="B4" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4" s="36" t="str">
+        <f>Assumptions!D57</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="36">
+        <f>C16</f>
+        <v>-282114.89652978</v>
+      </c>
+      <c r="E4" s="36">
+        <f>D16</f>
+        <v>-350737.70382146</v>
+      </c>
+      <c r="F4" s="36">
+        <f>E16</f>
+        <v>-349011.50496249</v>
+      </c>
+      <c r="G4" s="36">
+        <f>F16</f>
+        <v>-695465.18355908</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" s="30">
         <f>'5-Year P&amp;L'!C16</f>
         <v>-175486.28571429</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D5" s="30">
         <f>'5-Year P&amp;L'!D16</f>
         <v>38005.80352381</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E5" s="30">
         <f>'5-Year P&amp;L'!E16</f>
         <v>108354.80967446</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F5" s="30">
         <f>'5-Year P&amp;L'!F16</f>
         <v>-239825.06778109</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G5" s="30">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="30">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D7" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E7" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F7" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G7" s="30">
         <f>Assumptions!D58</f>
         <v>60000</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="30">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D8" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E8" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F8" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G8" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
         <v>46628.61081549</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="32">
-        <f>C6+C7</f>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="32">
+        <f>C7+C8</f>
         <v>106628.61081549</v>
       </c>
-      <c r="D8" s="32">
-        <f>D6+D7</f>
+      <c r="D9" s="32">
+        <f>D7+D8</f>
         <v>106628.61081549</v>
       </c>
-      <c r="E8" s="32">
-        <f>E6+E7</f>
+      <c r="E9" s="32">
+        <f>E7+E8</f>
         <v>106628.61081549</v>
       </c>
-      <c r="F8" s="32">
-        <f>F6+F7</f>
+      <c r="F9" s="32">
+        <f>F7+F8</f>
         <v>106628.61081549</v>
       </c>
-      <c r="G8" s="32">
-        <f>G6+G7</f>
+      <c r="G9" s="32">
+        <f>G7+G8</f>
         <v>106628.61081549</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="38">
-        <f>IF(C8&gt;0,C4/C8,IF(C4&gt;0,99.9,0))</f>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="38">
+        <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
         <v>-1.6457711</v>
       </c>
-      <c r="D10" s="38">
-        <f>IF(D8&gt;0,D4/D8,IF(D4&gt;0,99.9,0))</f>
+      <c r="D11" s="38">
+        <f>IF(D9&gt;0,D5/D9,IF(D5&gt;0,99.9,0))</f>
         <v>0.35643157</v>
       </c>
-      <c r="E10" s="39">
-        <f>IF(E8&gt;0,E4/E8,IF(E4&gt;0,99.9,0))</f>
+      <c r="E11" s="39">
+        <f>IF(E9&gt;0,E5/E9,IF(E5&gt;0,99.9,0))</f>
         <v>1.01618889</v>
       </c>
-      <c r="F10" s="38">
-        <f>IF(F8&gt;0,F4/F8,IF(F4&gt;0,99.9,0))</f>
+      <c r="F11" s="38">
+        <f>IF(F9&gt;0,F5/F9,IF(F5&gt;0,99.9,0))</f>
         <v>-2.24916245</v>
       </c>
-      <c r="G10" s="38">
-        <f>IF(G8&gt;0,G4/G8,IF(G4&gt;0,99.9,0))</f>
+      <c r="G11" s="38">
+        <f>IF(G9&gt;0,G5/G9,IF(G5&gt;0,99.9,0))</f>
         <v>-14.2150884</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="30">
-        <f>C4-C8</f>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="30">
+        <f>C5-C9</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D12" s="30">
-        <f>D4-D8</f>
+      <c r="D13" s="30">
+        <f>D5-D9</f>
         <v>-68622.80729168</v>
       </c>
-      <c r="E12" s="30">
-        <f>E4-E8</f>
+      <c r="E13" s="30">
+        <f>E5-E9</f>
         <v>1726.19885897</v>
       </c>
-      <c r="F12" s="30">
-        <f>F4-F8</f>
+      <c r="F13" s="30">
+        <f>F5-F9</f>
         <v>-346453.67859658</v>
       </c>
-      <c r="G12" s="30">
-        <f>G4-G8</f>
+      <c r="G13" s="30">
+        <f>G5-G9</f>
         <v>-1622363.73902756</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" s="40">
-        <f>Assumptions!D57+C12</f>
+        <v>156</v>
+      </c>
+      <c r="C14" s="36">
+        <f>C5-C9</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D14" s="40">
-        <f>C14+D12</f>
+      <c r="D14" s="36">
+        <f>D5-D9</f>
+        <v>-68622.80729168</v>
+      </c>
+      <c r="E14" s="36">
+        <f>E5-E9</f>
+        <v>1726.19885897</v>
+      </c>
+      <c r="F14" s="36">
+        <f>F5-F9</f>
+        <v>-346453.67859658</v>
+      </c>
+      <c r="G14" s="36">
+        <f>G5-G9</f>
+        <v>-1622363.73902756</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="33">
+        <f>C4+C14</f>
+        <v>-282114.89652978</v>
+      </c>
+      <c r="D16" s="33">
+        <f>D4+D14</f>
         <v>-350737.70382146</v>
       </c>
-      <c r="E14" s="40">
-        <f>D14+E12</f>
+      <c r="E16" s="33">
+        <f>E4+E14</f>
         <v>-349011.50496249</v>
       </c>
-      <c r="F14" s="40">
-        <f>E14+F12</f>
+      <c r="F16" s="33">
+        <f>F4+F14</f>
         <v>-695465.18355908</v>
       </c>
-      <c r="G14" s="40">
-        <f>F14+G12</f>
+      <c r="G16" s="33">
+        <f>G4+G14</f>
         <v>-2317828.92258663</v>
       </c>
     </row>
@@ -4211,7 +4367,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4239,7 +4395,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C4" s="29">
         <f>Drivers!C12</f>
@@ -4264,7 +4420,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C5" s="29">
         <f>Assumptions!D35</f>
@@ -4289,25 +4445,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="41">
+        <v>161</v>
+      </c>
+      <c r="C6" s="40">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="40">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="40">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="40">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="40">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -4340,13 +4496,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="28" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C3" s="30">
         <f>Assumptions!D59</f>
@@ -4355,7 +4511,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C4" s="35">
         <f>Assumptions!D60</f>
@@ -4373,7 +4529,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C6" s="36">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4382,10 +4538,10 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C8" s="38">
-        <f>'Cash Flow &amp; DSCR'!C10</f>
+        <f>'Cash Flow &amp; DSCR'!C11</f>
         <v>-1.6457711</v>
       </c>
     </row>
@@ -4407,7 +4563,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C12"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4417,7 +4573,7 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C1" s="13"/>
     </row>
@@ -4450,7 +4606,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C6" s="28">
         <f>Assumptions!D8</f>
@@ -4468,7 +4624,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C9" s="30">
         <f>Drivers!G10</f>
@@ -4477,23 +4633,83 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="40">
+        <v>170</v>
+      </c>
+      <c r="C10" s="41">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="12"/>
+    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="26"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="43">
+        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
+        <v>-0.28791851</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" s="35">
+        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
+        <v>0.51121464</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="30">
+        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
+        <v>11270</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="30">
+        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
+        <v>14301</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="38">
+        <f>'Cash Flow &amp; DSCR'!C11</f>
+        <v>-1.6457711</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="38">
+        <f>'Cash Flow &amp; DSCR'!G11</f>
+        <v>-14.2150884</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -28,7 +28,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+    <t>Generated March 27, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -142,7 +142,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -2620,7 +2620,7 @@
     <tabColor rgb="FFD97706"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:E78"/>
+  <dimension ref="B1:E77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -3028,32 +3028,40 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B64" s="17" t="s">
+    <row r="63" ht="24" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B63" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C65" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C66" s="18" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C67" s="18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="D67" s="20">
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C68" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D68" s="20">
         <v>0</v>
@@ -3061,71 +3069,63 @@
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C69" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D69" s="20">
-        <v>0</v>
+        <v>102</v>
+      </c>
+      <c r="D69" s="23">
+        <v>0.95</v>
       </c>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C70" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D70" s="23">
-        <v>0.95</v>
+        <v>103</v>
+      </c>
+      <c r="D70" s="21">
+        <v>8200</v>
       </c>
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C71" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D71" s="21">
-        <v>8200</v>
+        <v>9100</v>
       </c>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C72" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D72" s="21">
-        <v>9100</v>
-      </c>
-    </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C73" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D73" s="21">
         <v>10500</v>
       </c>
     </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C74" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D74" s="24"/>
+    </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C75" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D75" s="24"/>
+      <c r="C75" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D75" s="25" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C76" s="18" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C77" s="18" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D77" s="25" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C78" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D78" s="25" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3138,8 +3138,8 @@
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="C74:D74"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="235">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -556,6 +556,9 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
+    <t>Days Cash on Hand (Year 1)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -629,6 +632,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -965,7 +974,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1048,6 +1057,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1810,7 +1822,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1822,7 +1834,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1843,37 +1855,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="45" t="s">
+      <c r="B4" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="D4" s="46" t="s">
         <v>182</v>
       </c>
+      <c r="F4" s="47" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="48" t="s">
-        <v>184</v>
+      <c r="H6" s="49" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1898,7 +1910,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C8" s="30">
         <v>1414000</v>
@@ -1918,7 +1930,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C9" s="30">
         <v>985486.2857142857</v>
@@ -1938,7 +1950,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C10" s="30">
         <v>604000</v>
@@ -1958,7 +1970,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C11" s="30">
         <v>106628.6108154935</v>
@@ -2020,375 +2032,396 @@
       <c r="B14" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="50">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="50">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="51">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="50">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="50">
         <v>-0.2879185120528036</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="51">
+        <v>190</v>
+      </c>
+      <c r="C15" s="52">
         <v>11783.333333333334</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="52">
         <v>11263.25</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="52">
         <v>11152.36</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="52">
         <v>11157.2158</v>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="52">
         <v>11269.603524</v>
       </c>
-      <c r="H15" s="52" t="s">
-        <v>190</v>
+      <c r="H15" s="53" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="49">
+        <v>192</v>
+      </c>
+      <c r="C16" s="50">
         <v>0.6969492826833703</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="51">
         <v>0.5994943125398341</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="51">
         <v>0.5534195972076122</v>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="54">
         <v>0.5203488896294841</v>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="54">
         <v>0.5112146441389667</v>
       </c>
-      <c r="H16" s="52" t="s">
-        <v>192</v>
+      <c r="H16" s="53" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="C17" s="49">
+        <v>194</v>
+      </c>
+      <c r="C17" s="50">
         <v>0.22772277227722773</v>
       </c>
-      <c r="D17" s="53">
+      <c r="D17" s="54">
         <v>0.14723103899851286</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="54">
         <v>0.10210388952054393</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="54">
         <v>0.07884092687353057</v>
       </c>
-      <c r="G17" s="53">
+      <c r="G17" s="54">
         <v>0.06431705180190153</v>
       </c>
-      <c r="H17" s="52" t="s">
-        <v>194</v>
+      <c r="H17" s="53" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="49">
+      <c r="C18" s="50">
         <v>-0.12410628409779752</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="51">
         <v>0.016871597240498658</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="51">
         <v>0.03238621232769336</v>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="50">
         <v>-0.0537376600220211</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="50">
         <v>-0.26899528896187336</v>
       </c>
-      <c r="H18" s="52" t="s">
-        <v>195</v>
+      <c r="H18" s="53" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="C19" s="54">
+        <v>197</v>
+      </c>
+      <c r="C19" s="55">
         <v>3</v>
       </c>
-      <c r="D19" s="54">
+      <c r="D19" s="55">
         <v>3</v>
       </c>
-      <c r="E19" s="54">
+      <c r="E19" s="55">
         <v>3</v>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="55">
         <v>3</v>
       </c>
-      <c r="G19" s="54">
+      <c r="G19" s="55">
         <v>3</v>
       </c>
-      <c r="H19" s="52" t="s">
-        <v>197</v>
+      <c r="H19" s="53" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="C20" s="55">
+        <v>199</v>
+      </c>
+      <c r="C20" s="56">
         <v>-1.645771096258031</v>
       </c>
-      <c r="D20" s="55">
+      <c r="D20" s="56">
         <v>0.35643157341300485</v>
       </c>
-      <c r="E20" s="56">
+      <c r="E20" s="57">
         <v>1.0161888900715002</v>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="56">
         <v>-2.2491624522434597</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="56">
         <v>-14.215088395316705</v>
       </c>
-      <c r="H20" s="52" t="s">
-        <v>199</v>
+      <c r="H20" s="53" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="C21" s="57" t="str">
+        <v>201</v>
+      </c>
+      <c r="C21" s="58" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="57" t="str">
+      <c r="D21" s="58" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="57" t="str">
+      <c r="E21" s="58" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="57" t="str">
+      <c r="F21" s="58" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="57" t="str">
+      <c r="G21" s="58" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="52" t="s">
+      <c r="H21" s="53" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="C22" s="58">
+        <v>202</v>
+      </c>
+      <c r="C22" s="59">
         <v>-2</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="59">
         <v>-2</v>
       </c>
-      <c r="E22" s="58">
+      <c r="E22" s="59">
         <v>-1</v>
       </c>
-      <c r="F22" s="58">
+      <c r="F22" s="59">
         <v>-2</v>
       </c>
-      <c r="G22" s="58">
+      <c r="G22" s="59">
         <v>-4</v>
       </c>
-      <c r="H22" s="52" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="47" t="s">
+      <c r="H22" s="53" t="s">
         <v>203</v>
       </c>
-      <c r="C24" s="47" t="s">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="C23" s="59">
+        <v>0</v>
+      </c>
+      <c r="D23" s="59">
+        <v>0</v>
+      </c>
+      <c r="E23" s="59">
+        <v>0</v>
+      </c>
+      <c r="F23" s="59">
+        <v>0</v>
+      </c>
+      <c r="G23" s="59">
+        <v>0</v>
+      </c>
+      <c r="H23" s="53" t="s">
         <v>205</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="59" t="s">
+      <c r="C25" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="D25" s="48" t="s">
         <v>208</v>
       </c>
-      <c r="D25" s="61" t="s">
+      <c r="E25" s="48"/>
+      <c r="F25" s="48" t="s">
         <v>209</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62" t="s">
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="60" t="s">
         <v>210</v>
       </c>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="59" t="s">
+      <c r="C26" s="61" t="s">
         <v>211</v>
       </c>
-      <c r="C26" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="D26" s="61" t="s">
+      <c r="D26" s="62" t="s">
         <v>212</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62" t="s">
+      <c r="E26" s="62"/>
+      <c r="F26" s="63" t="s">
         <v>213</v>
       </c>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="59" t="s">
+      <c r="B27" s="60" t="s">
         <v>214</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="61" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="E27" s="62"/>
+      <c r="F27" s="63" t="s">
         <v>216</v>
       </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62" t="s">
+      <c r="G27" s="63"/>
+      <c r="H27" s="63"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="59" t="s">
+      <c r="C28" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="C28" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="62" t="s">
         <v>219</v>
       </c>
-      <c r="E28" s="61"/>
-      <c r="F28" s="62" t="s">
+      <c r="E28" s="62"/>
+      <c r="F28" s="63" t="s">
         <v>220</v>
       </c>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
+      <c r="G28" s="63"/>
+      <c r="H28" s="63"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="59" t="s">
+      <c r="B29" s="60" t="s">
         <v>221</v>
       </c>
-      <c r="C29" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="D29" s="61" t="s">
+      <c r="C29" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="D29" s="62" t="s">
         <v>222</v>
       </c>
-      <c r="E29" s="61"/>
-      <c r="F29" s="62" t="s">
+      <c r="E29" s="62"/>
+      <c r="F29" s="63" t="s">
         <v>223</v>
       </c>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="60" t="s">
         <v>224</v>
       </c>
-      <c r="C30" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="D30" s="61" t="s">
+      <c r="C30" s="61" t="s">
+        <v>211</v>
+      </c>
+      <c r="D30" s="62" t="s">
         <v>225</v>
       </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
+      <c r="E30" s="62"/>
+      <c r="F30" s="63" t="s">
         <v>226</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="60" t="s">
         <v>227</v>
       </c>
-      <c r="C31" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="D31" s="61" t="s">
+      <c r="C31" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="D31" s="62" t="s">
         <v>228</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="s">
+      <c r="E31" s="62"/>
+      <c r="F31" s="63" t="s">
         <v>229</v>
       </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="59" t="s">
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="60" t="s">
+        <v>230</v>
+      </c>
+      <c r="C32" s="61" t="s">
+        <v>211</v>
+      </c>
+      <c r="D32" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="E32" s="62"/>
+      <c r="F32" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="64" t="s">
-        <v>231</v>
-      </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+      <c r="C34" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="65" t="s">
+        <v>234</v>
+      </c>
+      <c r="C36" s="65"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65"/>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -2403,8 +2436,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -4563,7 +4598,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C20"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4700,16 +4735,24 @@
         <v>-14.2150884</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C19" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="240">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -596,6 +596,21 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -974,7 +989,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1079,6 +1094,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1822,7 +1843,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2071,365 +2092,440 @@
         <v>191</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="C16" s="50">
-        <v>0.6969492826833703</v>
-      </c>
-      <c r="D16" s="51">
-        <v>0.5994943125398341</v>
-      </c>
-      <c r="E16" s="51">
-        <v>0.5534195972076122</v>
-      </c>
-      <c r="F16" s="54">
-        <v>0.5203488896294841</v>
-      </c>
-      <c r="G16" s="54">
-        <v>0.5112146441389667</v>
-      </c>
-      <c r="H16" s="53" t="s">
+      <c r="C16" s="36">
+        <v>14134.290804414828</v>
+      </c>
+      <c r="D16" s="36">
+        <v>11606.36403645842</v>
+      </c>
+      <c r="E16" s="36">
+        <v>11146.606003803437</v>
+      </c>
+      <c r="F16" s="36">
+        <v>12023.349996491457</v>
+      </c>
+      <c r="G16" s="36">
+        <v>14514.331002055113</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="31" t="s">
+      <c r="C17" s="30">
+        <v>650</v>
+      </c>
+      <c r="D17" s="30">
+        <v>1116.6666666666667</v>
+      </c>
+      <c r="E17" s="30">
+        <v>1918.3760683760688</v>
+      </c>
+      <c r="F17" s="30">
+        <v>3295.671707210169</v>
+      </c>
+      <c r="G17" s="30">
+        <v>5661.794984181573</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="C17" s="50">
-        <v>0.22772277227722773</v>
-      </c>
-      <c r="D17" s="54">
-        <v>0.14723103899851286</v>
-      </c>
-      <c r="E17" s="54">
-        <v>0.10210388952054393</v>
-      </c>
-      <c r="F17" s="54">
-        <v>0.07884092687353057</v>
-      </c>
-      <c r="G17" s="54">
-        <v>0.06431705180190153</v>
-      </c>
-      <c r="H17" s="53" t="s">
+      <c r="C18" s="54">
+        <v>2683.3333333333335</v>
+      </c>
+      <c r="D18" s="52">
+        <v>1658.3</v>
+      </c>
+      <c r="E18" s="52">
+        <v>1138.6993333333332</v>
+      </c>
+      <c r="F18" s="52">
+        <v>879.645235</v>
+      </c>
+      <c r="G18" s="52">
+        <v>724.8276736400001</v>
+      </c>
+      <c r="H18" s="53" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" s="50">
-        <v>-0.12410628409779752</v>
-      </c>
-      <c r="D18" s="51">
-        <v>0.016871597240498658</v>
-      </c>
-      <c r="E18" s="51">
-        <v>0.03238621232769336</v>
-      </c>
-      <c r="F18" s="50">
-        <v>-0.0537376600220211</v>
-      </c>
-      <c r="G18" s="50">
-        <v>-0.26899528896187336</v>
-      </c>
-      <c r="H18" s="53" t="s">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="31" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="C19" s="55">
-        <v>3</v>
-      </c>
-      <c r="D19" s="55">
-        <v>3</v>
+      <c r="C19" s="41">
+        <v>-2350.957471081493</v>
+      </c>
+      <c r="D19" s="41">
+        <v>-343.1140364584216</v>
       </c>
       <c r="E19" s="55">
-        <v>3</v>
-      </c>
-      <c r="F19" s="55">
-        <v>3</v>
-      </c>
-      <c r="G19" s="55">
-        <v>3</v>
-      </c>
-      <c r="H19" s="53" t="s">
-        <v>198</v>
+        <v>5.753996196562657</v>
+      </c>
+      <c r="F19" s="41">
+        <v>-866.1341964914559</v>
+      </c>
+      <c r="G19" s="41">
+        <v>-3244.727478055112</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="C20" s="56">
-        <v>-1.645771096258031</v>
-      </c>
-      <c r="D20" s="56">
-        <v>0.35643157341300485</v>
-      </c>
-      <c r="E20" s="57">
-        <v>1.0161888900715002</v>
+        <v>197</v>
+      </c>
+      <c r="C20" s="50">
+        <v>0.6969492826833703</v>
+      </c>
+      <c r="D20" s="51">
+        <v>0.5994943125398341</v>
+      </c>
+      <c r="E20" s="51">
+        <v>0.5534195972076122</v>
       </c>
       <c r="F20" s="56">
-        <v>-2.2491624522434597</v>
+        <v>0.5203488896294841</v>
       </c>
       <c r="G20" s="56">
-        <v>-14.215088395316705</v>
+        <v>0.5112146441389667</v>
       </c>
       <c r="H20" s="53" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="C21" s="50">
+        <v>0.22772277227722773</v>
+      </c>
+      <c r="D21" s="56">
+        <v>0.14723103899851286</v>
+      </c>
+      <c r="E21" s="56">
+        <v>0.10210388952054393</v>
+      </c>
+      <c r="F21" s="56">
+        <v>0.07884092687353057</v>
+      </c>
+      <c r="G21" s="56">
+        <v>0.06431705180190153</v>
+      </c>
+      <c r="H21" s="53" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="50">
+        <v>-0.12410628409779752</v>
+      </c>
+      <c r="D22" s="51">
+        <v>0.016871597240498658</v>
+      </c>
+      <c r="E22" s="51">
+        <v>0.03238621232769336</v>
+      </c>
+      <c r="F22" s="50">
+        <v>-0.0537376600220211</v>
+      </c>
+      <c r="G22" s="50">
+        <v>-0.26899528896187336</v>
+      </c>
+      <c r="H22" s="53" t="s">
         <v>201</v>
       </c>
-      <c r="C21" s="58" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="57">
+        <v>3</v>
+      </c>
+      <c r="D23" s="57">
+        <v>3</v>
+      </c>
+      <c r="E23" s="57">
+        <v>3</v>
+      </c>
+      <c r="F23" s="57">
+        <v>3</v>
+      </c>
+      <c r="G23" s="57">
+        <v>3</v>
+      </c>
+      <c r="H23" s="53" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="58">
+        <v>-1.645771096258031</v>
+      </c>
+      <c r="D24" s="58">
+        <v>0.35643157341300485</v>
+      </c>
+      <c r="E24" s="59">
+        <v>1.0161888900715002</v>
+      </c>
+      <c r="F24" s="58">
+        <v>-2.2491624522434597</v>
+      </c>
+      <c r="G24" s="58">
+        <v>-14.215088395316705</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C25" s="60" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="58" t="str">
+      <c r="D25" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="58" t="str">
+      <c r="E25" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="58" t="str">
+      <c r="F25" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="58" t="str">
+      <c r="G25" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="53" t="s">
+      <c r="H25" s="53" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="C22" s="59">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="C26" s="61">
         <v>-2</v>
       </c>
-      <c r="D22" s="59">
+      <c r="D26" s="61">
         <v>-2</v>
       </c>
-      <c r="E22" s="59">
+      <c r="E26" s="61">
         <v>-1</v>
       </c>
-      <c r="F22" s="59">
+      <c r="F26" s="61">
         <v>-2</v>
       </c>
-      <c r="G22" s="59">
+      <c r="G26" s="61">
         <v>-4</v>
       </c>
-      <c r="H22" s="53" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="C23" s="59">
+      <c r="H26" s="53" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="C27" s="61">
         <v>0</v>
       </c>
-      <c r="D23" s="59">
+      <c r="D27" s="61">
         <v>0</v>
       </c>
-      <c r="E23" s="59">
+      <c r="E27" s="61">
         <v>0</v>
       </c>
-      <c r="F23" s="59">
+      <c r="F27" s="61">
         <v>0</v>
       </c>
-      <c r="G23" s="59">
+      <c r="G27" s="61">
         <v>0</v>
       </c>
-      <c r="H23" s="53" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>207</v>
-      </c>
-      <c r="D25" s="48" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48" t="s">
-        <v>209</v>
-      </c>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="60" t="s">
+      <c r="H27" s="53" t="s">
         <v>210</v>
       </c>
-      <c r="C26" s="61" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="D26" s="62" t="s">
+      <c r="C29" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63" t="s">
+      <c r="D29" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="60" t="s">
+      <c r="E29" s="48"/>
+      <c r="F29" s="48" t="s">
         <v>214</v>
       </c>
-      <c r="C27" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="D27" s="62" t="s">
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63" t="s">
+      <c r="C30" s="63" t="s">
         <v>216</v>
       </c>
-      <c r="G27" s="63"/>
-      <c r="H27" s="63"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="60" t="s">
+      <c r="D30" s="64" t="s">
         <v>217</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="E30" s="64"/>
+      <c r="F30" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="D28" s="62" t="s">
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="62" t="s">
         <v>219</v>
       </c>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63" t="s">
+      <c r="C31" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" s="64" t="s">
         <v>220</v>
       </c>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="60" t="s">
+      <c r="E31" s="64"/>
+      <c r="F31" s="65" t="s">
         <v>221</v>
       </c>
-      <c r="C29" s="64" t="s">
-        <v>218</v>
-      </c>
-      <c r="D29" s="62" t="s">
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="62" t="s">
         <v>222</v>
       </c>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63" t="s">
+      <c r="C32" s="66" t="s">
         <v>223</v>
       </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="60" t="s">
+      <c r="D32" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="C30" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="D30" s="62" t="s">
+      <c r="E32" s="64"/>
+      <c r="F32" s="65" t="s">
         <v>225</v>
       </c>
-      <c r="E30" s="62"/>
-      <c r="F30" s="63" t="s">
+      <c r="G32" s="65"/>
+      <c r="H32" s="65"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="62" t="s">
         <v>226</v>
       </c>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="60" t="s">
+      <c r="C33" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="D33" s="64" t="s">
         <v>227</v>
       </c>
-      <c r="C31" s="64" t="s">
-        <v>218</v>
-      </c>
-      <c r="D31" s="62" t="s">
+      <c r="E33" s="64"/>
+      <c r="F33" s="65" t="s">
         <v>228</v>
       </c>
-      <c r="E31" s="62"/>
-      <c r="F31" s="63" t="s">
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="62" t="s">
         <v>229</v>
       </c>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="60" t="s">
+      <c r="C34" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="C32" s="61" t="s">
-        <v>211</v>
-      </c>
-      <c r="D32" s="62" t="s">
+      <c r="E34" s="64"/>
+      <c r="F34" s="65" t="s">
         <v>231</v>
       </c>
-      <c r="E32" s="62"/>
-      <c r="F32" s="63" t="s">
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="62" t="s">
         <v>232</v>
       </c>
-      <c r="G32" s="63"/>
-      <c r="H32" s="63"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="31" t="s">
+      <c r="C35" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="D35" s="64" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="65" t="s">
+      <c r="E35" s="64"/>
+      <c r="F35" s="65" t="s">
         <v>234</v>
       </c>
-      <c r="C36" s="65"/>
-      <c r="D36" s="65"/>
-      <c r="E36" s="65"/>
-      <c r="F36" s="65"/>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" s="64" t="s">
+        <v>236</v>
+      </c>
+      <c r="E36" s="64"/>
+      <c r="F36" s="65" t="s">
+        <v>237</v>
+      </c>
       <c r="G36" s="65"/>
       <c r="H36" s="65"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -2438,8 +2534,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2485,48 +2589,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="232">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -556,9 +556,6 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
-    <t>Days Cash on Hand (Year 1)</t>
-  </si>
-  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -598,21 +595,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t>Cost per Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -647,12 +629,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>Days Cash on Hand</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -989,7 +965,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1074,9 +1050,6 @@
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1094,12 +1067,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="166" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1843,7 +1810,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1855,7 +1822,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1876,37 +1843,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="F4" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="F4" s="47" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="47" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="48" t="s">
+      <c r="C6" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="48" t="s">
         <v>184</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="E6" s="49" t="s">
-        <v>116</v>
-      </c>
-      <c r="F6" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="G6" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="H6" s="49" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1931,7 +1898,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C8" s="30">
         <v>1414000</v>
@@ -1951,7 +1918,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C9" s="30">
         <v>985486.2857142857</v>
@@ -1971,7 +1938,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C10" s="30">
         <v>604000</v>
@@ -1991,7 +1958,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C11" s="30">
         <v>106628.6108154935</v>
@@ -2053,497 +2020,391 @@
       <c r="B14" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="50">
+      <c r="C14" s="49">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="49">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="50">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="49">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="49">
         <v>-0.2879185120528036</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" s="51">
+        <v>11783.333333333334</v>
+      </c>
+      <c r="D15" s="51">
+        <v>11263.25</v>
+      </c>
+      <c r="E15" s="51">
+        <v>11152.36</v>
+      </c>
+      <c r="F15" s="51">
+        <v>11157.2158</v>
+      </c>
+      <c r="G15" s="51">
+        <v>11269.603524</v>
+      </c>
+      <c r="H15" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="C15" s="52">
-        <v>11783.333333333334</v>
-      </c>
-      <c r="D15" s="52">
-        <v>11263.25</v>
-      </c>
-      <c r="E15" s="52">
-        <v>11152.36</v>
-      </c>
-      <c r="F15" s="52">
-        <v>11157.2158</v>
-      </c>
-      <c r="G15" s="52">
-        <v>11269.603524</v>
-      </c>
-      <c r="H15" s="53" t="s">
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="31" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="31" t="s">
+      <c r="C16" s="49">
+        <v>0.6969492826833703</v>
+      </c>
+      <c r="D16" s="50">
+        <v>0.5994943125398341</v>
+      </c>
+      <c r="E16" s="50">
+        <v>0.5534195972076122</v>
+      </c>
+      <c r="F16" s="53">
+        <v>0.5203488896294841</v>
+      </c>
+      <c r="G16" s="53">
+        <v>0.5112146441389667</v>
+      </c>
+      <c r="H16" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="C16" s="36">
-        <v>14134.290804414828</v>
-      </c>
-      <c r="D16" s="36">
-        <v>11606.36403645842</v>
-      </c>
-      <c r="E16" s="36">
-        <v>11146.606003803437</v>
-      </c>
-      <c r="F16" s="36">
-        <v>12023.349996491457</v>
-      </c>
-      <c r="G16" s="36">
-        <v>14514.331002055113</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="C17" s="30">
-        <v>650</v>
-      </c>
-      <c r="D17" s="30">
-        <v>1116.6666666666667</v>
-      </c>
-      <c r="E17" s="30">
-        <v>1918.3760683760688</v>
-      </c>
-      <c r="F17" s="30">
-        <v>3295.671707210169</v>
-      </c>
-      <c r="G17" s="30">
-        <v>5661.794984181573</v>
+      <c r="C17" s="49">
+        <v>0.22772277227722773</v>
+      </c>
+      <c r="D17" s="53">
+        <v>0.14723103899851286</v>
+      </c>
+      <c r="E17" s="53">
+        <v>0.10210388952054393</v>
+      </c>
+      <c r="F17" s="53">
+        <v>0.07884092687353057</v>
+      </c>
+      <c r="G17" s="53">
+        <v>0.06431705180190153</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="C18" s="54">
-        <v>2683.3333333333335</v>
-      </c>
-      <c r="D18" s="52">
-        <v>1658.3</v>
-      </c>
-      <c r="E18" s="52">
-        <v>1138.6993333333332</v>
-      </c>
-      <c r="F18" s="52">
-        <v>879.645235</v>
-      </c>
-      <c r="G18" s="52">
-        <v>724.8276736400001</v>
-      </c>
-      <c r="H18" s="53" t="s">
+      <c r="B18" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="49">
+        <v>-0.12410628409779752</v>
+      </c>
+      <c r="D18" s="50">
+        <v>0.016871597240498658</v>
+      </c>
+      <c r="E18" s="50">
+        <v>0.03238621232769336</v>
+      </c>
+      <c r="F18" s="49">
+        <v>-0.0537376600220211</v>
+      </c>
+      <c r="G18" s="49">
+        <v>-0.26899528896187336</v>
+      </c>
+      <c r="H18" s="52" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="41">
-        <v>-2350.957471081493</v>
-      </c>
-      <c r="D19" s="41">
-        <v>-343.1140364584216</v>
-      </c>
-      <c r="E19" s="55">
-        <v>5.753996196562657</v>
-      </c>
-      <c r="F19" s="41">
-        <v>-866.1341964914559</v>
-      </c>
-      <c r="G19" s="41">
-        <v>-3244.727478055112</v>
+      <c r="C19" s="54">
+        <v>3</v>
+      </c>
+      <c r="D19" s="54">
+        <v>3</v>
+      </c>
+      <c r="E19" s="54">
+        <v>3</v>
+      </c>
+      <c r="F19" s="54">
+        <v>3</v>
+      </c>
+      <c r="G19" s="54">
+        <v>3</v>
+      </c>
+      <c r="H19" s="52" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" s="50">
-        <v>0.6969492826833703</v>
-      </c>
-      <c r="D20" s="51">
-        <v>0.5994943125398341</v>
-      </c>
-      <c r="E20" s="51">
-        <v>0.5534195972076122</v>
-      </c>
-      <c r="F20" s="56">
-        <v>0.5203488896294841</v>
-      </c>
-      <c r="G20" s="56">
-        <v>0.5112146441389667</v>
-      </c>
-      <c r="H20" s="53" t="s">
         <v>198</v>
+      </c>
+      <c r="C20" s="55">
+        <v>-1.645771096258031</v>
+      </c>
+      <c r="D20" s="55">
+        <v>0.35643157341300485</v>
+      </c>
+      <c r="E20" s="56">
+        <v>1.0161888900715002</v>
+      </c>
+      <c r="F20" s="55">
+        <v>-2.2491624522434597</v>
+      </c>
+      <c r="G20" s="55">
+        <v>-14.215088395316705</v>
+      </c>
+      <c r="H20" s="52" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="C21" s="50">
-        <v>0.22772277227722773</v>
-      </c>
-      <c r="D21" s="56">
-        <v>0.14723103899851286</v>
-      </c>
-      <c r="E21" s="56">
-        <v>0.10210388952054393</v>
-      </c>
-      <c r="F21" s="56">
-        <v>0.07884092687353057</v>
-      </c>
-      <c r="G21" s="56">
-        <v>0.06431705180190153</v>
-      </c>
-      <c r="H21" s="53" t="s">
         <v>200</v>
+      </c>
+      <c r="C21" s="57" t="str">
+        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="57" t="str">
+        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="57" t="str">
+        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="57" t="str">
+        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="57" t="str">
+        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" s="50">
-        <v>-0.12410628409779752</v>
-      </c>
-      <c r="D22" s="51">
-        <v>0.016871597240498658</v>
-      </c>
-      <c r="E22" s="51">
-        <v>0.03238621232769336</v>
-      </c>
-      <c r="F22" s="50">
-        <v>-0.0537376600220211</v>
-      </c>
-      <c r="G22" s="50">
-        <v>-0.26899528896187336</v>
-      </c>
-      <c r="H22" s="53" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="31" t="s">
+      <c r="C22" s="58">
+        <v>-2</v>
+      </c>
+      <c r="D22" s="58">
+        <v>-2</v>
+      </c>
+      <c r="E22" s="58">
+        <v>-1</v>
+      </c>
+      <c r="F22" s="58">
+        <v>-2</v>
+      </c>
+      <c r="G22" s="58">
+        <v>-4</v>
+      </c>
+      <c r="H22" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="C23" s="57">
-        <v>3</v>
-      </c>
-      <c r="D23" s="57">
-        <v>3</v>
-      </c>
-      <c r="E23" s="57">
-        <v>3</v>
-      </c>
-      <c r="F23" s="57">
-        <v>3</v>
-      </c>
-      <c r="G23" s="57">
-        <v>3</v>
-      </c>
-      <c r="H23" s="53" t="s">
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="47" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="31" t="s">
+      <c r="C24" s="47" t="s">
         <v>204</v>
       </c>
-      <c r="C24" s="58">
-        <v>-1.645771096258031</v>
-      </c>
-      <c r="D24" s="58">
-        <v>0.35643157341300485</v>
-      </c>
-      <c r="E24" s="59">
-        <v>1.0161888900715002</v>
-      </c>
-      <c r="F24" s="58">
-        <v>-2.2491624522434597</v>
-      </c>
-      <c r="G24" s="58">
-        <v>-14.215088395316705</v>
-      </c>
-      <c r="H24" s="53" t="s">
+      <c r="D24" s="47" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="31" t="s">
+      <c r="E24" s="47"/>
+      <c r="F24" s="47" t="s">
         <v>206</v>
       </c>
-      <c r="C25" s="60" t="str">
-        <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="60" t="str">
-        <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="60" t="str">
-        <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="60" t="str">
-        <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="60" t="str">
-        <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="53" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="31" t="s">
+      <c r="G24" s="47"/>
+      <c r="H24" s="47"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="59" t="s">
         <v>207</v>
       </c>
-      <c r="C26" s="61">
-        <v>-2</v>
-      </c>
-      <c r="D26" s="61">
-        <v>-2</v>
-      </c>
-      <c r="E26" s="61">
-        <v>-1</v>
-      </c>
-      <c r="F26" s="61">
-        <v>-2</v>
-      </c>
-      <c r="G26" s="61">
-        <v>-4</v>
-      </c>
-      <c r="H26" s="53" t="s">
+      <c r="C25" s="60" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="31" t="s">
+      <c r="D25" s="61" t="s">
         <v>209</v>
       </c>
-      <c r="C27" s="61">
-        <v>0</v>
-      </c>
-      <c r="D27" s="61">
-        <v>0</v>
-      </c>
-      <c r="E27" s="61">
-        <v>0</v>
-      </c>
-      <c r="F27" s="61">
-        <v>0</v>
-      </c>
-      <c r="G27" s="61">
-        <v>0</v>
-      </c>
-      <c r="H27" s="53" t="s">
+      <c r="E25" s="61"/>
+      <c r="F25" s="62" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="48" t="s">
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="59" t="s">
         <v>211</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C26" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D26" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="E26" s="61"/>
+      <c r="F26" s="62" t="s">
         <v>213</v>
       </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48" t="s">
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
+      <c r="C27" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" s="61" t="s">
+        <v>216</v>
+      </c>
+      <c r="E27" s="61"/>
+      <c r="F27" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="59" t="s">
+        <v>218</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="61" t="s">
+        <v>219</v>
+      </c>
+      <c r="E28" s="61"/>
+      <c r="F28" s="62" t="s">
+        <v>220</v>
+      </c>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="59" t="s">
+        <v>221</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="E29" s="61"/>
+      <c r="F29" s="62" t="s">
+        <v>223</v>
+      </c>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="62" t="s">
+      <c r="B30" s="59" t="s">
+        <v>224</v>
+      </c>
+      <c r="C30" s="63" t="s">
         <v>215</v>
       </c>
-      <c r="C30" s="63" t="s">
-        <v>216</v>
-      </c>
-      <c r="D30" s="64" t="s">
-        <v>217</v>
-      </c>
-      <c r="E30" s="64"/>
-      <c r="F30" s="65" t="s">
-        <v>218</v>
-      </c>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
+      <c r="D30" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="E30" s="61"/>
+      <c r="F30" s="62" t="s">
+        <v>226</v>
+      </c>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="62" t="s">
-        <v>219</v>
-      </c>
-      <c r="C31" s="63" t="s">
-        <v>216</v>
-      </c>
-      <c r="D31" s="64" t="s">
-        <v>220</v>
-      </c>
-      <c r="E31" s="64"/>
-      <c r="F31" s="65" t="s">
-        <v>221</v>
-      </c>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="62" t="s">
-        <v>222</v>
-      </c>
-      <c r="C32" s="66" t="s">
-        <v>223</v>
-      </c>
-      <c r="D32" s="64" t="s">
-        <v>224</v>
-      </c>
-      <c r="E32" s="64"/>
-      <c r="F32" s="65" t="s">
-        <v>225</v>
-      </c>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="62" t="s">
-        <v>226</v>
-      </c>
-      <c r="C33" s="66" t="s">
-        <v>223</v>
-      </c>
-      <c r="D33" s="64" t="s">
+      <c r="B31" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="E33" s="64"/>
-      <c r="F33" s="65" t="s">
+      <c r="C31" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="D31" s="61" t="s">
         <v>228</v>
       </c>
-      <c r="G33" s="65"/>
-      <c r="H33" s="65"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="62" t="s">
+      <c r="E31" s="61"/>
+      <c r="F31" s="62" t="s">
         <v>229</v>
       </c>
-      <c r="C34" s="63" t="s">
-        <v>216</v>
-      </c>
-      <c r="D34" s="64" t="s">
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="E34" s="64"/>
-      <c r="F34" s="65" t="s">
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="62" t="s">
-        <v>232</v>
-      </c>
-      <c r="C35" s="66" t="s">
-        <v>223</v>
-      </c>
-      <c r="D35" s="64" t="s">
-        <v>233</v>
-      </c>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
       <c r="E35" s="64"/>
-      <c r="F35" s="65" t="s">
-        <v>234</v>
-      </c>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="62" t="s">
-        <v>235</v>
-      </c>
-      <c r="C36" s="63" t="s">
-        <v>216</v>
-      </c>
-      <c r="D36" s="64" t="s">
-        <v>236</v>
-      </c>
-      <c r="E36" s="64"/>
-      <c r="F36" s="65" t="s">
-        <v>237</v>
-      </c>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="62" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2589,48 +2450,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4702,7 +4563,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C21"/>
+  <dimension ref="B1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4839,24 +4700,16 @@
         <v>-14.2150884</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C19" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="C21" s="12"/>
+      <c r="C20" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="240">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -556,6 +556,9 @@
     <t>DSCR (Year 5)</t>
   </si>
   <si>
+    <t>Days Cash on Hand (Year 1)</t>
+  </si>
+  <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -595,6 +598,21 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t>Cost per Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -629,6 +647,12 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>Days Cash on Hand</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -965,7 +989,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1050,6 +1074,9 @@
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1067,6 +1094,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="17" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1810,7 +1843,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1822,7 +1855,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1843,37 +1876,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="45" t="s">
+      <c r="B4" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="D4" s="46" t="s">
         <v>182</v>
       </c>
+      <c r="F4" s="47" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="47" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="48" t="s">
+      <c r="B6" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="48" t="s">
-        <v>184</v>
+      <c r="H6" s="49" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1898,7 +1931,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C8" s="30">
         <v>1414000</v>
@@ -1918,7 +1951,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C9" s="30">
         <v>985486.2857142857</v>
@@ -1938,7 +1971,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C10" s="30">
         <v>604000</v>
@@ -1958,7 +1991,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C11" s="30">
         <v>106628.6108154935</v>
@@ -2020,391 +2053,497 @@
       <c r="B14" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="49">
+      <c r="C14" s="50">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D14" s="49">
+      <c r="D14" s="50">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="51">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="50">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="50">
         <v>-0.2879185120528036</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="51">
+        <v>190</v>
+      </c>
+      <c r="C15" s="52">
         <v>11783.333333333334</v>
       </c>
-      <c r="D15" s="51">
+      <c r="D15" s="52">
         <v>11263.25</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="52">
         <v>11152.36</v>
       </c>
-      <c r="F15" s="51">
+      <c r="F15" s="52">
         <v>11157.2158</v>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="52">
         <v>11269.603524</v>
       </c>
-      <c r="H15" s="52" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H15" s="53" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="49">
-        <v>0.6969492826833703</v>
-      </c>
-      <c r="D16" s="50">
-        <v>0.5994943125398341</v>
-      </c>
-      <c r="E16" s="50">
-        <v>0.5534195972076122</v>
-      </c>
-      <c r="F16" s="53">
-        <v>0.5203488896294841</v>
-      </c>
-      <c r="G16" s="53">
-        <v>0.5112146441389667</v>
-      </c>
-      <c r="H16" s="52" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="31" t="s">
+      <c r="C16" s="36">
+        <v>14134.290804414828</v>
+      </c>
+      <c r="D16" s="36">
+        <v>11606.36403645842</v>
+      </c>
+      <c r="E16" s="36">
+        <v>11146.606003803437</v>
+      </c>
+      <c r="F16" s="36">
+        <v>12023.349996491457</v>
+      </c>
+      <c r="G16" s="36">
+        <v>14514.331002055113</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="C17" s="49">
-        <v>0.22772277227722773</v>
-      </c>
-      <c r="D17" s="53">
-        <v>0.14723103899851286</v>
-      </c>
-      <c r="E17" s="53">
-        <v>0.10210388952054393</v>
-      </c>
-      <c r="F17" s="53">
-        <v>0.07884092687353057</v>
-      </c>
-      <c r="G17" s="53">
-        <v>0.06431705180190153</v>
-      </c>
-      <c r="H17" s="52" t="s">
+      <c r="C17" s="30">
+        <v>650</v>
+      </c>
+      <c r="D17" s="30">
+        <v>1116.6666666666667</v>
+      </c>
+      <c r="E17" s="30">
+        <v>1918.3760683760688</v>
+      </c>
+      <c r="F17" s="30">
+        <v>3295.671707210169</v>
+      </c>
+      <c r="G17" s="30">
+        <v>5661.794984181573</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="28" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="C18" s="49">
-        <v>-0.12410628409779752</v>
-      </c>
-      <c r="D18" s="50">
-        <v>0.016871597240498658</v>
-      </c>
-      <c r="E18" s="50">
-        <v>0.03238621232769336</v>
-      </c>
-      <c r="F18" s="49">
-        <v>-0.0537376600220211</v>
-      </c>
-      <c r="G18" s="49">
-        <v>-0.26899528896187336</v>
-      </c>
-      <c r="H18" s="52" t="s">
+      <c r="C18" s="54">
+        <v>2683.3333333333335</v>
+      </c>
+      <c r="D18" s="52">
+        <v>1658.3</v>
+      </c>
+      <c r="E18" s="52">
+        <v>1138.6993333333332</v>
+      </c>
+      <c r="F18" s="52">
+        <v>879.645235</v>
+      </c>
+      <c r="G18" s="52">
+        <v>724.8276736400001</v>
+      </c>
+      <c r="H18" s="53" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C19" s="54">
-        <v>3</v>
-      </c>
-      <c r="D19" s="54">
-        <v>3</v>
-      </c>
-      <c r="E19" s="54">
-        <v>3</v>
-      </c>
-      <c r="F19" s="54">
-        <v>3</v>
-      </c>
-      <c r="G19" s="54">
-        <v>3</v>
-      </c>
-      <c r="H19" s="52" t="s">
-        <v>197</v>
+      <c r="C19" s="41">
+        <v>-2350.957471081493</v>
+      </c>
+      <c r="D19" s="41">
+        <v>-343.1140364584216</v>
+      </c>
+      <c r="E19" s="55">
+        <v>5.753996196562657</v>
+      </c>
+      <c r="F19" s="41">
+        <v>-866.1341964914559</v>
+      </c>
+      <c r="G19" s="41">
+        <v>-3244.727478055112</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="C20" s="50">
+        <v>0.6969492826833703</v>
+      </c>
+      <c r="D20" s="51">
+        <v>0.5994943125398341</v>
+      </c>
+      <c r="E20" s="51">
+        <v>0.5534195972076122</v>
+      </c>
+      <c r="F20" s="56">
+        <v>0.5203488896294841</v>
+      </c>
+      <c r="G20" s="56">
+        <v>0.5112146441389667</v>
+      </c>
+      <c r="H20" s="53" t="s">
         <v>198</v>
-      </c>
-      <c r="C20" s="55">
-        <v>-1.645771096258031</v>
-      </c>
-      <c r="D20" s="55">
-        <v>0.35643157341300485</v>
-      </c>
-      <c r="E20" s="56">
-        <v>1.0161888900715002</v>
-      </c>
-      <c r="F20" s="55">
-        <v>-2.2491624522434597</v>
-      </c>
-      <c r="G20" s="55">
-        <v>-14.215088395316705</v>
-      </c>
-      <c r="H20" s="52" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="31" t="s">
+        <v>199</v>
+      </c>
+      <c r="C21" s="50">
+        <v>0.22772277227722773</v>
+      </c>
+      <c r="D21" s="56">
+        <v>0.14723103899851286</v>
+      </c>
+      <c r="E21" s="56">
+        <v>0.10210388952054393</v>
+      </c>
+      <c r="F21" s="56">
+        <v>0.07884092687353057</v>
+      </c>
+      <c r="G21" s="56">
+        <v>0.06431705180190153</v>
+      </c>
+      <c r="H21" s="53" t="s">
         <v>200</v>
       </c>
-      <c r="C21" s="57" t="str">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="50">
+        <v>-0.12410628409779752</v>
+      </c>
+      <c r="D22" s="51">
+        <v>0.016871597240498658</v>
+      </c>
+      <c r="E22" s="51">
+        <v>0.03238621232769336</v>
+      </c>
+      <c r="F22" s="50">
+        <v>-0.0537376600220211</v>
+      </c>
+      <c r="G22" s="50">
+        <v>-0.26899528896187336</v>
+      </c>
+      <c r="H22" s="53" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="57">
+        <v>3</v>
+      </c>
+      <c r="D23" s="57">
+        <v>3</v>
+      </c>
+      <c r="E23" s="57">
+        <v>3</v>
+      </c>
+      <c r="F23" s="57">
+        <v>3</v>
+      </c>
+      <c r="G23" s="57">
+        <v>3</v>
+      </c>
+      <c r="H23" s="53" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="31" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="58">
+        <v>-1.645771096258031</v>
+      </c>
+      <c r="D24" s="58">
+        <v>0.35643157341300485</v>
+      </c>
+      <c r="E24" s="59">
+        <v>1.0161888900715002</v>
+      </c>
+      <c r="F24" s="58">
+        <v>-2.2491624522434597</v>
+      </c>
+      <c r="G24" s="58">
+        <v>-14.215088395316705</v>
+      </c>
+      <c r="H24" s="53" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="31" t="s">
+        <v>206</v>
+      </c>
+      <c r="C25" s="60" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D21" s="57" t="str">
+      <c r="D25" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="57" t="str">
+      <c r="E25" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="57" t="str">
+      <c r="F25" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="57" t="str">
+      <c r="G25" s="60" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="52" t="s">
+      <c r="H25" s="53" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="C22" s="58">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="C26" s="61">
         <v>-2</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D26" s="61">
         <v>-2</v>
       </c>
-      <c r="E22" s="58">
+      <c r="E26" s="61">
         <v>-1</v>
       </c>
-      <c r="F22" s="58">
+      <c r="F26" s="61">
         <v>-2</v>
       </c>
-      <c r="G22" s="58">
+      <c r="G26" s="61">
         <v>-4</v>
       </c>
-      <c r="H22" s="52" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="47" t="s">
-        <v>203</v>
-      </c>
-      <c r="C24" s="47" t="s">
-        <v>204</v>
-      </c>
-      <c r="D24" s="47" t="s">
-        <v>205</v>
-      </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="C25" s="60" t="s">
+      <c r="H26" s="53" t="s">
         <v>208</v>
       </c>
-      <c r="D25" s="61" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62" t="s">
+      <c r="C27" s="61">
+        <v>0</v>
+      </c>
+      <c r="D27" s="61">
+        <v>0</v>
+      </c>
+      <c r="E27" s="61">
+        <v>0</v>
+      </c>
+      <c r="F27" s="61">
+        <v>0</v>
+      </c>
+      <c r="G27" s="61">
+        <v>0</v>
+      </c>
+      <c r="H27" s="53" t="s">
         <v>210</v>
       </c>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="59" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="C26" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="D26" s="61" t="s">
+      <c r="C29" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62" t="s">
+      <c r="D29" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="59" t="s">
+      <c r="E29" s="48"/>
+      <c r="F29" s="48" t="s">
         <v>214</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="C30" s="63" t="s">
         <v>216</v>
       </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62" t="s">
+      <c r="D30" s="64" t="s">
         <v>217</v>
       </c>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="59" t="s">
+      <c r="E30" s="64"/>
+      <c r="F30" s="65" t="s">
         <v>218</v>
       </c>
-      <c r="C28" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" s="61" t="s">
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="62" t="s">
         <v>219</v>
       </c>
-      <c r="E28" s="61"/>
-      <c r="F28" s="62" t="s">
+      <c r="C31" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" s="64" t="s">
         <v>220</v>
       </c>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="59" t="s">
+      <c r="E31" s="64"/>
+      <c r="F31" s="65" t="s">
         <v>221</v>
       </c>
-      <c r="C29" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="D29" s="61" t="s">
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="62" t="s">
         <v>222</v>
       </c>
-      <c r="E29" s="61"/>
-      <c r="F29" s="62" t="s">
+      <c r="C32" s="66" t="s">
         <v>223</v>
       </c>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="59" t="s">
+      <c r="D32" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="C30" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="D30" s="61" t="s">
+      <c r="E32" s="64"/>
+      <c r="F32" s="65" t="s">
         <v>225</v>
       </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="62" t="s">
+      <c r="G32" s="65"/>
+      <c r="H32" s="65"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="62" t="s">
         <v>226</v>
       </c>
-      <c r="G30" s="62"/>
-      <c r="H30" s="62"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="59" t="s">
+      <c r="C33" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="D33" s="64" t="s">
         <v>227</v>
       </c>
-      <c r="C31" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="D31" s="61" t="s">
+      <c r="E33" s="64"/>
+      <c r="F33" s="65" t="s">
         <v>228</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="62" t="s">
+      <c r="G33" s="65"/>
+      <c r="H33" s="65"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="62" t="s">
         <v>229</v>
       </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="59" t="s">
+      <c r="C34" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" s="64" t="s">
+        <v>230</v>
+      </c>
+      <c r="E34" s="64"/>
+      <c r="F34" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="G34" s="65"/>
+      <c r="H34" s="65"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="62" t="s">
+        <v>232</v>
+      </c>
+      <c r="C35" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="D35" s="64" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" s="64"/>
+      <c r="F35" s="65" t="s">
+        <v>234</v>
+      </c>
+      <c r="G35" s="65"/>
+      <c r="H35" s="65"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="62" t="s">
+        <v>235</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="D36" s="64" t="s">
+        <v>236</v>
+      </c>
+      <c r="E36" s="64"/>
+      <c r="F36" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="G36" s="65"/>
+      <c r="H36" s="65"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="64" t="s">
-        <v>231</v>
-      </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="64"/>
+      <c r="C38" s="31" t="s">
+        <v>238</v>
+      </c>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2450,48 +2589,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4563,7 +4702,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:C20"/>
+  <dimension ref="B1:C21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4700,16 +4839,24 @@
         <v>-14.2150884</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="C20" s="12"/>
+      <c r="C19" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -13,14 +13,15 @@
     <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Financial Health" state="visible" r:id="rId13"/>
+    <sheet sheetId="10" name="Decision History" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="243">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -28,7 +29,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · nonprofit_501c3</t>
+    <t>Generated April 29, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -142,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -562,6 +563,15 @@
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
+  </si>
+  <si>
     <t>Heritage Academy Charter — Financial Health Dashboard</t>
   </si>
   <si>
@@ -682,7 +692,7 @@
     <t>Liquidity</t>
   </si>
   <si>
-    <t>Cash goes negative in month 0. The school will need outside funding to continue operating.</t>
+    <t>Cash goes negative in month 1. The school will need outside funding to continue operating.</t>
   </si>
   <si>
     <t>Secure a line of credit or bridge funding before operations begin.</t>
@@ -712,7 +722,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of -14.22x means operating income does not cover debt payments. This must be resolved.</t>
+    <t>DSCR of -14.22x is below the 1.15x amber threshold. Any shortfall in revenue makes debt unaffordable.</t>
   </si>
   <si>
     <t>Reduce loan amounts, extend terms, or increase revenue before committing to this debt.</t>
@@ -911,12 +921,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
+        <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EDF2"/>
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1061,9 +1071,6 @@
     <xf numFmtId="167" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1077,24 +1084,30 @@
     <xf numFmtId="3" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="17" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1107,9 +1120,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="17" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="17" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1843,6 +1853,72 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1855,7 +1931,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1876,37 +1952,37 @@
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="D4" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>183</v>
+      <c r="B4" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>185</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="C6" s="49" t="s">
+      <c r="B6" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="F6" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="49" t="s">
+      <c r="G6" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="49" t="s">
-        <v>185</v>
+      <c r="H6" s="50" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -1931,7 +2007,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C8" s="30">
         <v>1414000</v>
@@ -1951,7 +2027,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C9" s="30">
         <v>985486.2857142857</v>
@@ -1971,7 +2047,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C10" s="30">
         <v>604000</v>
@@ -1991,7 +2067,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C11" s="30">
         <v>106628.6108154935</v>
@@ -2053,48 +2129,48 @@
       <c r="B14" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="50">
+      <c r="C14" s="51">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D14" s="50">
+      <c r="D14" s="51">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="52">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="51">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="51">
         <v>-0.2879185120528036</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="C15" s="52">
+        <v>193</v>
+      </c>
+      <c r="C15" s="53">
         <v>11783.333333333334</v>
       </c>
-      <c r="D15" s="52">
+      <c r="D15" s="53">
         <v>11263.25</v>
       </c>
-      <c r="E15" s="52">
+      <c r="E15" s="53">
         <v>11152.36</v>
       </c>
-      <c r="F15" s="52">
+      <c r="F15" s="53">
         <v>11157.2158</v>
       </c>
-      <c r="G15" s="52">
+      <c r="G15" s="53">
         <v>11269.603524</v>
       </c>
-      <c r="H15" s="53" t="s">
-        <v>191</v>
+      <c r="H15" s="54" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="31" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C16" s="36">
         <v>14134.290804414828</v>
@@ -2114,7 +2190,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C17" s="30">
         <v>650</v>
@@ -2134,165 +2210,165 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="C18" s="54">
+        <v>197</v>
+      </c>
+      <c r="C18" s="55">
         <v>2683.3333333333335</v>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="53">
         <v>1658.3</v>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="53">
         <v>1138.6993333333332</v>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="53">
         <v>879.645235</v>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="53">
         <v>724.8276736400001</v>
       </c>
-      <c r="H18" s="53" t="s">
-        <v>195</v>
+      <c r="H18" s="54" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="C19" s="41">
+        <v>199</v>
+      </c>
+      <c r="C19" s="40">
         <v>-2350.957471081493</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="40">
         <v>-343.1140364584216</v>
       </c>
-      <c r="E19" s="55">
+      <c r="E19" s="56">
         <v>5.753996196562657</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="40">
         <v>-866.1341964914559</v>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="40">
         <v>-3244.727478055112</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="C20" s="50">
+        <v>200</v>
+      </c>
+      <c r="C20" s="51">
         <v>0.6969492826833703</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="52">
         <v>0.5994943125398341</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="52">
         <v>0.5534195972076122</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="57">
         <v>0.5203488896294841</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="57">
         <v>0.5112146441389667</v>
       </c>
-      <c r="H20" s="53" t="s">
-        <v>198</v>
+      <c r="H20" s="54" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="C21" s="50">
+        <v>202</v>
+      </c>
+      <c r="C21" s="51">
         <v>0.22772277227722773</v>
       </c>
-      <c r="D21" s="56">
+      <c r="D21" s="57">
         <v>0.14723103899851286</v>
       </c>
-      <c r="E21" s="56">
+      <c r="E21" s="57">
         <v>0.10210388952054393</v>
       </c>
-      <c r="F21" s="56">
+      <c r="F21" s="57">
         <v>0.07884092687353057</v>
       </c>
-      <c r="G21" s="56">
+      <c r="G21" s="57">
         <v>0.06431705180190153</v>
       </c>
-      <c r="H21" s="53" t="s">
-        <v>200</v>
+      <c r="H21" s="54" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="50">
+      <c r="C22" s="51">
         <v>-0.12410628409779752</v>
       </c>
-      <c r="D22" s="51">
+      <c r="D22" s="52">
         <v>0.016871597240498658</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="52">
         <v>0.03238621232769336</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="51">
         <v>-0.0537376600220211</v>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="51">
         <v>-0.26899528896187336</v>
       </c>
-      <c r="H22" s="53" t="s">
-        <v>201</v>
+      <c r="H22" s="54" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="C23" s="57">
+        <v>205</v>
+      </c>
+      <c r="C23" s="58">
         <v>3</v>
       </c>
-      <c r="D23" s="57">
+      <c r="D23" s="58">
         <v>3</v>
       </c>
-      <c r="E23" s="57">
+      <c r="E23" s="58">
         <v>3</v>
       </c>
-      <c r="F23" s="57">
+      <c r="F23" s="58">
         <v>3</v>
       </c>
-      <c r="G23" s="57">
+      <c r="G23" s="58">
         <v>3</v>
       </c>
-      <c r="H23" s="53" t="s">
-        <v>203</v>
+      <c r="H23" s="54" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="C24" s="58">
+        <v>207</v>
+      </c>
+      <c r="C24" s="59">
         <v>-1.645771096258031</v>
       </c>
-      <c r="D24" s="58">
+      <c r="D24" s="59">
         <v>0.35643157341300485</v>
       </c>
       <c r="E24" s="59">
         <v>1.0161888900715002</v>
       </c>
-      <c r="F24" s="58">
+      <c r="F24" s="59">
         <v>-2.2491624522434597</v>
       </c>
-      <c r="G24" s="58">
+      <c r="G24" s="59">
         <v>-14.215088395316705</v>
       </c>
-      <c r="H24" s="53" t="s">
-        <v>205</v>
+      <c r="H24" s="54" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="31" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C25" s="60" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
@@ -2314,13 +2390,13 @@
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="54" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="31" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C26" s="61">
         <v>-2</v>
@@ -2337,13 +2413,13 @@
       <c r="G26" s="61">
         <v>-4</v>
       </c>
-      <c r="H26" s="53" t="s">
-        <v>208</v>
+      <c r="H26" s="54" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="31" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C27" s="61">
         <v>0</v>
@@ -2360,142 +2436,142 @@
       <c r="G27" s="61">
         <v>0</v>
       </c>
-      <c r="H27" s="53" t="s">
-        <v>210</v>
+      <c r="H27" s="54" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="48" t="s">
-        <v>211</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>212</v>
-      </c>
-      <c r="D29" s="48" t="s">
-        <v>213</v>
-      </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48" t="s">
+      <c r="B29" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
+      <c r="C29" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="D29" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="62" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C30" s="63" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E30" s="64"/>
       <c r="F30" s="65" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G30" s="65"/>
       <c r="H30" s="65"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="62" t="s">
+        <v>222</v>
+      </c>
+      <c r="C31" s="63" t="s">
         <v>219</v>
       </c>
-      <c r="C31" s="63" t="s">
-        <v>216</v>
-      </c>
       <c r="D31" s="64" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E31" s="64"/>
       <c r="F31" s="65" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G31" s="65"/>
       <c r="H31" s="65"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="62" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C32" s="66" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D32" s="64" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E32" s="64"/>
       <c r="F32" s="65" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="G32" s="65"/>
       <c r="H32" s="65"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="62" t="s">
+        <v>229</v>
+      </c>
+      <c r="C33" s="66" t="s">
         <v>226</v>
       </c>
-      <c r="C33" s="66" t="s">
-        <v>223</v>
-      </c>
       <c r="D33" s="64" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E33" s="64"/>
       <c r="F33" s="65" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="G33" s="65"/>
       <c r="H33" s="65"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="62" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C34" s="63" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D34" s="64" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E34" s="64"/>
       <c r="F34" s="65" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G34" s="65"/>
       <c r="H34" s="65"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="62" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C35" s="66" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D35" s="64" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E35" s="64"/>
       <c r="F35" s="65" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="G35" s="65"/>
       <c r="H35" s="65"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="62" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C36" s="63" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D36" s="64" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E36" s="64"/>
       <c r="F36" s="65" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="G36" s="65"/>
       <c r="H36" s="65"/>
@@ -2505,7 +2581,7 @@
         <v>39</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D38" s="31"/>
       <c r="E38" s="31"/>
@@ -2513,7 +2589,7 @@
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="67" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C40" s="67"/>
       <c r="D40" s="67"/>
@@ -2627,10 +2703,10 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4390,7 +4466,7 @@
         <f>IF(D9&gt;0,D5/D9,IF(D5&gt;0,99.9,0))</f>
         <v>0.35643157</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="38">
         <f>IF(E9&gt;0,E5/E9,IF(E5&gt;0,99.9,0))</f>
         <v>1.01618889</v>
       </c>
@@ -4586,23 +4662,23 @@
       <c r="B6" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="39">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="39">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="39">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="39">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="39">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -4774,13 +4850,13 @@
       <c r="B10" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="40">
         <f>'5-Year P&amp;L'!G16</f>
         <v>-1515735.12821206</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="41" t="s">
         <v>171</v>
       </c>
       <c r="C12" s="26"/>
@@ -4789,7 +4865,7 @@
       <c r="B13" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="42">
         <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
         <v>-0.28791851</v>
       </c>
@@ -4843,7 +4919,7 @@
       <c r="B19" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="C19" s="44">
+      <c r="C19" s="43">
         <v>0</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -29,7 +29,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · nonprofit_501c3</t>
+    <t>Generated May 1, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -29,7 +29,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · nonprofit_501c3</t>
+    <t>Generated May 7, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -1919,7 +1919,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -1929,7 +1929,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>183</v>
       </c>
@@ -1939,8 +1939,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>40</v>
       </c>
@@ -1950,6 +1951,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="46" t="s">
@@ -2440,7 +2442,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="49" t="s">
         <v>214</v>
       </c>
@@ -2456,8 +2458,9 @@
       </c>
       <c r="G29" s="49"/>
       <c r="H29" s="49"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="49"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="62" t="s">
         <v>218</v>
       </c>
@@ -2473,8 +2476,9 @@
       </c>
       <c r="G30" s="65"/>
       <c r="H30" s="65"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="65"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="62" t="s">
         <v>222</v>
       </c>
@@ -2490,8 +2494,9 @@
       </c>
       <c r="G31" s="65"/>
       <c r="H31" s="65"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="65"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="62" t="s">
         <v>225</v>
       </c>
@@ -2507,8 +2512,9 @@
       </c>
       <c r="G32" s="65"/>
       <c r="H32" s="65"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="65"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="62" t="s">
         <v>229</v>
       </c>
@@ -2524,8 +2530,9 @@
       </c>
       <c r="G33" s="65"/>
       <c r="H33" s="65"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="65"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="62" t="s">
         <v>232</v>
       </c>
@@ -2541,8 +2548,9 @@
       </c>
       <c r="G34" s="65"/>
       <c r="H34" s="65"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="65"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="62" t="s">
         <v>235</v>
       </c>
@@ -2558,8 +2566,9 @@
       </c>
       <c r="G35" s="65"/>
       <c r="H35" s="65"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="65"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="62" t="s">
         <v>238</v>
       </c>
@@ -2575,6 +2584,7 @@
       </c>
       <c r="G36" s="65"/>
       <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="62" t="s">
@@ -2587,7 +2597,7 @@
       <c r="E38" s="31"/>
       <c r="F38" s="31"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="67" t="s">
         <v>242</v>
       </c>
@@ -2597,29 +2607,30 @@
       <c r="F40" s="67"/>
       <c r="G40" s="67"/>
       <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -3011,7 +3022,7 @@
         <v>65</v>
       </c>
       <c r="D26" s="22">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Charter_ADA_Grade-Band.xlsx
@@ -10,18 +10,20 @@
     <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Cash Flow &amp; DSCR" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Decision History" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
+    <sheet sheetId="7" name="AR &amp; Restricted Recon" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Staffing" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Loan Snapshot" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Summary" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Stress Tests" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Decision History" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Financial Health" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="277">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -29,7 +31,7 @@
     <t>Heritage Academy Charter</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · nonprofit_501c3</t>
+    <t>Generated May 9, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +145,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -452,7 +454,10 @@
     <t>Operating Margin</t>
   </si>
   <si>
-    <t>Capital &amp; Debt Service</t>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Principal &amp; Capital Outlays</t>
   </si>
   <si>
     <t>Net Income</t>
@@ -497,6 +502,42 @@
     <t>Ending Cash</t>
   </si>
   <si>
+    <t>AR Schedule &amp; Restricted-vs-Unrestricted Cash Recon</t>
+  </si>
+  <si>
+    <t>AR = year's collected tuition × 30-day weighted delay ÷ 365. Bad debt = contracted − collected.</t>
+  </si>
+  <si>
+    <t>Accounts Receivable Schedule</t>
+  </si>
+  <si>
+    <t>Contracted Tuition (gross)</t>
+  </si>
+  <si>
+    <t>Collected Tuition (cash-basis)</t>
+  </si>
+  <si>
+    <t>Bad Debt (contracted − collected)</t>
+  </si>
+  <si>
+    <t>Year-end AR Balance (30-day delay)</t>
+  </si>
+  <si>
+    <t>Restricted vs Unrestricted Cash</t>
+  </si>
+  <si>
+    <t>Total Cash Position (accrual)</t>
+  </si>
+  <si>
+    <t>Restricted Cash (capital/program-restricted)</t>
+  </si>
+  <si>
+    <t>Unrestricted Cash (DSCR/runway basis)</t>
+  </si>
+  <si>
+    <t>Note: DSCR and cash-runway covenants in this packet are computed off Unrestricted Cash (row 14). Restricted gifts cannot legally service debt and are excluded from coverage tests.</t>
+  </si>
+  <si>
     <t>Staffing Detail</t>
   </si>
   <si>
@@ -563,6 +604,75 @@
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
+    <t>Standard Lender Stress Tests</t>
+  </si>
+  <si>
+    <t>Five fixed downside scenarios re-run on the canonical engine. Identical figures appear on the founder dashboard, consultant view, and lender packet PDF.</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Δ vs Base (Y1)</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>Canonical engine output. All scenarios below are deltas vs this row.</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-Even Students</t>
+  </si>
+  <si>
+    <t>Cash Runway (mo)</t>
+  </si>
+  <si>
+    <t>Break-Even Year</t>
+  </si>
+  <si>
+    <t>Enrollment -10%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 10% — the standard lender enrollment-miss sensitivity.</t>
+  </si>
+  <si>
+    <t>0y</t>
+  </si>
+  <si>
+    <t>Enrollment -20%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 20% — the stretch downside lenders use to confirm the school can survive a soft-launch.</t>
+  </si>
+  <si>
+    <t>ESA / Public Funding Delayed 3 Months</t>
+  </si>
+  <si>
+    <t>Year-1 ESA, school-choice, and public-funding receipts reduced by 25% (≈ 3 months delayed) to simulate a slow first disbursement.</t>
+  </si>
+  <si>
+    <t>Rent Shock +25%</t>
+  </si>
+  <si>
+    <t>Occupancy &amp; facility expense rows escalated by 25% — covers a lease renewal, market-rate reset, or unbudgeted CAM/utilities surprise.</t>
+  </si>
+  <si>
+    <t>Founder Comp Normalized to Market</t>
+  </si>
+  <si>
+    <t>Founder compensation re-cast at the market-rate benchmark (with benefits + payroll tax). The lender / board view of true operating cost.</t>
+  </si>
+  <si>
     <t>Decision History</t>
   </si>
   <si>
@@ -584,9 +694,6 @@
     <t>○ Red = action needed</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
     <t>Benchmark</t>
   </si>
   <si>
@@ -642,9 +749,6 @@
   </si>
   <si>
     <t>≥ 3 sources</t>
-  </si>
-  <si>
-    <t>DSCR</t>
   </si>
   <si>
     <t>≥ 1.25x</t>
@@ -762,7 +866,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -860,6 +964,18 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -999,7 +1115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1071,6 +1187,10 @@
     <xf numFmtId="167" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1084,15 +1204,40 @@
     <xf numFmtId="3" fontId="17" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1129,7 +1274,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1138,10 +1283,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1853,6 +1998,1345 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="28" t="str">
+        <f>Assumptions!D5</f>
+        <v>Heritage Academy Charter</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="28" t="str">
+        <f>Assumptions!D7</f>
+        <v>Charter School</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="28" t="str">
+        <f>Assumptions!D6</f>
+        <v>AZ</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="28">
+        <f>Assumptions!D8</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="29">
+        <f>Assumptions!D16</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="30">
+        <f>Drivers!G10</f>
+        <v>5634801.762</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C10" s="42">
+        <f>'5-Year P&amp;L'!G16</f>
+        <v>-1515735.12821206</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="C12" s="26"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="44">
+        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
+        <v>-0.28791851</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="35">
+        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
+        <v>0.51121464</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="30">
+        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
+        <v>11270</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="C16" s="30">
+        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
+        <v>14301</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="38">
+        <f>'Cash Flow &amp; DSCR'!C11</f>
+        <v>-1.6457711</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="C18" s="38">
+        <f>'Cash Flow &amp; DSCR'!G11</f>
+        <v>-14.2150884</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C21" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B21:C21"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFD97706"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="30">
+        <v>-169663.61081549362</v>
+      </c>
+      <c r="D7" s="30">
+        <v>550669.3891845066</v>
+      </c>
+      <c r="E7" s="30">
+        <v>1449561.7891845065</v>
+      </c>
+      <c r="F7" s="30">
+        <v>2403509.461184507</v>
+      </c>
+      <c r="G7" s="30">
+        <v>3426280.0633445065</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" s="29">
+        <v>-2.64</v>
+      </c>
+      <c r="D8" s="29">
+        <v>12.81</v>
+      </c>
+      <c r="E8" s="29">
+        <v>32.09</v>
+      </c>
+      <c r="F8" s="29">
+        <v>52.55</v>
+      </c>
+      <c r="G8" s="29">
+        <v>74.48</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="30">
+        <v>-94663.61081549362</v>
+      </c>
+      <c r="D9" s="30">
+        <v>456005.778369013</v>
+      </c>
+      <c r="E9" s="30">
+        <v>1905567.5675535195</v>
+      </c>
+      <c r="F9" s="30">
+        <v>4309077.0287380265</v>
+      </c>
+      <c r="G9" s="30">
+        <v>7735357.092082533</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="29">
+        <v>133</v>
+      </c>
+      <c r="D10" s="29">
+        <v>142</v>
+      </c>
+      <c r="E10" s="29">
+        <v>146</v>
+      </c>
+      <c r="F10" s="29">
+        <v>147</v>
+      </c>
+      <c r="G10" s="29">
+        <v>146</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="29">
+        <v>6</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="54" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="B14" s="50"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C16" s="30">
+        <v>-258663.61081549362</v>
+      </c>
+      <c r="D16" s="30">
+        <v>369429.3891845066</v>
+      </c>
+      <c r="E16" s="30">
+        <v>1172751.7891845065</v>
+      </c>
+      <c r="F16" s="30">
+        <v>2027589.4611845068</v>
+      </c>
+      <c r="G16" s="30">
+        <v>2947830.0633445065</v>
+      </c>
+      <c r="H16" s="36">
+        <v>-89000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C17" s="29">
+        <v>-4.55</v>
+      </c>
+      <c r="D17" s="29">
+        <v>8.92</v>
+      </c>
+      <c r="E17" s="29">
+        <v>26.15</v>
+      </c>
+      <c r="F17" s="29">
+        <v>44.48</v>
+      </c>
+      <c r="G17" s="29">
+        <v>64.22</v>
+      </c>
+      <c r="H17" s="54">
+        <v>-1.9099999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="30">
+        <v>-183663.61081549362</v>
+      </c>
+      <c r="D18" s="30">
+        <v>185765.778369013</v>
+      </c>
+      <c r="E18" s="30">
+        <v>1358517.5675535195</v>
+      </c>
+      <c r="F18" s="30">
+        <v>3386107.0287380265</v>
+      </c>
+      <c r="G18" s="30">
+        <v>6333937.092082533</v>
+      </c>
+      <c r="H18" s="36">
+        <v>-89000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19" s="29">
+        <v>131</v>
+      </c>
+      <c r="D19" s="29">
+        <v>141</v>
+      </c>
+      <c r="E19" s="29">
+        <v>145</v>
+      </c>
+      <c r="F19" s="29">
+        <v>147</v>
+      </c>
+      <c r="G19" s="29">
+        <v>146</v>
+      </c>
+      <c r="H19" s="54">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="29">
+        <v>5</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="54">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="51" t="s">
+        <v>209</v>
+      </c>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C25" s="30">
+        <v>-347663.6108154935</v>
+      </c>
+      <c r="D25" s="30">
+        <v>188189.3891845066</v>
+      </c>
+      <c r="E25" s="30">
+        <v>895941.7891845065</v>
+      </c>
+      <c r="F25" s="30">
+        <v>1651669.4611845068</v>
+      </c>
+      <c r="G25" s="30">
+        <v>2469380.0633445065</v>
+      </c>
+      <c r="H25" s="36">
+        <v>-177999.99999999988</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="29">
+        <v>-6.46</v>
+      </c>
+      <c r="D26" s="29">
+        <v>5.04</v>
+      </c>
+      <c r="E26" s="29">
+        <v>20.21</v>
+      </c>
+      <c r="F26" s="29">
+        <v>36.42</v>
+      </c>
+      <c r="G26" s="29">
+        <v>53.96</v>
+      </c>
+      <c r="H26" s="54">
+        <v>-3.82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="30">
+        <v>-272663.6108154935</v>
+      </c>
+      <c r="D27" s="30">
+        <v>-84474.2216309869</v>
+      </c>
+      <c r="E27" s="30">
+        <v>811467.5675535196</v>
+      </c>
+      <c r="F27" s="30">
+        <v>2463137.0287380265</v>
+      </c>
+      <c r="G27" s="30">
+        <v>4932517.092082533</v>
+      </c>
+      <c r="H27" s="36">
+        <v>-177999.99999999988</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="29">
+        <v>129</v>
+      </c>
+      <c r="D28" s="29">
+        <v>139</v>
+      </c>
+      <c r="E28" s="29">
+        <v>145</v>
+      </c>
+      <c r="F28" s="29">
+        <v>147</v>
+      </c>
+      <c r="G28" s="29">
+        <v>146</v>
+      </c>
+      <c r="H28" s="54">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="29">
+        <v>4</v>
+      </c>
+      <c r="D29" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="54">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="52" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="51" t="s">
+        <v>211</v>
+      </c>
+      <c r="B33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" s="30">
+        <v>-428413.6108154935</v>
+      </c>
+      <c r="D34" s="30">
+        <v>550669.3891845066</v>
+      </c>
+      <c r="E34" s="30">
+        <v>1449561.7891845065</v>
+      </c>
+      <c r="F34" s="30">
+        <v>2403509.461184507</v>
+      </c>
+      <c r="G34" s="30">
+        <v>3426280.0633445065</v>
+      </c>
+      <c r="H34" s="36">
+        <v>-258749.99999999988</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C35" s="29">
+        <v>-8.19</v>
+      </c>
+      <c r="D35" s="29">
+        <v>12.81</v>
+      </c>
+      <c r="E35" s="29">
+        <v>32.09</v>
+      </c>
+      <c r="F35" s="29">
+        <v>52.55</v>
+      </c>
+      <c r="G35" s="29">
+        <v>74.48</v>
+      </c>
+      <c r="H35" s="54">
+        <v>-5.549999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="30">
+        <v>-353413.6108154935</v>
+      </c>
+      <c r="D36" s="30">
+        <v>197255.7783690131</v>
+      </c>
+      <c r="E36" s="30">
+        <v>1646817.5675535197</v>
+      </c>
+      <c r="F36" s="30">
+        <v>4050327.0287380265</v>
+      </c>
+      <c r="G36" s="30">
+        <v>7476607.092082533</v>
+      </c>
+      <c r="H36" s="36">
+        <v>-258749.99999999988</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C37" s="29">
+        <v>177</v>
+      </c>
+      <c r="D37" s="29">
+        <v>142</v>
+      </c>
+      <c r="E37" s="29">
+        <v>146</v>
+      </c>
+      <c r="F37" s="29">
+        <v>147</v>
+      </c>
+      <c r="G37" s="29">
+        <v>146</v>
+      </c>
+      <c r="H37" s="54">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="C38" s="29">
+        <v>4</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="54">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C39" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H39" s="52" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="B41" s="50"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="50"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C43" s="30">
+        <v>-236746.9441488271</v>
+      </c>
+      <c r="D43" s="30">
+        <v>467754.3891845066</v>
+      </c>
+      <c r="E43" s="30">
+        <v>1364158.3891845066</v>
+      </c>
+      <c r="F43" s="30">
+        <v>2315545.4791845065</v>
+      </c>
+      <c r="G43" s="30">
+        <v>3335675.2318845065</v>
+      </c>
+      <c r="H43" s="36">
+        <v>-67083.33333333349</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" s="29">
+        <v>-4.08</v>
+      </c>
+      <c r="D44" s="29">
+        <v>11.03</v>
+      </c>
+      <c r="E44" s="29">
+        <v>30.26</v>
+      </c>
+      <c r="F44" s="29">
+        <v>50.66</v>
+      </c>
+      <c r="G44" s="29">
+        <v>72.54</v>
+      </c>
+      <c r="H44" s="54">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C45" s="30">
+        <v>-161746.9441488271</v>
+      </c>
+      <c r="D45" s="30">
+        <v>306007.4450356795</v>
+      </c>
+      <c r="E45" s="30">
+        <v>1670165.834220186</v>
+      </c>
+      <c r="F45" s="30">
+        <v>3985711.3134046923</v>
+      </c>
+      <c r="G45" s="30">
+        <v>7321386.545289199</v>
+      </c>
+      <c r="H45" s="36">
+        <v>-67083.33333333349</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="29">
+        <v>141</v>
+      </c>
+      <c r="D46" s="29">
+        <v>150</v>
+      </c>
+      <c r="E46" s="29">
+        <v>155</v>
+      </c>
+      <c r="F46" s="29">
+        <v>157</v>
+      </c>
+      <c r="G46" s="29">
+        <v>156</v>
+      </c>
+      <c r="H46" s="54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" s="29">
+        <v>5</v>
+      </c>
+      <c r="D47" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="54">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="52" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="50" t="s">
+        <v>214</v>
+      </c>
+      <c r="B50" s="50"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
+      <c r="G50" s="50"/>
+      <c r="H50" s="50"/>
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" s="51"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="51"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" s="30">
+        <v>-156298.61081549362</v>
+      </c>
+      <c r="D52" s="30">
+        <v>530621.8891845066</v>
+      </c>
+      <c r="E52" s="30">
+        <v>1389419.2891845065</v>
+      </c>
+      <c r="F52" s="30">
+        <v>2343366.961184507</v>
+      </c>
+      <c r="G52" s="30">
+        <v>3319360.0633445065</v>
+      </c>
+      <c r="H52" s="36">
+        <v>13365</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="C53" s="29">
+        <v>-2.35</v>
+      </c>
+      <c r="D53" s="29">
+        <v>12.38</v>
+      </c>
+      <c r="E53" s="29">
+        <v>30.8</v>
+      </c>
+      <c r="F53" s="29">
+        <v>51.26</v>
+      </c>
+      <c r="G53" s="29">
+        <v>72.19</v>
+      </c>
+      <c r="H53" s="54">
+        <v>0.29000000000000004</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" s="30">
+        <v>-94663.61081549362</v>
+      </c>
+      <c r="D54" s="30">
+        <v>456005.778369013</v>
+      </c>
+      <c r="E54" s="30">
+        <v>1905567.5675535195</v>
+      </c>
+      <c r="F54" s="30">
+        <v>4309077.0287380265</v>
+      </c>
+      <c r="G54" s="30">
+        <v>7735357.092082533</v>
+      </c>
+      <c r="H54" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C55" s="29">
+        <v>133</v>
+      </c>
+      <c r="D55" s="29">
+        <v>142</v>
+      </c>
+      <c r="E55" s="29">
+        <v>146</v>
+      </c>
+      <c r="F55" s="29">
+        <v>147</v>
+      </c>
+      <c r="G55" s="29">
+        <v>146</v>
+      </c>
+      <c r="H55" s="54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="C56" s="29">
+        <v>6</v>
+      </c>
+      <c r="D56" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" s="54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="C57" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="D57" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="52" t="s">
+        <v>207</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A51:H51"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="B1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1868,7 +3352,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -1878,26 +3362,26 @@
       <c r="H1" s="13"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="B2" s="56" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
+      <c r="B4" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1913,7 +3397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -1931,7 +3415,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1954,37 +3438,37 @@
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>185</v>
-      </c>
-      <c r="F4" s="48" t="s">
-        <v>186</v>
+      <c r="B4" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="50" t="s">
+      <c r="B6" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="61" t="s">
         <v>115</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="50" t="s">
+      <c r="G6" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="50" t="s">
-        <v>188</v>
+      <c r="H6" s="61" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2009,7 +3493,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
       <c r="C8" s="30">
         <v>1414000</v>
@@ -2029,7 +3513,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="C9" s="30">
         <v>985486.2857142857</v>
@@ -2049,7 +3533,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="28" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="C10" s="30">
         <v>604000</v>
@@ -2069,7 +3553,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="C11" s="30">
         <v>106628.6108154935</v>
@@ -2089,7 +3573,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="31" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="33">
         <v>-282114.8965297792</v>
@@ -2109,7 +3593,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="33">
         <v>-282114.8965297792</v>
@@ -2129,50 +3613,50 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="C14" s="51">
+        <v>146</v>
+      </c>
+      <c r="C14" s="62">
         <v>-0.19951548552318188</v>
       </c>
-      <c r="D14" s="51">
+      <c r="D14" s="62">
         <v>-0.03046314664581019</v>
       </c>
-      <c r="E14" s="52">
+      <c r="E14" s="63">
         <v>0.0005159442661968101</v>
       </c>
-      <c r="F14" s="51">
+      <c r="F14" s="62">
         <v>-0.07762995822770193</v>
       </c>
-      <c r="G14" s="51">
+      <c r="G14" s="62">
         <v>-0.2879185120528036</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="31" t="s">
-        <v>193</v>
-      </c>
-      <c r="C15" s="53">
+        <v>228</v>
+      </c>
+      <c r="C15" s="64">
         <v>11783.333333333334</v>
       </c>
-      <c r="D15" s="53">
+      <c r="D15" s="64">
         <v>11263.25</v>
       </c>
-      <c r="E15" s="53">
+      <c r="E15" s="64">
         <v>11152.36</v>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="64">
         <v>11157.2158</v>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="64">
         <v>11269.603524</v>
       </c>
-      <c r="H15" s="54" t="s">
-        <v>194</v>
+      <c r="H15" s="65" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="31" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="C16" s="36">
         <v>14134.290804414828</v>
@@ -2192,7 +3676,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="C17" s="30">
         <v>650</v>
@@ -2212,402 +3696,402 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="28" t="s">
-        <v>197</v>
-      </c>
-      <c r="C18" s="55">
+        <v>232</v>
+      </c>
+      <c r="C18" s="66">
         <v>2683.3333333333335</v>
       </c>
-      <c r="D18" s="53">
+      <c r="D18" s="64">
         <v>1658.3</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="64">
         <v>1138.6993333333332</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="64">
         <v>879.645235</v>
       </c>
-      <c r="G18" s="53">
+      <c r="G18" s="64">
         <v>724.8276736400001</v>
       </c>
-      <c r="H18" s="54" t="s">
-        <v>198</v>
+      <c r="H18" s="65" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="31" t="s">
-        <v>199</v>
-      </c>
-      <c r="C19" s="40">
+        <v>234</v>
+      </c>
+      <c r="C19" s="42">
         <v>-2350.957471081493</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="42">
         <v>-343.1140364584216</v>
       </c>
-      <c r="E19" s="56">
+      <c r="E19" s="67">
         <v>5.753996196562657</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="42">
         <v>-866.1341964914559</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="42">
         <v>-3244.727478055112</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="C20" s="51">
+        <v>235</v>
+      </c>
+      <c r="C20" s="62">
         <v>0.6969492826833703</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="63">
         <v>0.5994943125398341</v>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="63">
         <v>0.5534195972076122</v>
       </c>
-      <c r="F20" s="57">
+      <c r="F20" s="68">
         <v>0.5203488896294841</v>
       </c>
-      <c r="G20" s="57">
+      <c r="G20" s="68">
         <v>0.5112146441389667</v>
       </c>
-      <c r="H20" s="54" t="s">
-        <v>201</v>
+      <c r="H20" s="65" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="C21" s="51">
+        <v>237</v>
+      </c>
+      <c r="C21" s="62">
         <v>0.22772277227722773</v>
       </c>
-      <c r="D21" s="57">
+      <c r="D21" s="68">
         <v>0.14723103899851286</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="68">
         <v>0.10210388952054393</v>
       </c>
-      <c r="F21" s="57">
+      <c r="F21" s="68">
         <v>0.07884092687353057</v>
       </c>
-      <c r="G21" s="57">
+      <c r="G21" s="68">
         <v>0.06431705180190153</v>
       </c>
-      <c r="H21" s="54" t="s">
-        <v>203</v>
+      <c r="H21" s="65" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="51">
+      <c r="C22" s="62">
         <v>-0.12410628409779752</v>
       </c>
-      <c r="D22" s="52">
+      <c r="D22" s="63">
         <v>0.016871597240498658</v>
       </c>
-      <c r="E22" s="52">
+      <c r="E22" s="63">
         <v>0.03238621232769336</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="62">
         <v>-0.0537376600220211</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="62">
         <v>-0.26899528896187336</v>
       </c>
-      <c r="H22" s="54" t="s">
-        <v>204</v>
+      <c r="H22" s="65" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="C23" s="58">
+        <v>240</v>
+      </c>
+      <c r="C23" s="69">
         <v>3</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D23" s="69">
         <v>3</v>
       </c>
-      <c r="E23" s="58">
+      <c r="E23" s="69">
         <v>3</v>
       </c>
-      <c r="F23" s="58">
+      <c r="F23" s="69">
         <v>3</v>
       </c>
-      <c r="G23" s="58">
+      <c r="G23" s="69">
         <v>3</v>
       </c>
-      <c r="H23" s="54" t="s">
-        <v>206</v>
+      <c r="H23" s="65" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="C24" s="59">
+        <v>201</v>
+      </c>
+      <c r="C24" s="70">
         <v>-1.645771096258031</v>
       </c>
-      <c r="D24" s="59">
+      <c r="D24" s="70">
         <v>0.35643157341300485</v>
       </c>
-      <c r="E24" s="59">
+      <c r="E24" s="70">
         <v>1.0161888900715002</v>
       </c>
-      <c r="F24" s="59">
+      <c r="F24" s="70">
         <v>-2.2491624522434597</v>
       </c>
-      <c r="G24" s="59">
+      <c r="G24" s="70">
         <v>-14.215088395316705</v>
       </c>
-      <c r="H24" s="54" t="s">
-        <v>208</v>
+      <c r="H24" s="65" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="C25" s="60" t="str">
+        <v>243</v>
+      </c>
+      <c r="C25" s="71" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="60" t="str">
+      <c r="D25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="60" t="str">
+      <c r="E25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="60" t="str">
+      <c r="F25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="60" t="str">
+      <c r="G25" s="71" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="54" t="s">
+      <c r="H25" s="65" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="C26" s="61">
+        <v>244</v>
+      </c>
+      <c r="C26" s="72">
         <v>-2</v>
       </c>
-      <c r="D26" s="61">
+      <c r="D26" s="72">
         <v>-2</v>
       </c>
-      <c r="E26" s="61">
+      <c r="E26" s="72">
         <v>-1</v>
       </c>
-      <c r="F26" s="61">
+      <c r="F26" s="72">
         <v>-2</v>
       </c>
-      <c r="G26" s="61">
+      <c r="G26" s="72">
         <v>-4</v>
       </c>
-      <c r="H26" s="54" t="s">
-        <v>211</v>
+      <c r="H26" s="65" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="C27" s="61">
-        <v>0</v>
-      </c>
-      <c r="D27" s="61">
-        <v>0</v>
-      </c>
-      <c r="E27" s="61">
-        <v>0</v>
-      </c>
-      <c r="F27" s="61">
-        <v>0</v>
-      </c>
-      <c r="G27" s="61">
-        <v>0</v>
-      </c>
-      <c r="H27" s="54" t="s">
-        <v>213</v>
+        <v>246</v>
+      </c>
+      <c r="C27" s="72">
+        <v>0</v>
+      </c>
+      <c r="D27" s="72">
+        <v>0</v>
+      </c>
+      <c r="E27" s="72">
+        <v>0</v>
+      </c>
+      <c r="F27" s="72">
+        <v>0</v>
+      </c>
+      <c r="G27" s="72">
+        <v>0</v>
+      </c>
+      <c r="H27" s="65" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="49" t="s">
-        <v>214</v>
-      </c>
-      <c r="C29" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="D29" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49" t="s">
-        <v>217</v>
-      </c>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
+      <c r="B29" s="60" t="s">
+        <v>248</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="D29" s="60" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60" t="s">
+        <v>251</v>
+      </c>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="62" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="D30" s="64" t="s">
-        <v>220</v>
-      </c>
-      <c r="E30" s="64"/>
-      <c r="F30" s="65" t="s">
-        <v>221</v>
-      </c>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
+      <c r="B30" s="73" t="s">
+        <v>252</v>
+      </c>
+      <c r="C30" s="74" t="s">
+        <v>253</v>
+      </c>
+      <c r="D30" s="75" t="s">
+        <v>254</v>
+      </c>
+      <c r="E30" s="75"/>
+      <c r="F30" s="76" t="s">
+        <v>255</v>
+      </c>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="62" t="s">
-        <v>222</v>
-      </c>
-      <c r="C31" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="D31" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="E31" s="64"/>
-      <c r="F31" s="65" t="s">
-        <v>224</v>
-      </c>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
+      <c r="B31" s="73" t="s">
+        <v>256</v>
+      </c>
+      <c r="C31" s="74" t="s">
+        <v>253</v>
+      </c>
+      <c r="D31" s="75" t="s">
+        <v>257</v>
+      </c>
+      <c r="E31" s="75"/>
+      <c r="F31" s="76" t="s">
+        <v>258</v>
+      </c>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="62" t="s">
-        <v>225</v>
-      </c>
-      <c r="C32" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="D32" s="64" t="s">
-        <v>227</v>
-      </c>
-      <c r="E32" s="64"/>
-      <c r="F32" s="65" t="s">
-        <v>228</v>
-      </c>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
+      <c r="B32" s="73" t="s">
+        <v>259</v>
+      </c>
+      <c r="C32" s="77" t="s">
+        <v>260</v>
+      </c>
+      <c r="D32" s="75" t="s">
+        <v>261</v>
+      </c>
+      <c r="E32" s="75"/>
+      <c r="F32" s="76" t="s">
+        <v>262</v>
+      </c>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+      <c r="I32" s="76"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="62" t="s">
-        <v>229</v>
-      </c>
-      <c r="C33" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="D33" s="64" t="s">
-        <v>230</v>
-      </c>
-      <c r="E33" s="64"/>
-      <c r="F33" s="65" t="s">
-        <v>231</v>
-      </c>
-      <c r="G33" s="65"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="65"/>
+      <c r="B33" s="73" t="s">
+        <v>263</v>
+      </c>
+      <c r="C33" s="77" t="s">
+        <v>260</v>
+      </c>
+      <c r="D33" s="75" t="s">
+        <v>264</v>
+      </c>
+      <c r="E33" s="75"/>
+      <c r="F33" s="76" t="s">
+        <v>265</v>
+      </c>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+      <c r="I33" s="76"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="62" t="s">
-        <v>232</v>
-      </c>
-      <c r="C34" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="D34" s="64" t="s">
-        <v>233</v>
-      </c>
-      <c r="E34" s="64"/>
-      <c r="F34" s="65" t="s">
-        <v>234</v>
-      </c>
-      <c r="G34" s="65"/>
-      <c r="H34" s="65"/>
-      <c r="I34" s="65"/>
+      <c r="B34" s="73" t="s">
+        <v>266</v>
+      </c>
+      <c r="C34" s="74" t="s">
+        <v>253</v>
+      </c>
+      <c r="D34" s="75" t="s">
+        <v>267</v>
+      </c>
+      <c r="E34" s="75"/>
+      <c r="F34" s="76" t="s">
+        <v>268</v>
+      </c>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="76"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="62" t="s">
-        <v>235</v>
-      </c>
-      <c r="C35" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="D35" s="64" t="s">
-        <v>236</v>
-      </c>
-      <c r="E35" s="64"/>
-      <c r="F35" s="65" t="s">
-        <v>237</v>
-      </c>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
+      <c r="B35" s="73" t="s">
+        <v>269</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>260</v>
+      </c>
+      <c r="D35" s="75" t="s">
+        <v>270</v>
+      </c>
+      <c r="E35" s="75"/>
+      <c r="F35" s="76" t="s">
+        <v>271</v>
+      </c>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="62" t="s">
-        <v>238</v>
-      </c>
-      <c r="C36" s="63" t="s">
-        <v>219</v>
-      </c>
-      <c r="D36" s="64" t="s">
-        <v>239</v>
-      </c>
-      <c r="E36" s="64"/>
-      <c r="F36" s="65" t="s">
-        <v>240</v>
-      </c>
-      <c r="G36" s="65"/>
-      <c r="H36" s="65"/>
-      <c r="I36" s="65"/>
+      <c r="B36" s="73" t="s">
+        <v>272</v>
+      </c>
+      <c r="C36" s="74" t="s">
+        <v>253</v>
+      </c>
+      <c r="D36" s="75" t="s">
+        <v>273</v>
+      </c>
+      <c r="E36" s="75"/>
+      <c r="F36" s="76" t="s">
+        <v>274</v>
+      </c>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="62" t="s">
+      <c r="B38" s="73" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="D38" s="31"/>
       <c r="E38" s="31"/>
       <c r="F38" s="31"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="67" t="s">
-        <v>242</v>
-      </c>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
+      <c r="B40" s="78" t="s">
+        <v>276</v>
+      </c>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3855,7 +5339,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G25"/>
+  <dimension ref="B1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4171,118 +5655,138 @@
         <v>143</v>
       </c>
       <c r="C19" s="30">
-        <f>'Cash Flow &amp; DSCR'!C9</f>
-        <v>106628.61081549</v>
+        <v>20283</v>
       </c>
       <c r="D19" s="30">
-        <f>'Cash Flow &amp; DSCR'!D9</f>
-        <v>106628.61081549</v>
+        <v>18658</v>
       </c>
       <c r="E19" s="30">
-        <f>'Cash Flow &amp; DSCR'!E9</f>
-        <v>106628.61081549</v>
+        <v>16933</v>
       </c>
       <c r="F19" s="30">
-        <f>'Cash Flow &amp; DSCR'!F9</f>
-        <v>106628.61081549</v>
+        <v>15102</v>
       </c>
       <c r="G19" s="30">
-        <f>'Cash Flow &amp; DSCR'!G9</f>
-        <v>106628.61081549</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="31" t="s">
+        <v>13157</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="C21" s="33">
-        <f>C16-C19</f>
+      <c r="C20" s="30">
+        <f>'Cash Flow &amp; DSCR'!C9-C19</f>
+        <v>86345.27727044</v>
+      </c>
+      <c r="D20" s="30">
+        <f>'Cash Flow &amp; DSCR'!D9-D19</f>
+        <v>87970.19632545</v>
+      </c>
+      <c r="E20" s="30">
+        <f>'Cash Flow &amp; DSCR'!E9-E19</f>
+        <v>89695.33683222</v>
+      </c>
+      <c r="F20" s="30">
+        <f>'Cash Flow &amp; DSCR'!F9-F19</f>
+        <v>91526.88023061</v>
+      </c>
+      <c r="G20" s="30">
+        <f>'Cash Flow &amp; DSCR'!G9-G19</f>
+        <v>93471.38921815</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="33">
+        <f>C16-C19-C20</f>
         <v>-282114.89652978</v>
       </c>
-      <c r="D21" s="33">
-        <f>D16-D19</f>
+      <c r="D22" s="33">
+        <f>D16-D19-D20</f>
         <v>-68622.80729168</v>
       </c>
-      <c r="E21" s="34">
-        <f>E16-E19</f>
+      <c r="E22" s="34">
+        <f>E16-E19-E20</f>
         <v>1726.19885897</v>
       </c>
-      <c r="F21" s="33">
-        <f>F16-F19</f>
+      <c r="F22" s="33">
+        <f>F16-F19-F20</f>
         <v>-346453.67859658</v>
       </c>
-      <c r="G21" s="33">
-        <f>G16-G19</f>
+      <c r="G22" s="33">
+        <f>G16-G19-G20</f>
         <v>-1622363.73902756</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="C22" s="35">
-        <f>IF(C10&gt;0,C21/C10,0)</f>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C23" s="35">
+        <f>IF(C10&gt;0,C22/C10,0)</f>
         <v>-0.19951549</v>
       </c>
-      <c r="D22" s="35">
-        <f>IF(D10&gt;0,D21/D10,0)</f>
+      <c r="D23" s="35">
+        <f>IF(D10&gt;0,D22/D10,0)</f>
         <v>-0.03046315</v>
       </c>
-      <c r="E22" s="35">
-        <f>IF(E10&gt;0,E21/E10,0)</f>
+      <c r="E23" s="35">
+        <f>IF(E10&gt;0,E22/E10,0)</f>
         <v>0.00051594</v>
       </c>
-      <c r="F22" s="35">
-        <f>IF(F10&gt;0,F21/F10,0)</f>
+      <c r="F23" s="35">
+        <f>IF(F10&gt;0,F22/F10,0)</f>
         <v>-0.07762996</v>
       </c>
-      <c r="G22" s="35">
-        <f>IF(G10&gt;0,G21/G10,0)</f>
+      <c r="G23" s="35">
+        <f>IF(G10&gt;0,G22/G10,0)</f>
         <v>-0.28791851</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" s="36">
-        <f>C21</f>
-        <v>-282114.89652978</v>
-      </c>
-      <c r="D24" s="36">
-        <f>C24+D21</f>
-        <v>-350737.70382146</v>
-      </c>
-      <c r="E24" s="36">
-        <f>D24+E21</f>
-        <v>-349011.50496249</v>
-      </c>
-      <c r="F24" s="36">
-        <f>E24+F21</f>
-        <v>-695465.18355908</v>
-      </c>
-      <c r="G24" s="36">
-        <f>F24+G21</f>
-        <v>-2317828.92258663</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="C25" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="37" t="s">
+      <c r="C25" s="36">
+        <f>C22</f>
+        <v>-282114.89652978</v>
+      </c>
+      <c r="D25" s="36">
+        <f>C25+D22</f>
+        <v>-350737.70382146</v>
+      </c>
+      <c r="E25" s="36">
+        <f>D25+E22</f>
+        <v>-349011.50496249</v>
+      </c>
+      <c r="F25" s="36">
+        <f>E25+F22</f>
+        <v>-695465.18355908</v>
+      </c>
+      <c r="G25" s="36">
+        <f>F25+G22</f>
+        <v>-2317828.92258663</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="37" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4314,7 +5818,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4342,7 +5846,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="36" t="str">
         <f>Assumptions!D57</f>
@@ -4367,7 +5871,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C5" s="30">
         <f>'5-Year P&amp;L'!C16</f>
@@ -4392,7 +5896,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C7" s="30">
         <f>Assumptions!D58</f>
@@ -4417,7 +5921,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" s="30">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4442,7 +5946,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="32">
         <f>C7+C8</f>
@@ -4467,7 +5971,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="31" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C11" s="38">
         <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
@@ -4492,7 +5996,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="30">
         <f>C5-C9</f>
@@ -4517,7 +6021,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="36">
         <f>C5-C9</f>
@@ -4542,7 +6046,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C16" s="33">
         <f>C4+C14</f>
@@ -4580,6 +6084,267 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF7C3AED"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:G17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="26"/>
+      <c r="C4" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="30">
+        <v>0</v>
+      </c>
+      <c r="D6" s="30">
+        <v>0</v>
+      </c>
+      <c r="E6" s="30">
+        <v>0</v>
+      </c>
+      <c r="F6" s="30">
+        <v>0</v>
+      </c>
+      <c r="G6" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="30">
+        <v>0</v>
+      </c>
+      <c r="D7" s="30">
+        <v>0</v>
+      </c>
+      <c r="E7" s="30">
+        <v>0</v>
+      </c>
+      <c r="F7" s="30">
+        <v>0</v>
+      </c>
+      <c r="G7" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="34" t="str">
+        <f>C6-C7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="34" t="str">
+        <f>D6-D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="34" t="str">
+        <f>E6-E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="34" t="str">
+        <f>F6-F7</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="34" t="str">
+        <f>G6-G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="32" t="str">
+        <f>C7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="32" t="str">
+        <f>D7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="32" t="str">
+        <f>E7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="32" t="str">
+        <f>F7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="32" t="str">
+        <f>G7*30/365</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="39"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="30">
+        <v>-282114.8965297792</v>
+      </c>
+      <c r="D12" s="30">
+        <v>-350737.7038214635</v>
+      </c>
+      <c r="E12" s="30">
+        <v>-349011.5049624947</v>
+      </c>
+      <c r="F12" s="30">
+        <v>-695465.1835590771</v>
+      </c>
+      <c r="G12" s="30">
+        <v>-2317828.922586633</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="C13" s="30">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="C14" s="33">
+        <f>C12-C13</f>
+        <v>-282114.89652978</v>
+      </c>
+      <c r="D14" s="33">
+        <f>D12-D13</f>
+        <v>-350737.70382146</v>
+      </c>
+      <c r="E14" s="33">
+        <f>E12-E13</f>
+        <v>-349011.50496249</v>
+      </c>
+      <c r="F14" s="33">
+        <f>F12-F13</f>
+        <v>-695465.18355908</v>
+      </c>
+      <c r="G14" s="33">
+        <f>G12-G13</f>
+        <v>-2317828.92258663</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B16:G17"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4593,7 +6358,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4621,7 +6386,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="C4" s="29">
         <f>Drivers!C12</f>
@@ -4646,7 +6411,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="28" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="C5" s="29">
         <f>Assumptions!D35</f>
@@ -4671,25 +6436,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="C6" s="39">
+        <v>174</v>
+      </c>
+      <c r="C6" s="41">
         <f>C4+C5</f>
         <v>15</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="41">
         <f>D4+D5</f>
         <v>21</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="41">
         <f>E4+E5</f>
         <v>29</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="41">
         <f>F4+F5</f>
         <v>36</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="41">
         <f>G4+G5</f>
         <v>44</v>
       </c>
@@ -4706,7 +6471,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD97706"/>
@@ -4722,13 +6487,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="28" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C3" s="30">
         <f>Assumptions!D59</f>
@@ -4737,7 +6502,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C4" s="35">
         <f>Assumptions!D60</f>
@@ -4755,7 +6520,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C6" s="36">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4764,7 +6529,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="28" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="C8" s="38">
         <f>'Cash Flow &amp; DSCR'!C11</f>
@@ -4781,174 +6546,4 @@
     <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF328555"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="28" t="str">
-        <f>Assumptions!D5</f>
-        <v>Heritage Academy Charter</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="28" t="str">
-        <f>Assumptions!D7</f>
-        <v>Charter School</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="28" t="str">
-        <f>Assumptions!D6</f>
-        <v>AZ</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="28">
-        <f>Assumptions!D8</f>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="29">
-        <f>Assumptions!D16</f>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C9" s="30">
-        <f>Drivers!G10</f>
-        <v>5634801.762</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="C10" s="40">
-        <f>'5-Year P&amp;L'!G16</f>
-        <v>-1515735.12821206</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="C12" s="26"/>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" s="42">
-        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
-        <v>-0.28791851</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C14" s="35">
-        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
-        <v>0.51121464</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" s="30">
-        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
-        <v>11270</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C16" s="30">
-        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
-        <v>14301</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" s="38">
-        <f>'Cash Flow &amp; DSCR'!C11</f>
-        <v>-1.6457711</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C18" s="38">
-        <f>'Cash Flow &amp; DSCR'!G11</f>
-        <v>-14.2150884</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="C21" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B21:C21"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>